--- a/review/State-Not-Situation-German-review.xlsx
+++ b/review/State-Not-Situation-German-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="German review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$266</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$279</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F266"/>
+  <dimension ref="A1:F279"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -831,7 +831,7 @@
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Ein Feldführer für den Moment, bevor aus Deutung Wirklichkeit wird. Sechzehn Fälle. Drei Befunde. Eine Frage: Zustand oder Situation? Von Ivana Budišin.</t>
+          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird. Sechzehn Fälle. Drei Befunde. Eine Frage: Zustand oder Situation? Von Ivana Budišin.</t>
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
@@ -855,7 +855,7 @@
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Das Cover zu State. Not Situation. von Ivana Budišin: das Wort STATE groß in Rot über NOT SITUATION in Schwarz, auf cremefarbenem Grund.</t>
+          <t>Das Cover von State. Not Situation. von Ivana Budišin: das Wort STATE groß in Rot über NOT SITUATION in Schwarz, auf Cremeweiß.</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -903,7 +903,7 @@
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Die ersten Seiten aus State. Not Situation. von Ivana Budišin: ein Pilot, Dunst über offenem Wasser und ein Satz der Federal Aviation Administration.</t>
+          <t>Die ersten Seiten von State. Not Situation. von Ivana Budišin: ein Pilot, Dunst über offenem Wasser und ein Satz der Federal Aviation Administration.</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -951,7 +951,7 @@
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial zu State. Not Situation. von Ivana Budišin: Covermotiv, Foto der Autorin, Biografie, Publikationsdaten und Kontakt.</t>
+          <t>Pressematerial zu State. Not Situation. von Ivana Budišin: Cover, Foto der Autorin, Biografie, bibliografische Angaben und Kontakt.</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -1011,7 +1011,7 @@
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Lesen</t>
+          <t>Leseprobe</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Erscheint in Kürze</t>
+          <t>Erscheint demnächst</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>ihre@email.com</t>
+          <t>name@beispiel.de</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Benachrichtigen Sie mich</t>
+          <t>Benachrichtigen</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Schreiben Sie mir, um benachrichtigt zu werden</t>
+          <t>Per E-Mail benachrichtigen lassen</t>
         </is>
       </c>
       <c r="E32" s="11" t="n"/>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Sagen Sie mir Bescheid, wenn State. Not Situation. erscheint</t>
+          <t>Benachrichtigung, wenn State. Not Situation. erscheint</t>
         </is>
       </c>
       <c r="E33" s="11" t="n"/>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Bitte sagen Sie mir Bescheid, wenn State. Not Situation. erhältlich ist.</t>
+          <t>Bitte geben Sie mir Bescheid, wenn State. Not Situation. erhältlich ist.</t>
         </is>
       </c>
       <c r="E34" s="11" t="n"/>
@@ -1611,7 +1611,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Ein Feldführer für den Moment, bevor aus Deutung Wirklichkeit wird</t>
+          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
         </is>
       </c>
       <c r="E39" s="11" t="n"/>
@@ -1702,12 +1702,12 @@
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>The book open at its half title page, which reads State. Not Situation.</t>
+          <t>The book open at its title page, which reads State. Not Situation.</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Das Buch, aufgeschlagen auf dem Schmutztitel, auf dem State. Not Situation. steht.</t>
+          <t>Das Buch, aufgeschlagen auf der Titelseite, auf der State. Not Situation. steht.</t>
         </is>
       </c>
       <c r="E43" s="11" t="n"/>
@@ -1764,7 +1764,7 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>“BEFORE WE BEGIN” — THE THREE INSTRUCTIONS</t>
+          <t>“THE FIRST MISREADING” — PAGE 10, THE FIVE READINGS</t>
         </is>
       </c>
       <c r="B46" s="8" t="n"/>
@@ -1776,22 +1776,22 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>reading.eyebrow</t>
+          <t>misreading.eyebrow</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>The first misreading</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Bevor wir beginnen</t>
+          <t>Die erste Fehldeutung</t>
         </is>
       </c>
       <c r="E47" s="11" t="n"/>
@@ -1800,22 +1800,22 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>reading.lead</t>
+          <t>misreading.lines[0]</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
+          <t>Nothing went wrong on this day.</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>Was auch immer Sie fühlen, während Sie diesen Satz lesen.</t>
+          <t>An diesem Tag ging nichts schief.</t>
         </is>
       </c>
       <c r="E48" s="11" t="n"/>
@@ -1824,22 +1824,22 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>misreading.lines[1]</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>The instruments were working.</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Prüfen Sie Ihren Kiefer.</t>
+          <t>Die Instrumente funktionierten.</t>
         </is>
       </c>
       <c r="E49" s="11" t="n"/>
@@ -1848,22 +1848,22 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>misreading.lines[2]</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>The data was there the whole time.</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Prüfen Sie Ihren Atem.</t>
+          <t>Die Daten waren die ganze Zeit da.</t>
         </is>
       </c>
       <c r="E50" s="11" t="n"/>
@@ -1872,22 +1872,22 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>misreading.investigationLabel</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>This book is the</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Prüfen Sie Ihre Schultern.</t>
+          <t>Dieses Buch ist die</t>
         </is>
       </c>
       <c r="E51" s="11" t="n"/>
@@ -1896,46 +1896,46 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>misreading.investigation</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>Investigation.</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Was Sie gefunden haben, ist ein Befund.</t>
+          <t>Untersuchung.</t>
         </is>
       </c>
       <c r="E52" s="11" t="n"/>
       <c r="F52" s="11" t="n"/>
     </row>
-    <row r="53" ht="60" customHeight="1">
+    <row r="53" ht="30" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>reading.afterResult</t>
+          <t>misreading.readingsLabel</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+          <t>The same day, five readings</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Ein Befund des Instruments, das gerade alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Er kann auch falsch sein. Sie können es erst wissen, wenn Sie die Einstellungen des Instruments gesehen haben.</t>
+          <t>Derselbe Tag, fünf Befunde</t>
         </is>
       </c>
       <c r="E53" s="11" t="n"/>
@@ -1944,58 +1944,70 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” — the three instructions</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B54" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>misreading.readings[0].text</t>
         </is>
       </c>
       <c r="C54" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>A heaviness arrives before the day does.</t>
         </is>
       </c>
       <c r="D54" s="10" t="inlineStr">
         <is>
-          <t>Ist das die Situation? Oder ist das der Zustand?</t>
+          <t>Eine Schwere ist da, bevor der Tag da ist.</t>
         </is>
       </c>
       <c r="E54" s="11" t="n"/>
       <c r="F54" s="11" t="n"/>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
-        <is>
-          <t>THE STATE LINE — TIME, ATTENTION, SAFETY</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="n"/>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="9" t="inlineStr">
+        <is>
+          <t>“The first misreading” — page 10, the five readings</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>misreading.readings[1].text</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>A two-line email reads like a verdict.</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Eine zweizeilige E-Mail liest sich wie ein Urteil.</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="n"/>
+      <c r="F55" s="11" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>loops.eyebrow</t>
+          <t>misreading.readings[2].text</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>The state line</t>
+          <t>Five neutral words tighten a jaw.</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Die Zustandslinie</t>
+          <t>Fünf neutrale Wörter spannen einen Kiefer an.</t>
         </is>
       </c>
       <c r="E56" s="11" t="n"/>
@@ -2004,46 +2016,46 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>loops.title</t>
+          <t>misreading.readings[3].text</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>Three systems ran through Katrin’s morning.</t>
+          <t>An unanswered message starts charging rent.</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Drei Systeme liefen durch Katrins Morgen.</t>
+          <t>Eine unbeantwortete Nachricht fängt an, Miete zu verlangen.</t>
         </is>
       </c>
       <c r="E57" s="11" t="n"/>
       <c r="F57" s="11" t="n"/>
     </row>
-    <row r="58" ht="90" customHeight="1">
+    <row r="58" ht="30" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>loops.intro</t>
+          <t>misreading.readings[4].text</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Two letters and a full stop feel hostile.</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie viel Gewicht die Signale Ihres Körpers bekommen, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Sie sind ein Werkzeug zum Sortieren, eine Möglichkeit, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
+          <t>Zwei Buchstaben und ein Punkt fühlen sich feindselig an.</t>
         </is>
       </c>
       <c r="E58" s="11" t="n"/>
@@ -2052,22 +2064,22 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>loops.items[0].name</t>
+          <t>misreading.closing[0]</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>The body speaks first.</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Zeit</t>
+          <t>Der Körper spricht zuerst.</t>
         </is>
       </c>
       <c r="E59" s="11" t="n"/>
@@ -2076,118 +2088,106 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“The first misreading” — page 10, the five readings</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>loops.items[0].legend</t>
+          <t>misreading.closing[1]</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>Circadian phase, sleep debt, metabolic state</t>
+          <t>The mind explains second.</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Zirkadiane Phase, Schlafdefizit, Stoffwechselzustand</t>
+          <t>Der Kopf erklärt danach.</t>
         </is>
       </c>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
     </row>
-    <row r="61" ht="45" customHeight="1">
-      <c r="A61" s="9" t="inlineStr">
-        <is>
-          <t>The state line — Time, Attention, Safety</t>
-        </is>
-      </c>
-      <c r="B61" s="9" t="inlineStr">
-        <is>
-          <t>loops.items[0].body</t>
-        </is>
-      </c>
-      <c r="C61" s="10" t="inlineStr">
-        <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
-        </is>
-      </c>
-      <c r="D61" s="10" t="inlineStr">
-        <is>
-          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Wenn das Timing nicht stimmt, steigt die Grundempfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
-        </is>
-      </c>
-      <c r="E61" s="11" t="n"/>
-      <c r="F61" s="11" t="n"/>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="7" t="inlineStr">
+        <is>
+          <t>“YOU KNOW THE DAY” — PAGES 12 TO 13</t>
+        </is>
+      </c>
+      <c r="B61" s="8" t="n"/>
+      <c r="C61" s="8" t="n"/>
+      <c r="D61" s="8" t="n"/>
+      <c r="E61" s="8" t="n"/>
+      <c r="F61" s="8" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“You know the day” — pages 12 to 13</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>loops.items[1].name</t>
+          <t>knowTheDay.eyebrow</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>You know the day</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Aufmerksamkeit</t>
+          <t>Sie kennen diesen Tag</t>
         </is>
       </c>
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
     </row>
-    <row r="63" ht="30" customHeight="1">
+    <row r="63" ht="150" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“You know the day” — pages 12 to 13</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>loops.items[1].legend</t>
+          <t>knowTheDay.runs[0]</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Reward loops, checking, task switching</t>
+          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Belohnungsschleifen, Nachsehen, Aufgabenwechsel</t>
+          <t>Der Tag, den ich meine, ist von der anderen Art. Der Tag, an dem nichts schiefging und sich alles falsch anfühlte. Er fing an, bevor Sie merkten, dass er anfing. Irgendwo zwischen Wecker und Dusche, zwischen Dusche und Küche, zwischen Küche und dem ersten Schluck von dem, was auch immer Sie trinken, um der Mensch zu werden, den der Morgen verlangt. Etwas war schon da. Es fühlte sich eher an wie eine Textur. Eine Trägheit in den Gliedern, ein Widerstreben in der Brust, eine leise Schwere, die hinter Ihren Gedanken saß wie Regenwetter hinter Glas.</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
     </row>
-    <row r="64" ht="60" customHeight="1">
+    <row r="64" ht="75" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“You know the day” — pages 12 to 13</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>loops.items[1].body</t>
+          <t>knowTheDay.runs[1]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Das System, das Belohnung, Neues und den nächsten Reiz verfolgt. Wenn es gekapert ist, verengt sich der Fokus auf den billigsten Input, der gerade da ist, und die teure Arbeit fühlt sich schwer an.</t>
+          <t>Sie haben diesen Tag schon erlebt. Jeder hat diesen Tag schon erlebt. Sie haben ihn Dutzende Male erlebt und Sie werden ihn wieder erleben und jedes Mal wird sich die Geschichte anfühlen wie die Wahrheit und jedes Mal wird der Morgen danach die Geschichte auflösen.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
@@ -2196,106 +2196,106 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“You know the day” — pages 12 to 13</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>loops.items[2].name</t>
+          <t>knowTheDay.runs[2]</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Sicherheit</t>
+          <t>Der Körper sprach zuerst. Der Kopf erklärte danach, und diese Erklärung fühlte sich an wie das Ereignis.</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" ht="105" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>The state line — Time, Attention, Safety</t>
+          <t>“You know the day” — pages 12 to 13</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>loops.items[2].legend</t>
+          <t>knowTheDay.runs[3]</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Threat detection, first drafts, misreads</t>
+          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Bedrohung erkennen, erste Entwürfe, falsche Befunde</t>
+          <t>In diesem Buch geht es um diesen Fehler. Es geht um diesen Irrtum als etwas Tägliches, Beiläufiges, Unsichtbares, das zum Leben in einem Körper dazugehört, der ständig Signale erzeugt, die Ihr Kopf ständig liest oder falsch liest. Vor all dem, vor der Wissenschaft und dem Mechanismus und dem Grund, warum das Instrument gestern falsch kalibriert war, probieren Sie jetzt gleich etwas aus.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
     </row>
-    <row r="67" ht="75" customHeight="1">
-      <c r="A67" s="9" t="inlineStr">
-        <is>
-          <t>The state line — Time, Attention, Safety</t>
-        </is>
-      </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>loops.items[2].body</t>
-        </is>
-      </c>
-      <c r="C67" s="10" t="inlineStr">
-        <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
-        </is>
-      </c>
-      <c r="D67" s="10" t="inlineStr">
-        <is>
-          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale. Auf Dinge wie Bewertung durch andere, Ausschluss, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es liefert Deutungen, die sich wie Tatsachen anfühlen.</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="n"/>
-      <c r="F67" s="11" t="n"/>
-    </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>CASE EVIDENCE CARDS</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+    <row r="67" ht="22" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="n"/>
+      <c r="C67" s="8" t="n"/>
+      <c r="D67" s="8" t="n"/>
+      <c r="E67" s="8" t="n"/>
+      <c r="F67" s="8" t="n"/>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>“Try something right now” — the three instructions, page 13</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>reading.eyebrow</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>Try something right now</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Probieren Sie jetzt gleich etwas aus</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="11" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>cases.eyebrow</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Case evidence</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Beweismaterial</t>
+          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
@@ -2304,22 +2304,22 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>cases.title</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Sixteen cases. Three readings.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Sechzehn Fälle. Drei Befunde.</t>
+          <t>Spüren Sie Ihren Kiefer.</t>
         </is>
       </c>
       <c r="E70" s="11" t="n"/>
@@ -2328,22 +2328,22 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>cases.intro</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Every chapter opens on one of these pages.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel beginnt mit einer solchen Seite.</t>
+          <t>Spüren Sie Ihren Atem.</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
@@ -2352,22 +2352,22 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>Spüren Sie Ihre Schultern.</t>
         </is>
       </c>
       <c r="E72" s="11" t="n"/>
@@ -2376,46 +2376,46 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].quote</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>“Something is off.”</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>„Irgendetwas stimmt nicht.“</t>
+          <t>Was Sie gefunden haben, ist ein Befund.</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="30" customHeight="1">
+    <row r="74" ht="60" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>reading.afterResult</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Ein Befund, abgelesen an dem Instrument, das in diesem Moment alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Oder auch nicht. Das können Sie nicht wissen, bevor Sie die Einstellungen gesehen haben.</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
@@ -2424,70 +2424,58 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>reading.question</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>Is this the situation? Or is this the state?</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Zwei Minuten vor dem Wecker.</t>
+          <t>Ist das die Situation? Oder ist das der Zustand?</t>
         </is>
       </c>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>cases.items[0].verifiedLabel</t>
-        </is>
-      </c>
-      <c r="C76" s="10" t="inlineStr">
-        <is>
-          <t>Verified event</t>
-        </is>
-      </c>
-      <c r="D76" s="10" t="inlineStr">
-        <is>
-          <t>Bestätigtes Ereignis</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="n"/>
-      <c r="F76" s="11" t="n"/>
+    <row r="76" ht="22" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
+        <is>
+          <t>THE BOOK — THE PAGE 20 HEADING, THE AUTHOR’S ACCOUNT, WHO IT IS FOR</t>
+        </is>
+      </c>
+      <c r="B76" s="8" t="n"/>
+      <c r="C76" s="8" t="n"/>
+      <c r="D76" s="8" t="n"/>
+      <c r="E76" s="8" t="n"/>
+      <c r="F76" s="8" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>book.eyebrow</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Nichts ist geschehen.</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E77" s="11" t="n"/>
@@ -2496,22 +2484,22 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>book.heading</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>„ok.“</t>
+          <t>Derselbe Morgen. Derselbe Absatz. Dieselbe Katrin. Andere Einstellungen am Instrument.</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2520,46 +2508,46 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>book.headingSource</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Seite 20</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
     </row>
-    <row r="80" ht="30" customHeight="1">
+    <row r="80" ht="135" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>book.paragraphs[0]</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Zwei Buchstaben. Ein Punkt.</t>
+          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
@@ -2568,22 +2556,22 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>book.paragraphs[1]</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Bestätigter Tonfall</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
@@ -2592,118 +2580,106 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>book.readersEyebrow</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Who it is for</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Keiner.</t>
+          <t>Für wen es ist</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
     </row>
-    <row r="83" ht="30" customHeight="1">
+    <row r="83" ht="75" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>book.readersAnchor</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>“Oddly capable.”</t>
+          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>„Seltsam tatkräftig.“</t>
+          <t>Dieses Buch ersetzt keine professionelle Hilfe, und es behandelt komplexe Erkrankungen nicht als Fragen des Lebensstils. Es arbeitet in der Lücke zwischen gesund und klinisch, in dem Raum, in dem die meisten Menschen an den meisten Tagen leben.</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
     </row>
-    <row r="84" ht="30" customHeight="1">
+    <row r="84" ht="75" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].inputLabel</t>
+          <t>book.readers</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="inlineStr">
-        <is>
-          <t>cases.items[2].input</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>Quiet house. Open screen. Late hour.</t>
-        </is>
-      </c>
-      <c r="D85" s="10" t="inlineStr">
-        <is>
-          <t>Stilles Haus. Offener Bildschirm. Späte Stunde.</t>
-        </is>
-      </c>
-      <c r="E85" s="11" t="n"/>
-      <c r="F85" s="11" t="n"/>
+    <row r="85" ht="22" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
+          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="n"/>
+      <c r="C85" s="8" t="n"/>
+      <c r="D85" s="8" t="n"/>
+      <c r="E85" s="8" t="n"/>
+      <c r="F85" s="8" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>excerpt.eyebrow</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>Next reading</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Nächster Befund</t>
+          <t>Lesen</t>
         </is>
       </c>
       <c r="E86" s="11" t="n"/>
@@ -2712,22 +2688,22 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>excerpt.title</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>06:38.</t>
+          <t>Before the chapters</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>06:38.</t>
+          <t>Vor den Kapiteln</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
@@ -2736,22 +2712,22 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
+          <t>Der Pilot</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
@@ -2760,22 +2736,22 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>excerpt.runningHead</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
@@ -2784,22 +2760,22 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>excerpt.cta</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Sechs gewöhnliche Ereignisse. Ein ausgelaugter Tag.</t>
+          <t>Leseprobe lesen</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
@@ -2808,22 +2784,22 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Krise</t>
+          <t>Weiterlesen</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2832,22 +2808,22 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Keine.</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
@@ -2856,214 +2832,214 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>cases.items[4].quote</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>„Das ist Zustand, nicht Situation.“</t>
+          <t>Lesemodus</t>
         </is>
       </c>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
     </row>
-    <row r="94" ht="30" customHeight="1">
+    <row r="94" ht="105" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>cases.items[4].inputLabel</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
     </row>
-    <row r="95" ht="30" customHeight="1">
+    <row r="95" ht="210" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>cases.items[4].input</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Wenig Treibstoff. Erloschenes Licht. Ein Geräusch auf Kies.</t>
+          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
     </row>
-    <row r="96" ht="30" customHeight="1">
+    <row r="96" ht="150" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>cases.items[4].verifiedLabel</t>
+          <t>excerpt.paragraphs[2]</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Bedrohung</t>
+          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
     </row>
-    <row r="97" ht="30" customHeight="1">
+    <row r="97" ht="165" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>cases.items[4].verified</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Noch nicht sichtbar.</t>
+          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
     </row>
-    <row r="98" ht="30" customHeight="1">
+    <row r="98" ht="120" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>cases.items[5].quote</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>“She reads tomorrow’s.”</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>„Sie liest den von morgen.“</t>
+          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
     </row>
-    <row r="99" ht="30" customHeight="1">
+    <row r="99" ht="135" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>cases.items[5].inputLabel</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="30" customHeight="1">
+    <row r="100" ht="75" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>cases.items[5].input</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>Rested. Fed. Calm.</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Ausgeruht. Satt. Ruhig.</t>
+          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
         </is>
       </c>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
     </row>
-    <row r="101" ht="30" customHeight="1">
+    <row r="101" ht="240" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>cases.items[5].verifiedLabel</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Verified Monday</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Bestätigter Montag</t>
+          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
@@ -3072,58 +3048,70 @@
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>cases.items[5].verified</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Not yet happened.</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Noch nicht eingetreten.</t>
+          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
     </row>
-    <row r="103" ht="22" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
-        <is>
-          <t>THE EXTRACT — OPENING PAGES OF THE BOOK</t>
-        </is>
-      </c>
-      <c r="B103" s="8" t="n"/>
-      <c r="C103" s="8" t="n"/>
-      <c r="D103" s="8" t="n"/>
-      <c r="E103" s="8" t="n"/>
-      <c r="F103" s="8" t="n"/>
+    <row r="103" ht="135" customHeight="1">
+      <c r="A103" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B103" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.closing</t>
+        </is>
+      </c>
+      <c r="C103" s="10" t="inlineStr">
+        <is>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
+        </is>
+      </c>
+      <c r="D103" s="10" t="inlineStr">
+        <is>
+          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="n"/>
+      <c r="F103" s="11" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>excerpt.eyebrow</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Lesen</t>
+          <t>Seite 26</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3132,22 +3120,22 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Vor den Kapiteln</t>
+          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
@@ -3156,22 +3144,22 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot</t>
+          <t>Die Leseprobe in dieser Sprache folgt.</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
@@ -3180,22 +3168,22 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
@@ -3204,22 +3192,22 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe lesen</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
@@ -3228,262 +3216,250 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>excerpt.folios[2]</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Weiterlesen</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
     </row>
-    <row r="110" ht="30" customHeight="1">
-      <c r="A110" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book</t>
-        </is>
-      </c>
-      <c r="B110" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.back</t>
-        </is>
-      </c>
-      <c r="C110" s="10" t="inlineStr">
-        <is>
-          <t>Back to the book</t>
-        </is>
-      </c>
-      <c r="D110" s="10" t="inlineStr">
-        <is>
-          <t>Zurück zum Buch</t>
-        </is>
-      </c>
-      <c r="E110" s="11" t="n"/>
-      <c r="F110" s="11" t="n"/>
+    <row r="110" ht="22" customHeight="1">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>CASE EVIDENCE CARDS</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n"/>
+      <c r="C110" s="8" t="n"/>
+      <c r="D110" s="8" t="n"/>
+      <c r="E110" s="8" t="n"/>
+      <c r="F110" s="8" t="n"/>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>cases.eyebrow</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Lesemodus</t>
+          <t>Beweismaterial</t>
         </is>
       </c>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
     </row>
-    <row r="112" ht="105" customHeight="1">
+    <row r="112" ht="30" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>cases.pageLabel</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Am Abend des 16. Juli 1999 startete ein kleines einmotoriges Flugzeug in New Jersey. Es war auf dem Weg nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich sicher zu fühlen, und noch neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Stunden in der Luft. Die Ausbildung, die ihn berechtigt hätte, allein nach den Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
     </row>
-    <row r="113" ht="210" customHeight="1">
+    <row r="113" ht="30" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>cases.items[0].quote</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so langsam auslöscht, dass Sie den Horizont erst vermissen, wenn Sie ihn suchen und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Sie sehen Straßen, Gebäude, eine Geometrie, die Ihren Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der wie eine zweite Dunkelheit auf der Oberfläche liegt, gibt es nichts. Außerhalb des Cockpits wird die Welt in jede Richtung gleichmäßig grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie ruhiger Geradeausflug. Ein langsames Sinken fühlt sich an, als bliebe die Höhe gleich.</t>
+          <t>„Irgendetwas stimmt nicht.“</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
     </row>
-    <row r="114" ht="135" customHeight="1">
+    <row r="114" ht="30" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>cases.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, misst Änderungen der Bewegung. Wenn Sie in eine Kurve gehen, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn bemerkt die Drehung. Bleibt die Kurve aber fünfzehn oder zwanzig Sekunden lang gleich, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt und nicht die Lage, schließt daraus, dass die Kurve vorbei ist. Sie haben das Gefühl, waagerecht zu fliegen, tun es aber nicht.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
       <c r="F114" s="11" t="n"/>
     </row>
-    <row r="115" ht="165" customHeight="1">
+    <row r="115" ht="30" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>cases.items[0].input</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
+          <t>Zwei Minuten vor dem Wecker.</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
       <c r="F115" s="11" t="n"/>
     </row>
-    <row r="116" ht="135" customHeight="1">
+    <row r="116" ht="30" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>cases.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Die Kurve wurde enger. Die Nase sank. Die Geschwindigkeit stieg. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale – Piloten haben dafür einen Namen, mit der düsteren Genauigkeit eines Berufs, der jede Art benannt hat, auf die er Menschen verliert: Todesspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere kamen beim Aufprall ums Leben.</t>
+          <t>Bestätigtes Ereignis</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
       <c r="F116" s="11" t="n"/>
     </row>
-    <row r="117" ht="135" customHeight="1">
+    <row r="117" ht="30" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[5]</t>
+          <t>cases.items[0].verified</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung ergab kein technisches Versagen. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde Federal Aviation Administration hat für Piloten, die in diese Situation geraten, eine Anweisung, und sie ist einen Satz lang. Sie ist wörtlich gemeint und gilt für Ihr Leben so direkt wie für ein Cockpit:</t>
+          <t>Nichts ist passiert.</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
       <c r="F117" s="11" t="n"/>
     </row>
-    <row r="118" ht="75" customHeight="1">
+    <row r="118" ht="30" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>cases.items[1].quote</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle allein fliegen. Er war achtunddreißig Jahre alt.</t>
+          <t>„ok.“</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
     </row>
-    <row r="119" ht="240" customHeight="1">
+    <row r="119" ht="30" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>cases.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Sie steuern einen Körper, der Signale sendet, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die sich als Frage nach Ihrer Karriere ausgibt. Der Koffeinschub, der sich als Angst wegen einer E-Mail ausgibt. Der niedrige Blutzucker, der sich als Beweis dafür ausgibt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Gewissheit kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und dieses Instrument war schon falsch eingestellt, bevor die Situation überhaupt da war. Diese Instrumente gibt es wirklich. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. Sie liefern gerade jetzt Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3492,22 +3468,22 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>cases.items[1].input</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
+          <t>Zwei Buchstaben. Ein Punkt.</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3516,22 +3492,22 @@
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>cases.items[1].verifiedLabel</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>Verified tone</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
+          <t>Bestätigter Tonfall</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3540,22 +3516,22 @@
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>cases.items[1].verified</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Die Leseprobe in dieser Sprache folgt.</t>
+          <t>Keiner.</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3564,22 +3540,22 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>cases.items[2].quote</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3588,22 +3564,22 @@
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>cases.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
@@ -3612,58 +3588,70 @@
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>cases.items[2].input</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
         </is>
       </c>
       <c r="E125" s="11" t="n"/>
       <c r="F125" s="11" t="n"/>
     </row>
-    <row r="126" ht="22" customHeight="1">
-      <c r="A126" s="7" t="inlineStr">
-        <is>
-          <t>AUDIO PLAYER</t>
-        </is>
-      </c>
-      <c r="B126" s="8" t="n"/>
-      <c r="C126" s="8" t="n"/>
-      <c r="D126" s="8" t="n"/>
-      <c r="E126" s="8" t="n"/>
-      <c r="F126" s="8" t="n"/>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="9" t="inlineStr">
+        <is>
+          <t>Case evidence cards</t>
+        </is>
+      </c>
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>cases.items[2].verifiedLabel</t>
+        </is>
+      </c>
+      <c r="C126" s="10" t="inlineStr">
+        <is>
+          <t>Verified crisis</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
+        <is>
+          <t>Bestätigte Krise</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="n"/>
+      <c r="F126" s="11" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>listen.eyebrow</t>
+          <t>cases.items[2].verified</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Hören</t>
+          <t>Keine.</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3672,22 +3660,22 @@
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>cases.items[3].quote</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>“This is state, not situation.”</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Hörprobe</t>
+          <t>„Das ist Zustand, nicht Situation.“</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3696,22 +3684,22 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>cases.items[3].inputLabel</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Gelesen von der Autorin</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3720,22 +3708,22 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>cases.items[3].input</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Low fuel. Dead light. A sound on grit.</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Abspielen</t>
+          <t>Wenig Treibstoff. Kaputtes Licht. Ein Geräusch auf Splitt.</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3744,22 +3732,22 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>cases.items[3].verifiedLabel</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Verified threat</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Bestätigte Bedrohung</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3768,22 +3756,22 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>cases.items[3].verified</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Not yet visible.</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Wiedergabeposition</t>
+          <t>Noch nicht sichtbar.</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3792,22 +3780,22 @@
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>cases.closing</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Verstrichen</t>
+          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3816,82 +3804,82 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>Audio player</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>cases.closingSource</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Dauer</t>
+          <t>Seite 20</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Audio player</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>listen.unavailable</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>The recording will be added here.</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Die Aufnahme folgt an dieser Stelle.</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="n"/>
-      <c r="F135" s="11" t="n"/>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>ABOUT THE BOOK, EVIDENCE MARKERS, CHAPTER MAP</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="n"/>
-      <c r="C136" s="8" t="n"/>
-      <c r="D136" s="8" t="n"/>
-      <c r="E136" s="8" t="n"/>
-      <c r="F136" s="8" t="n"/>
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n"/>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>Audio player (hidden until a recording exists)</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>listen.eyebrow</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>Listen</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Hören</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="11" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>about.eyebrow</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Das Buch</t>
+          <t>Hörprobe</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3900,46 +3888,46 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>about.title</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>The body is a sensor before it is a narrator.</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Der Körper ist ein Sensor, bevor er ein Erzähler ist.</t>
+          <t>Gelesen von der Autorin</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
     </row>
-    <row r="139" ht="60" customHeight="1">
+    <row r="139" ht="30" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>about.quote</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading.</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>In diesem Buch geht es um diesen Fehler. Es geht um diesen Irrtum als tägliches, allgegenwärtiges, unsichtbares Merkmal des Lebens in einem Körper, der ständig Signale sendet, die Ihr Kopf ständig liest oder falsch liest.</t>
+          <t>Abspielen</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3948,46 +3936,46 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>about.quoteSource</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Page 12</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Seite 12</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
     </row>
-    <row r="141" ht="135" customHeight="1">
+    <row r="141" ht="30" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>about.paragraphs[0]</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Über sechzehn Tage hinweg geht Katrin durch gewöhnliche Situationen, in denen ihr erster Befund zu dem, was gerade geschieht, einem zweiten Blick nicht immer standhält. Jedes Kapitel folgt einem dieser Momente in die Psychologie dahinter: von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zur Frage, wie wir andere Menschen einschätzen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kommt.</t>
+          <t>Wiedergabeposition</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3996,22 +3984,22 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>about.paragraphs[1]</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie vertrauen.</t>
+          <t>Verstrichen</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
@@ -4020,22 +4008,22 @@
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>about.mapLine</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Dauer</t>
         </is>
       </c>
       <c r="E143" s="11" t="n"/>
@@ -4044,118 +4032,106 @@
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>about.evidenceEyebrow</t>
+          <t>listen.unavailable</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>The recording will be added here.</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Bevor wir beginnen</t>
+          <t>Die Aufnahme folgt hier.</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="135" customHeight="1">
-      <c r="A145" s="9" t="inlineStr">
-        <is>
-          <t>About the book, evidence markers, chapter map</t>
-        </is>
-      </c>
-      <c r="B145" s="9" t="inlineStr">
-        <is>
-          <t>about.evidenceIntro</t>
-        </is>
-      </c>
-      <c r="C145" s="10" t="inlineStr">
-        <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
-        </is>
-      </c>
-      <c r="D145" s="10" t="inlineStr">
-        <is>
-          <t>Dieses Buch stellt Behauptungen über das Gehirn und den Körper auf, und diese Behauptungen sind unterschiedlich gut belegt. Manche stützen sich auf jahrzehntelange Forschung, die immer wieder bestätigt wurde. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche führen gesichertes Wissen plausibel weiter, sind aber in der genauen Form, die dieses Buch beschreibt, nie direkt geprüft worden. Sie sollten wissen, was davon was ist.</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="n"/>
-      <c r="F145" s="11" t="n"/>
+    <row r="145" ht="22" customHeight="1">
+      <c r="A145" s="7" t="inlineStr">
+        <is>
+          <t>A MAP OF THE BOOK — THE THREE SYSTEMS, THE EVIDENCE MARKERS, THE SIXTEEN CHAPTERS, THE SCIENTIFIC HEARTBEAT</t>
+        </is>
+      </c>
+      <c r="B145" s="8" t="n"/>
+      <c r="C145" s="8" t="n"/>
+      <c r="D145" s="8" t="n"/>
+      <c r="E145" s="8" t="n"/>
+      <c r="F145" s="8" t="n"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>about.grades[0].label</t>
+          <t>map.eyebrow</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>A map of the book</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Eine Karte des Buches</t>
         </is>
       </c>
       <c r="E146" s="11" t="n"/>
       <c r="F146" s="11" t="n"/>
     </row>
-    <row r="147" ht="30" customHeight="1">
+    <row r="147" ht="90" customHeight="1">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>about.grades[0].shape</t>
+          <t>map.systemsIntro</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>Clean, strong heartbeat.</t>
+          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>Sauberer, kräftiger Herzschlag.</t>
+          <t>An Katrins Morgen waren drei Systeme am Werk. Zeit fing um 06:38 an und hörte nicht mehr auf. Aufmerksamkeit griff um 06:52 nach dem Handy. Sicherheit schrieb um 07:25, was die E-Mail bedeutete. Sie kann keines davon benennen. Das Einzige, was sie benennen kann, ist David, und David ist der kleinste Teil davon.</t>
         </is>
       </c>
       <c r="E147" s="11" t="n"/>
       <c r="F147" s="11" t="n"/>
     </row>
-    <row r="148" ht="30" customHeight="1">
+    <row r="148" ht="90" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>about.grades[0].meaning</t>
+          <t>map.sortingTool</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Replicated, robust evidence.</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Vielfach bestätigt, belastbar.</t>
+          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
@@ -4164,46 +4140,46 @@
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>about.grades[1].label</t>
+          <t>map.loops[0].name</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Zeit</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
       <c r="F149" s="11" t="n"/>
     </row>
-    <row r="150" ht="30" customHeight="1">
+    <row r="150" ht="45" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>about.grades[1].shape</t>
+          <t>map.loops[0].body</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Irregular, lower amplitude.</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Unregelmäßig, geringere Amplitude.</t>
+          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
@@ -4212,46 +4188,46 @@
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>about.grades[1].meaning</t>
+          <t>map.loops[1].name</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Suggestive but incomplete.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Ein Hinweis, aber unvollständig.</t>
+          <t>Aufmerksamkeit</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
       <c r="F151" s="11" t="n"/>
     </row>
-    <row r="152" ht="30" customHeight="1">
+    <row r="152" ht="60" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>about.grades[2].label</t>
+          <t>map.loops[1].body</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Niedrig</t>
+          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf das, was gerade da ist und am wenigsten Mühe macht, und die Arbeit, die einem viel abverlangt, fühlt sich schwer an.</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
@@ -4260,46 +4236,46 @@
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>about.grades[2].shape</t>
+          <t>map.loops[2].name</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Near-flatline, faint ripple.</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Nahezu Nulllinie, schwache Welle.</t>
+          <t>Sicherheit</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
       <c r="F153" s="11" t="n"/>
     </row>
-    <row r="154" ht="30" customHeight="1">
+    <row r="154" ht="75" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>about.grades[2].meaning</t>
+          <t>map.loops[2].body</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Plausible hypothesis only.</t>
+          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Nur eine plausible Vermutung.</t>
+          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Auf Dinge wie Bewertung durch andere, Ausgrenzung, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
@@ -4308,94 +4284,94 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>about.overreachEyebrow</t>
+          <t>map.evidenceEyebrow</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Where the chapters say more than their sources</t>
+          <t>Before we begin</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Wo die Kapitel mehr sagen als ihre Quellen</t>
+          <t>Bevor wir anfangen</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
       <c r="F155" s="11" t="n"/>
     </row>
-    <row r="156" ht="45" customHeight="1">
+    <row r="156" ht="120" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>about.overreach</t>
+          <t>map.evidenceIntro</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>The chapters are stories and have been left as written. These are the places a careful reader will catch, collected once here.</t>
+          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Die Kapitel sind Geschichten und stehen so, wie sie geschrieben sind. Dies sind die Stellen, die aufmerksamen Leserinnen und Lesern auffallen werden, hier einmal gesammelt.</t>
+          <t>Dieses Buch macht Aussagen über Gehirn und Körper, und diese Aussagen sind unterschiedlich gut belegt. Manche stützen sich auf Jahrzehnte replizierter Forschung. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche sind plausible Weiterführungen gesicherter Erkenntnisse, die in genau der Form, die dieses Buch beschreibt, noch nicht direkt geprüft wurden. Sie sollten wissen, was davon was ist.</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
     </row>
-    <row r="157" ht="30" customHeight="1">
+    <row r="157" ht="180" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>about.readersEyebrow</t>
+          <t>map.evidenceMarkers</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Für wen es ist</t>
+          <t>Im ganzen Buch tragen wissenschaftliche Aussagen eine Markierung, die zeigt, wie gut sie belegt sind. Stützt sich ein Ergebnis auf solide, replizierte Belege, sehen Sie am Rand eine Grafik, gekennzeichnet als hoch belegt, mit einem tiefroten Herzschlag. Sind die Belege zwar ein Hinweis, aber unvollständig, steht dort mittel belegt, mit einem orangefarbenen Herzschlag. Ist eine Aussage eine plausible Hypothese, die noch strengere Prüfungen braucht, ist sie als niedrig markiert, in verblasstem Grau. Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt. Es will eine plausible Geschichte nicht als gesicherte Wahrheit behandeln. Diese Markierungen sind eine Bremse dagegen.</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
     </row>
-    <row r="158" ht="75" customHeight="1">
+    <row r="158" ht="30" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>about.readers</t>
+          <t>map.grades[0].label</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann gemerkt haben, dass etwas anderes vor sich ging. Und für Leserinnen und Leser, die sich für die Psychologie dahinter interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und wieder korrigieren.</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4404,22 +4380,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>about.mapEyebrow</t>
+          <t>map.grades[1].label</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>A map of the book</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Eine Karte des Buches</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4428,22 +4404,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>about.mapTitle</t>
+          <t>map.grades[2].label</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4452,22 +4428,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>about.mapSubtitle</t>
+          <t>map.investigationTitle</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Same life. Different instrument settings.</t>
+          <t>The Investigation</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
+          <t>Die Untersuchung</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4476,22 +4452,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>about.pageColumn</t>
+          <t>map.mapLine</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4500,22 +4476,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[0].title</t>
+          <t>map.pageColumn</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4524,22 +4500,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[1].title</t>
+          <t>map.chapters[0].title</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Das Radar hatte recht</t>
+          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4548,22 +4524,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[2].title</t>
+          <t>map.chapters[1].title</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Warum sich bei Schlafmangel neutraler Input feindselig anfühlt</t>
+          <t>Das Radar hatte recht</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4572,22 +4548,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[3].title</t>
+          <t>map.chapters[2].title</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Die Erleichterung, die zum Juckreiz wird</t>
+          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4596,22 +4572,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[4].title</t>
+          <t>map.chapters[3].title</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Der vorhersehbare Reiz</t>
+          <t>Die Erleichterung, die zum Juckreiz wird</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4620,22 +4596,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[5].title</t>
+          <t>map.chapters[4].title</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Warum sich Abende dehnen und Morgen schrumpfen</t>
+          <t>Der vorhersehbare Auslöser</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4644,22 +4620,22 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[6].title</t>
+          <t>map.chapters[5].title</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Warum Ruhe nicht immer erholsam ist</t>
+          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
@@ -4668,22 +4644,22 @@
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[7].title</t>
+          <t>map.chapters[6].title</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Warum Sie das, was zählt, nicht beginnen können</t>
+          <t>Warum Ruhe nicht immer erholsam ist</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4692,22 +4668,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[8].title</t>
+          <t>map.chapters[7].title</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>The Open File</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Die offene Akte</t>
+          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4716,22 +4692,22 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[9].title</t>
+          <t>map.chapters[8].title</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Kommen zwei Nervensysteme in eine Küche</t>
+          <t>Die offene Akte</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
@@ -4740,22 +4716,22 @@
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[10].title</t>
+          <t>map.chapters[9].title</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>Der Streit, der der Dienstag war</t>
+          <t>Kommen zwei Nervensysteme in eine Küche</t>
         </is>
       </c>
       <c r="E173" s="11" t="n"/>
@@ -4764,22 +4740,22 @@
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[11].title</t>
+          <t>map.chapters[10].title</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Der Donnerstag, der der Mittwochabend war</t>
+          <t>Der Streit, der Dienstag war</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4788,22 +4764,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[12].title</t>
+          <t>map.chapters[11].title</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Das saubere Instrumentenbrett</t>
+          <t>Der Donnerstag, der Mittwochabend war</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4812,22 +4788,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[13].title</t>
+          <t>map.chapters[12].title</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Das eine Mal, als der Körper recht hatte</t>
+          <t>Das saubere Instrumentenbrett</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4836,22 +4812,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[14].title</t>
+          <t>map.chapters[13].title</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Es geht nicht um mich</t>
+          <t>Das eine Mal, als der Körper recht hatte</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4860,22 +4836,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>about.chapters[15].title</t>
+          <t>map.chapters[14].title</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Die Vorhersage</t>
+          <t>Es geht nicht um mich</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4884,58 +4860,70 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>About the book, evidence markers, chapter map</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>about.mapFooter</t>
+          <t>map.chapters[15].title</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
+          <t>Die Vorhersage</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
       <c r="F179" s="11" t="n"/>
     </row>
-    <row r="180" ht="22" customHeight="1">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t>ABOUT THE AUTHOR</t>
-        </is>
-      </c>
-      <c r="B180" s="8" t="n"/>
-      <c r="C180" s="8" t="n"/>
-      <c r="D180" s="8" t="n"/>
-      <c r="E180" s="8" t="n"/>
-      <c r="F180" s="8" t="n"/>
-    </row>
-    <row r="181" ht="30" customHeight="1">
+    <row r="180" ht="30" customHeight="1">
+      <c r="A180" s="9" t="inlineStr">
+        <is>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+        </is>
+      </c>
+      <c r="B180" s="9" t="inlineStr">
+        <is>
+          <t>map.mapFooter</t>
+        </is>
+      </c>
+      <c r="C180" s="10" t="inlineStr">
+        <is>
+          <t>The Scientific Heartbeat follows the chapters.</t>
+        </is>
+      </c>
+      <c r="D180" s="10" t="inlineStr">
+        <is>
+          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
+        </is>
+      </c>
+      <c r="E180" s="11" t="n"/>
+      <c r="F180" s="11" t="n"/>
+    </row>
+    <row r="181" ht="75" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>author.eyebrow</t>
+          <t>map.heartbeat[0]</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>The author</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Die Autorin</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
@@ -4944,22 +4932,22 @@
     <row r="182" ht="30" customHeight="1">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
         <is>
-          <t>author.title</t>
+          <t>map.heartbeat[1]</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E182" s="11" t="n"/>
@@ -4968,50 +4956,38 @@
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>map.heartbeatSource</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Page 226</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, fotografiert vor einem dunkelgrauen Hintergrund.</t>
+          <t>Seite 226</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
       <c r="F183" s="11" t="n"/>
     </row>
-    <row r="184" ht="30" customHeight="1">
-      <c r="A184" s="9" t="inlineStr">
-        <is>
-          <t>About the author</t>
-        </is>
-      </c>
-      <c r="B184" s="9" t="inlineStr">
-        <is>
-          <t>author.photoPlaceholder</t>
-        </is>
-      </c>
-      <c r="C184" s="10" t="inlineStr">
-        <is>
-          <t>Author photograph to follow</t>
-        </is>
-      </c>
-      <c r="D184" s="10" t="inlineStr">
-        <is>
-          <t>Foto der Autorin folgt</t>
-        </is>
-      </c>
-      <c r="E184" s="11" t="n"/>
-      <c r="F184" s="11" t="n"/>
+    <row r="184" ht="22" customHeight="1">
+      <c r="A184" s="7" t="inlineStr">
+        <is>
+          <t>ABOUT THE AUTHOR</t>
+        </is>
+      </c>
+      <c r="B184" s="8" t="n"/>
+      <c r="C184" s="8" t="n"/>
+      <c r="D184" s="8" t="n"/>
+      <c r="E184" s="8" t="n"/>
+      <c r="F184" s="8" t="n"/>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="9" t="inlineStr">
@@ -5021,17 +4997,17 @@
       </c>
       <c r="B185" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>author.eyebrow</t>
         </is>
       </c>
       <c r="C185" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>The author</t>
         </is>
       </c>
       <c r="D185" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin, sie lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Die Autorin</t>
         </is>
       </c>
       <c r="E185" s="11" t="n"/>
@@ -5045,17 +5021,17 @@
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>Website der Praxis</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
@@ -5069,17 +5045,17 @@
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
         </is>
       </c>
       <c r="E187" s="11" t="n"/>
@@ -5093,137 +5069,149 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>Foto der Autorin folgt</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
       <c r="F188" s="11" t="n"/>
     </row>
-    <row r="189" ht="22" customHeight="1">
-      <c r="A189" s="7" t="inlineStr">
-        <is>
-          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
-        </is>
-      </c>
-      <c r="B189" s="8" t="n"/>
-      <c r="C189" s="8" t="n"/>
-      <c r="D189" s="8" t="n"/>
-      <c r="E189" s="8" t="n"/>
-      <c r="F189" s="8" t="n"/>
+    <row r="189" ht="30" customHeight="1">
+      <c r="A189" s="9" t="inlineStr">
+        <is>
+          <t>About the author</t>
+        </is>
+      </c>
+      <c r="B189" s="9" t="inlineStr">
+        <is>
+          <t>author.bio</t>
+        </is>
+      </c>
+      <c r="C189" s="10" t="inlineStr">
+        <is>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+        </is>
+      </c>
+      <c r="D189" s="10" t="inlineStr">
+        <is>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+        </is>
+      </c>
+      <c r="E189" s="11" t="n"/>
+      <c r="F189" s="11" t="n"/>
     </row>
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>Companion tool (currently hidden)</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>companion.eyebrow</t>
+          <t>author.websiteLabel</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Alongside the book</t>
+          <t>Practice website</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Begleitend zum Buch</t>
+          <t>Website der Praxis</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
       <c r="F190" s="11" t="n"/>
     </row>
-    <row r="191" ht="22" customHeight="1">
-      <c r="A191" s="7" t="inlineStr">
-        <is>
-          <t>PRESS PAGE</t>
-        </is>
-      </c>
-      <c r="B191" s="8" t="n"/>
-      <c r="C191" s="8" t="n"/>
-      <c r="D191" s="8" t="n"/>
-      <c r="E191" s="8" t="n"/>
-      <c r="F191" s="8" t="n"/>
+    <row r="191" ht="30" customHeight="1">
+      <c r="A191" s="9" t="inlineStr">
+        <is>
+          <t>About the author</t>
+        </is>
+      </c>
+      <c r="B191" s="9" t="inlineStr">
+        <is>
+          <t>author.contactLabel</t>
+        </is>
+      </c>
+      <c r="C191" s="10" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="D191" s="10" t="inlineStr">
+        <is>
+          <t>Kontakt</t>
+        </is>
+      </c>
+      <c r="E191" s="11" t="n"/>
+      <c r="F191" s="11" t="n"/>
     </row>
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>press.eyebrow</t>
+          <t>author.pressLabel</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
       <c r="F192" s="11" t="n"/>
     </row>
-    <row r="193" ht="30" customHeight="1">
-      <c r="A193" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B193" s="9" t="inlineStr">
-        <is>
-          <t>press.title</t>
-        </is>
-      </c>
-      <c r="C193" s="10" t="inlineStr">
-        <is>
-          <t>Press materials</t>
-        </is>
-      </c>
-      <c r="D193" s="10" t="inlineStr">
-        <is>
-          <t>Pressematerial</t>
-        </is>
-      </c>
-      <c r="E193" s="11" t="n"/>
-      <c r="F193" s="11" t="n"/>
-    </row>
-    <row r="194" ht="45" customHeight="1">
+    <row r="193" ht="22" customHeight="1">
+      <c r="A193" s="7" t="inlineStr">
+        <is>
+          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
+        </is>
+      </c>
+      <c r="B193" s="8" t="n"/>
+      <c r="C193" s="8" t="n"/>
+      <c r="D193" s="8" t="n"/>
+      <c r="E193" s="8" t="n"/>
+      <c r="F193" s="8" t="n"/>
+    </row>
+    <row r="194" ht="30" customHeight="1">
       <c r="A194" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>The book’s last sentence, above the notify form</t>
         </is>
       </c>
       <c r="B194" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>Rezensionsexemplare, gedruckt und digital, gibt es auf Anfrage. Abdruckrechte für Auszüge sowie Interviews und Veranstaltungen nach Absprache.</t>
+          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
         </is>
       </c>
       <c r="E194" s="11" t="n"/>
@@ -5232,98 +5220,74 @@
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>The book’s last sentence, above the notify form</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>closing.source</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Seite 225</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
       <c r="F195" s="11" t="n"/>
     </row>
-    <row r="196" ht="30" customHeight="1">
-      <c r="A196" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B196" s="9" t="inlineStr">
-        <is>
-          <t>press.assetsHeading</t>
-        </is>
-      </c>
-      <c r="C196" s="10" t="inlineStr">
-        <is>
-          <t>Downloads</t>
-        </is>
-      </c>
-      <c r="D196" s="10" t="inlineStr">
-        <is>
-          <t>Downloads</t>
-        </is>
-      </c>
-      <c r="E196" s="11" t="n"/>
-      <c r="F196" s="11" t="n"/>
+    <row r="196" ht="22" customHeight="1">
+      <c r="A196" s="7" t="inlineStr">
+        <is>
+          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
+        </is>
+      </c>
+      <c r="B196" s="8" t="n"/>
+      <c r="C196" s="8" t="n"/>
+      <c r="D196" s="8" t="n"/>
+      <c r="E196" s="8" t="n"/>
+      <c r="F196" s="8" t="n"/>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Companion tool (currently hidden)</t>
         </is>
       </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>companion.eyebrow</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>Alongside the book</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>Cover-Vorderseite, hohe Auflösung</t>
+          <t>Begleitend zum Buch</t>
         </is>
       </c>
       <c r="E197" s="11" t="n"/>
       <c r="F197" s="11" t="n"/>
     </row>
-    <row r="198" ht="30" customHeight="1">
-      <c r="A198" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B198" s="9" t="inlineStr">
-        <is>
-          <t>press.assets[0].note</t>
-        </is>
-      </c>
-      <c r="C198" s="10" t="inlineStr">
-        <is>
-          <t>JPEG, 2400 px wide</t>
-        </is>
-      </c>
-      <c r="D198" s="10" t="inlineStr">
-        <is>
-          <t>JPEG, 2400 px breit</t>
-        </is>
-      </c>
-      <c r="E198" s="11" t="n"/>
-      <c r="F198" s="11" t="n"/>
+    <row r="198" ht="22" customHeight="1">
+      <c r="A198" s="7" t="inlineStr">
+        <is>
+          <t>PRESS PAGE</t>
+        </is>
+      </c>
+      <c r="B198" s="8" t="n"/>
+      <c r="C198" s="8" t="n"/>
+      <c r="D198" s="8" t="n"/>
+      <c r="E198" s="8" t="n"/>
+      <c r="F198" s="8" t="n"/>
     </row>
     <row r="199" ht="30" customHeight="1">
       <c r="A199" s="9" t="inlineStr">
@@ -5333,17 +5297,17 @@
       </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E199" s="11" t="n"/>
@@ -5357,17 +5321,17 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
@@ -5381,17 +5345,17 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Buchabbildung, freigestellt</t>
+          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
@@ -5405,17 +5369,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5429,17 +5393,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Web-Banner</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5453,17 +5417,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Cover, Vorderseite, hohe Auflösung</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5477,17 +5441,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.assets[0].note</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>JPEG, 2400 px wide</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>Social-Media-Bild, quadratisch</t>
+          <t>JPEG, 2400 px breit</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5501,17 +5465,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Foto der Autorin</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5525,17 +5489,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>Social-Media-Bild, Hochformat</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5549,17 +5513,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.assets[2].label</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Book render, transparent background</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Buchansicht, freigestellt</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5573,17 +5537,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>Social-Media-Bild, Querformat</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5597,17 +5561,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.assets[3].label</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Web banner</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Webbanner</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5621,17 +5585,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe, die ersten Seiten</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5645,17 +5609,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>PDF, vier Seiten</t>
+          <t>Bild für Social Media, quadratisch</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5669,17 +5633,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin auf Anfrage.</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5693,17 +5657,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>Biografie</t>
+          <t>Bild für Social Media, Hochformat</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5717,17 +5681,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>Kurz</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5741,17 +5705,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin, sie lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Bild für Social Media, Querformat</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5765,17 +5729,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>Lang</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5789,17 +5753,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>Publikation</t>
+          <t>Leseprobe, die ersten Seiten</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5813,17 +5777,17 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>Titel</t>
+          <t>PDF, vier Seiten</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
@@ -5837,17 +5801,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Foto der Autorin auf Anfrage.</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5861,17 +5825,17 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Untertitel</t>
+          <t>Biografie</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
@@ -5885,17 +5849,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Ein Feldführer für den Moment, bevor aus Deutung Wirklichkeit wird</t>
+          <t>Kurz</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5909,17 +5873,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.bios[0].text</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Autorin</t>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5933,17 +5897,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Lang</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5957,17 +5921,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Verlag</t>
+          <t>Bibliografische Angaben</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5981,17 +5945,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxemburg</t>
+          <t>Titel</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -6005,17 +5969,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>Erscheinungsjahr</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -6029,17 +5993,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Untertitel</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6053,17 +6017,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6077,17 +6041,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in (15,2 × 22,9 cm)</t>
+          <t>Autorin</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6101,17 +6065,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Umfang</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6125,17 +6089,17 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.facts[3].label</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>278 Seiten</t>
+          <t>Verlag</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
@@ -6149,17 +6113,17 @@
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Budisin Publishing, Luxemburg</t>
         </is>
       </c>
       <c r="E233" s="11" t="n"/>
@@ -6173,17 +6137,17 @@
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Erscheinungsjahr</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6197,17 +6161,17 @@
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.facts[4].value</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>Kategorie</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6221,17 +6185,17 @@
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Kognitive Psychologie</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6245,17 +6209,17 @@
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].label</t>
+          <t>press.facts[5].value</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Paperback, 6 × 9 in</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>Sprache</t>
+          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
@@ -6269,17 +6233,17 @@
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>Englisch. Französische und deutsche Ausgaben folgen.</t>
+          <t>Umfang</t>
         </is>
       </c>
       <c r="E238" s="11" t="n"/>
@@ -6293,17 +6257,17 @@
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>Pflichtexemplar</t>
+          <t>278 Seiten</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
@@ -6317,17 +6281,17 @@
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>Eine CIP-Aufnahme liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6341,23 +6305,23 @@
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>Über das Buch</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
       <c r="F241" s="11" t="n"/>
     </row>
-    <row r="242" ht="135" customHeight="1">
+    <row r="242" ht="30" customHeight="1">
       <c r="A242" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6365,17 +6329,17 @@
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.description[0]</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>Über sechzehn Tage hinweg geht Katrin durch gewöhnliche Situationen, in denen ihr erster Befund zu dem, was gerade geschieht, einem zweiten Blick nicht immer standhält. Jedes Kapitel folgt einem dieser Momente in die Psychologie dahinter: von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zur Frage, wie wir andere Menschen einschätzen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kommt.</t>
+          <t>Kategorie</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
@@ -6389,17 +6353,17 @@
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie vertrauen.</t>
+          <t>Psychologie / Kognitive Psychologie</t>
         </is>
       </c>
       <c r="E243" s="11" t="n"/>
@@ -6413,23 +6377,23 @@
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>Sixteen cases. Three readings. One question: state or situation?</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D244" s="10" t="inlineStr">
         <is>
-          <t>Sechzehn Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Sprache</t>
         </is>
       </c>
       <c r="E244" s="11" t="n"/>
       <c r="F244" s="11" t="n"/>
     </row>
-    <row r="245" ht="75" customHeight="1">
+    <row r="245" ht="30" customHeight="1">
       <c r="A245" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6437,17 +6401,17 @@
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>Every chapter carries a confidence marker showing how much evidence its claims rest on, and the reference section lists both the work each chapter is built on and the work that limits it, together with the places where the chapters say more than their sources.</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel trägt ein Zeichen dafür, wie gut seine Aussagen belegt sind, und im Literaturverzeichnis stehen die Arbeiten, auf denen ein Kapitel aufbaut, die Arbeiten, die ihm Grenzen setzen, und die Stellen, an denen die Kapitel mehr sagen als ihre Quellen.</t>
+          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
         </is>
       </c>
       <c r="E245" s="11" t="n"/>
@@ -6461,17 +6425,17 @@
       </c>
       <c r="B246" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>press.facts[10].label</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>Mitwirkende</t>
+          <t>Pflichtexemplar</t>
         </is>
       </c>
       <c r="E246" s="11" t="n"/>
@@ -6485,17 +6449,17 @@
       </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].label</t>
+          <t>press.facts[10].value</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
         <is>
-          <t>Cover design</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Covergestaltung</t>
+          <t>Ein CIP-Eintrag liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
         </is>
       </c>
       <c r="E247" s="11" t="n"/>
@@ -6509,23 +6473,23 @@
       </c>
       <c r="B248" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].value</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Über das Buch</t>
         </is>
       </c>
       <c r="E248" s="11" t="n"/>
       <c r="F248" s="11" t="n"/>
     </row>
-    <row r="249" ht="30" customHeight="1">
+    <row r="249" ht="135" customHeight="1">
       <c r="A249" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6533,17 +6497,17 @@
       </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].label</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
         <is>
-          <t>Book design and typesetting</t>
+          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>Buchgestaltung und Satz</t>
+          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
         </is>
       </c>
       <c r="E249" s="11" t="n"/>
@@ -6557,17 +6521,17 @@
       </c>
       <c r="B250" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].value</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D250" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E250" s="11" t="n"/>
@@ -6581,23 +6545,23 @@
       </c>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].label</t>
+          <t>press.description[2]</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
         <is>
-          <t>Published by</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>Erschienen bei</t>
+          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E251" s="11" t="n"/>
       <c r="F251" s="11" t="n"/>
     </row>
-    <row r="252" ht="30" customHeight="1">
+    <row r="252" ht="75" customHeight="1">
       <c r="A252" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6605,17 +6569,17 @@
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].value</t>
+          <t>press.description[3]</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E252" s="11" t="n"/>
@@ -6629,53 +6593,65 @@
       </c>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>press.back</t>
+          <t>press.description[4]</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>Zurück zum Buch</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E253" s="11" t="n"/>
       <c r="F253" s="11" t="n"/>
     </row>
-    <row r="254" ht="22" customHeight="1">
-      <c r="A254" s="7" t="inlineStr">
-        <is>
-          <t>FOOT OF EVERY PAGE</t>
-        </is>
-      </c>
-      <c r="B254" s="8" t="n"/>
-      <c r="C254" s="8" t="n"/>
-      <c r="D254" s="8" t="n"/>
-      <c r="E254" s="8" t="n"/>
-      <c r="F254" s="8" t="n"/>
+    <row r="254" ht="30" customHeight="1">
+      <c r="A254" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B254" s="9" t="inlineStr">
+        <is>
+          <t>press.creditsHeading</t>
+        </is>
+      </c>
+      <c r="C254" s="10" t="inlineStr">
+        <is>
+          <t>Credits</t>
+        </is>
+      </c>
+      <c r="D254" s="10" t="inlineStr">
+        <is>
+          <t>Mitwirkende</t>
+        </is>
+      </c>
+      <c r="E254" s="11" t="n"/>
+      <c r="F254" s="11" t="n"/>
     </row>
     <row r="255" ht="30" customHeight="1">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>footer.band</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
         <is>
-          <t>Before you believe the story.</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>Bevor Sie der Geschichte glauben.</t>
+          <t>Umschlaggestaltung</t>
         </is>
       </c>
       <c r="E255" s="11" t="n"/>
@@ -6684,22 +6660,22 @@
     <row r="256" ht="30" customHeight="1">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
         <is>
-          <t>footer.rights</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E256" s="11" t="n"/>
@@ -6708,22 +6684,22 @@
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>footer.pressLink</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>Buchgestaltung und Satz</t>
         </is>
       </c>
       <c r="E257" s="11" t="n"/>
@@ -6732,22 +6708,22 @@
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
         <is>
-          <t>footer.contactLink</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E258" s="11" t="n"/>
@@ -6756,106 +6732,106 @@
     <row r="259" ht="30" customHeight="1">
       <c r="A259" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B259" s="9" t="inlineStr">
         <is>
-          <t>footer.madeLine</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
         <is>
-          <t>Same life. Different instrument settings.</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
+          <t>Erschienen bei</t>
         </is>
       </c>
       <c r="E259" s="11" t="n"/>
       <c r="F259" s="11" t="n"/>
     </row>
-    <row r="260" ht="22" customHeight="1">
-      <c r="A260" s="7" t="inlineStr">
-        <is>
-          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
-        </is>
-      </c>
-      <c r="B260" s="8" t="n"/>
-      <c r="C260" s="8" t="n"/>
-      <c r="D260" s="8" t="n"/>
-      <c r="E260" s="8" t="n"/>
-      <c r="F260" s="8" t="n"/>
+    <row r="260" ht="30" customHeight="1">
+      <c r="A260" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B260" s="9" t="inlineStr">
+        <is>
+          <t>press.credits[2].value</t>
+        </is>
+      </c>
+      <c r="C260" s="10" t="inlineStr">
+        <is>
+          <t>Budisin Publishing</t>
+        </is>
+      </c>
+      <c r="D260" s="10" t="inlineStr">
+        <is>
+          <t>Budisin Publishing</t>
+        </is>
+      </c>
+      <c r="E260" s="11" t="n"/>
+      <c r="F260" s="11" t="n"/>
     </row>
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>a11y.mainLandmark</t>
+          <t>press.back</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
         <is>
-          <t>Main content</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>Hauptinhalt</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E261" s="11" t="n"/>
       <c r="F261" s="11" t="n"/>
     </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B262" s="9" t="inlineStr">
-        <is>
-          <t>a11y.coverFigure</t>
-        </is>
-      </c>
-      <c r="C262" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D262" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch</t>
-        </is>
-      </c>
-      <c r="E262" s="11" t="n"/>
-      <c r="F262" s="11" t="n"/>
+    <row r="262" ht="22" customHeight="1">
+      <c r="A262" s="7" t="inlineStr">
+        <is>
+          <t>FOOT OF EVERY PAGE</t>
+        </is>
+      </c>
+      <c r="B262" s="8" t="n"/>
+      <c r="C262" s="8" t="n"/>
+      <c r="D262" s="8" t="n"/>
+      <c r="E262" s="8" t="n"/>
+      <c r="F262" s="8" t="n"/>
     </row>
     <row r="263" ht="30" customHeight="1">
       <c r="A263" s="9" t="inlineStr">
         <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B263" s="9" t="inlineStr">
         <is>
-          <t>a11y.languageSwitcher</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C263" s="10" t="inlineStr">
         <is>
-          <t>Choose language</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D263" s="10" t="inlineStr">
         <is>
-          <t>Sprache wählen</t>
+          <t>Bevor Sie der Geschichte glauben.</t>
         </is>
       </c>
       <c r="E263" s="11" t="n"/>
@@ -6864,22 +6840,22 @@
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
         <is>
-          <t>a11y.languageComing</t>
+          <t>footer.method[0]</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
         <is>
-          <t>edition to follow</t>
+          <t>Read the dashboard.</t>
         </is>
       </c>
       <c r="D264" s="10" t="inlineStr">
         <is>
-          <t>Ausgabe folgt</t>
+          <t>Lesen Sie die Instrumente ab.</t>
         </is>
       </c>
       <c r="E264" s="11" t="n"/>
@@ -6888,22 +6864,22 @@
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>a11y.casesRegion</t>
+          <t>footer.method[1]</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
         <is>
-          <t>Case evidence pages from the book</t>
+          <t>Delay the story.</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>Seiten mit Beweismaterial aus dem Buch</t>
+          <t>Lassen Sie die Geschichte warten.</t>
         </is>
       </c>
       <c r="E265" s="11" t="n"/>
@@ -6912,29 +6888,329 @@
     <row r="266" ht="30" customHeight="1">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
         <is>
-          <t>a11y.bookOpening</t>
+          <t>footer.method[2]</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
         <is>
-          <t>The book, opening</t>
+          <t>Take the reading again.</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>Das Buch, das sich öffnet</t>
+          <t>Lesen Sie noch einmal ab.</t>
         </is>
       </c>
       <c r="E266" s="11" t="n"/>
       <c r="F266" s="11" t="n"/>
     </row>
+    <row r="267" ht="30" customHeight="1">
+      <c r="A267" s="9" t="inlineStr">
+        <is>
+          <t>Foot of every page</t>
+        </is>
+      </c>
+      <c r="B267" s="9" t="inlineStr">
+        <is>
+          <t>footer.rights</t>
+        </is>
+      </c>
+      <c r="C267" s="10" t="inlineStr">
+        <is>
+          <t>© 2026 Budisin Publishing</t>
+        </is>
+      </c>
+      <c r="D267" s="10" t="inlineStr">
+        <is>
+          <t>© 2026 Budisin Publishing</t>
+        </is>
+      </c>
+      <c r="E267" s="11" t="n"/>
+      <c r="F267" s="11" t="n"/>
+    </row>
+    <row r="268" ht="30" customHeight="1">
+      <c r="A268" s="9" t="inlineStr">
+        <is>
+          <t>Foot of every page</t>
+        </is>
+      </c>
+      <c r="B268" s="9" t="inlineStr">
+        <is>
+          <t>footer.pressLink</t>
+        </is>
+      </c>
+      <c r="C268" s="10" t="inlineStr">
+        <is>
+          <t>Press</t>
+        </is>
+      </c>
+      <c r="D268" s="10" t="inlineStr">
+        <is>
+          <t>Presse</t>
+        </is>
+      </c>
+      <c r="E268" s="11" t="n"/>
+      <c r="F268" s="11" t="n"/>
+    </row>
+    <row r="269" ht="30" customHeight="1">
+      <c r="A269" s="9" t="inlineStr">
+        <is>
+          <t>Foot of every page</t>
+        </is>
+      </c>
+      <c r="B269" s="9" t="inlineStr">
+        <is>
+          <t>footer.contactLink</t>
+        </is>
+      </c>
+      <c r="C269" s="10" t="inlineStr">
+        <is>
+          <t>Contact</t>
+        </is>
+      </c>
+      <c r="D269" s="10" t="inlineStr">
+        <is>
+          <t>Kontakt</t>
+        </is>
+      </c>
+      <c r="E269" s="11" t="n"/>
+      <c r="F269" s="11" t="n"/>
+    </row>
+    <row r="270" ht="30" customHeight="1">
+      <c r="A270" s="9" t="inlineStr">
+        <is>
+          <t>Foot of every page</t>
+        </is>
+      </c>
+      <c r="B270" s="9" t="inlineStr">
+        <is>
+          <t>footer.madeLine</t>
+        </is>
+      </c>
+      <c r="C270" s="10" t="inlineStr">
+        <is>
+          <t>Same life. Different instrument settings.</t>
+        </is>
+      </c>
+      <c r="D270" s="10" t="inlineStr">
+        <is>
+          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
+        </is>
+      </c>
+      <c r="E270" s="11" t="n"/>
+      <c r="F270" s="11" t="n"/>
+    </row>
+    <row r="271" ht="22" customHeight="1">
+      <c r="A271" s="7" t="inlineStr">
+        <is>
+          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
+        </is>
+      </c>
+      <c r="B271" s="8" t="n"/>
+      <c r="C271" s="8" t="n"/>
+      <c r="D271" s="8" t="n"/>
+      <c r="E271" s="8" t="n"/>
+      <c r="F271" s="8" t="n"/>
+    </row>
+    <row r="272" ht="30" customHeight="1">
+      <c r="A272" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B272" s="9" t="inlineStr">
+        <is>
+          <t>a11y.mainLandmark</t>
+        </is>
+      </c>
+      <c r="C272" s="10" t="inlineStr">
+        <is>
+          <t>Main content</t>
+        </is>
+      </c>
+      <c r="D272" s="10" t="inlineStr">
+        <is>
+          <t>Hauptinhalt</t>
+        </is>
+      </c>
+      <c r="E272" s="11" t="n"/>
+      <c r="F272" s="11" t="n"/>
+    </row>
+    <row r="273" ht="30" customHeight="1">
+      <c r="A273" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B273" s="9" t="inlineStr">
+        <is>
+          <t>a11y.coverFigure</t>
+        </is>
+      </c>
+      <c r="C273" s="10" t="inlineStr">
+        <is>
+          <t>The book</t>
+        </is>
+      </c>
+      <c r="D273" s="10" t="inlineStr">
+        <is>
+          <t>Das Buch</t>
+        </is>
+      </c>
+      <c r="E273" s="11" t="n"/>
+      <c r="F273" s="11" t="n"/>
+    </row>
+    <row r="274" ht="30" customHeight="1">
+      <c r="A274" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B274" s="9" t="inlineStr">
+        <is>
+          <t>a11y.languageSwitcher</t>
+        </is>
+      </c>
+      <c r="C274" s="10" t="inlineStr">
+        <is>
+          <t>Choose language</t>
+        </is>
+      </c>
+      <c r="D274" s="10" t="inlineStr">
+        <is>
+          <t>Sprache wählen</t>
+        </is>
+      </c>
+      <c r="E274" s="11" t="n"/>
+      <c r="F274" s="11" t="n"/>
+    </row>
+    <row r="275" ht="30" customHeight="1">
+      <c r="A275" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B275" s="9" t="inlineStr">
+        <is>
+          <t>a11y.languageComing</t>
+        </is>
+      </c>
+      <c r="C275" s="10" t="inlineStr">
+        <is>
+          <t>edition to follow</t>
+        </is>
+      </c>
+      <c r="D275" s="10" t="inlineStr">
+        <is>
+          <t>Ausgabe folgt</t>
+        </is>
+      </c>
+      <c r="E275" s="11" t="n"/>
+      <c r="F275" s="11" t="n"/>
+    </row>
+    <row r="276" ht="30" customHeight="1">
+      <c r="A276" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B276" s="9" t="inlineStr">
+        <is>
+          <t>a11y.casesRegion</t>
+        </is>
+      </c>
+      <c r="C276" s="10" t="inlineStr">
+        <is>
+          <t>Case evidence pages from the book</t>
+        </is>
+      </c>
+      <c r="D276" s="10" t="inlineStr">
+        <is>
+          <t>Seiten mit Beweismaterial aus dem Buch</t>
+        </is>
+      </c>
+      <c r="E276" s="11" t="n"/>
+      <c r="F276" s="11" t="n"/>
+    </row>
+    <row r="277" ht="30" customHeight="1">
+      <c r="A277" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B277" s="9" t="inlineStr">
+        <is>
+          <t>a11y.bookOpening</t>
+        </is>
+      </c>
+      <c r="C277" s="10" t="inlineStr">
+        <is>
+          <t>The book, opening</t>
+        </is>
+      </c>
+      <c r="D277" s="10" t="inlineStr">
+        <is>
+          <t>Das Buch beim Aufschlagen</t>
+        </is>
+      </c>
+      <c r="E277" s="11" t="n"/>
+      <c r="F277" s="11" t="n"/>
+    </row>
+    <row r="278" ht="30" customHeight="1">
+      <c r="A278" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B278" s="9" t="inlineStr">
+        <is>
+          <t>a11y.misreadingRegion</t>
+        </is>
+      </c>
+      <c r="C278" s="10" t="inlineStr">
+        <is>
+          <t>Page 10 of the book</t>
+        </is>
+      </c>
+      <c r="D278" s="10" t="inlineStr">
+        <is>
+          <t>Seite 10 des Buches</t>
+        </is>
+      </c>
+      <c r="E278" s="11" t="n"/>
+      <c r="F278" s="11" t="n"/>
+    </row>
+    <row r="279" ht="30" customHeight="1">
+      <c r="A279" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B279" s="9" t="inlineStr">
+        <is>
+          <t>a11y.mapRegion</t>
+        </is>
+      </c>
+      <c r="C279" s="10" t="inlineStr">
+        <is>
+          <t>A map of the book</t>
+        </is>
+      </c>
+      <c r="D279" s="10" t="inlineStr">
+        <is>
+          <t>Eine Karte des Buches</t>
+        </is>
+      </c>
+      <c r="E279" s="11" t="n"/>
+      <c r="F279" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F266"/>
+  <autoFilter ref="A1:F279"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/State-Not-Situation-German-review.xlsx
+++ b/review/State-Not-Situation-German-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="German review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$279</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$281</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F279"/>
+  <dimension ref="A1:F281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2112,7 +2112,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>“YOU KNOW THE DAY” — PAGES 12 TO 13</t>
+          <t>“YOU KNOW THE DAY” — PAGE 12, ABOVE THE THREE INSTRUCTIONS</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -2124,7 +2124,7 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
@@ -2145,137 +2145,137 @@
       <c r="E62" s="11" t="n"/>
       <c r="F62" s="11" t="n"/>
     </row>
-    <row r="63" ht="150" customHeight="1">
+    <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[0]</t>
+          <t>knowTheDay.moreLabel</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
+          <t>More from page 12</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Der Tag, den ich meine, ist von der anderen Art. Der Tag, an dem nichts schiefging und sich alles falsch anfühlte. Er fing an, bevor Sie merkten, dass er anfing. Irgendwo zwischen Wecker und Dusche, zwischen Dusche und Küche, zwischen Küche und dem ersten Schluck von dem, was auch immer Sie trinken, um der Mensch zu werden, den der Morgen verlangt. Etwas war schon da. Es fühlte sich eher an wie eine Textur. Eine Trägheit in den Gliedern, ein Widerstreben in der Brust, eine leise Schwere, die hinter Ihren Gedanken saß wie Regenwetter hinter Glas.</t>
+          <t>Mehr von Seite 12</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
     </row>
-    <row r="64" ht="75" customHeight="1">
+    <row r="64" ht="150" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[1]</t>
+          <t>knowTheDay.runs[0]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
+          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Sie haben diesen Tag schon erlebt. Jeder hat diesen Tag schon erlebt. Sie haben ihn Dutzende Male erlebt und Sie werden ihn wieder erleben und jedes Mal wird sich die Geschichte anfühlen wie die Wahrheit und jedes Mal wird der Morgen danach die Geschichte auflösen.</t>
+          <t>Der Tag, den ich meine, ist von der anderen Art. Der Tag, an dem nichts schiefging und sich alles falsch anfühlte. Er fing an, bevor Sie merkten, dass er anfing. Irgendwo zwischen Wecker und Dusche, zwischen Dusche und Küche, zwischen Küche und dem ersten Schluck von dem, was auch immer Sie trinken, um der Mensch zu werden, den der Morgen verlangt. Etwas war schon da. Es fühlte sich eher an wie eine Textur. Eine Trägheit in den Gliedern, ein Widerstreben in der Brust, eine leise Schwere, die hinter Ihren Gedanken saß wie Regenwetter hinter Glas.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
     </row>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="75" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[2]</t>
+          <t>knowTheDay.runs[1]</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
+          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Der Körper sprach zuerst. Der Kopf erklärte danach, und diese Erklärung fühlte sich an wie das Ereignis.</t>
+          <t>Sie haben diesen Tag schon erlebt. Jeder hat diesen Tag schon erlebt. Sie haben ihn Dutzende Male erlebt und Sie werden ihn wieder erleben und jedes Mal wird sich die Geschichte anfühlen wie die Wahrheit und jedes Mal wird der Morgen danach die Geschichte auflösen.</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
     </row>
-    <row r="66" ht="105" customHeight="1">
+    <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — pages 12 to 13</t>
+          <t>“You know the day” — page 12, above the three instructions</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[3]</t>
+          <t>knowTheDay.runs[2]</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
+          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>In diesem Buch geht es um diesen Fehler. Es geht um diesen Irrtum als etwas Tägliches, Beiläufiges, Unsichtbares, das zum Leben in einem Körper dazugehört, der ständig Signale erzeugt, die Ihr Kopf ständig liest oder falsch liest. Vor all dem, vor der Wissenschaft und dem Mechanismus und dem Grund, warum das Instrument gestern falsch kalibriert war, probieren Sie jetzt gleich etwas aus.</t>
+          <t>Der Körper sprach zuerst. Der Kopf erklärte danach, und diese Erklärung fühlte sich an wie das Ereignis.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
     </row>
-    <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="7" t="inlineStr">
+    <row r="67" ht="105" customHeight="1">
+      <c r="A67" s="9" t="inlineStr">
+        <is>
+          <t>“You know the day” — page 12, above the three instructions</t>
+        </is>
+      </c>
+      <c r="B67" s="9" t="inlineStr">
+        <is>
+          <t>knowTheDay.runs[3]</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>In diesem Buch geht es um diesen Fehler. Es geht um diesen Irrtum als etwas Tägliches, Beiläufiges, Unsichtbares, das zum Leben in einem Körper dazugehört, der ständig Signale erzeugt, die Ihr Kopf ständig liest oder falsch liest. Vor all dem, vor der Wissenschaft und dem Mechanismus und dem Grund, warum das Instrument gestern falsch kalibriert war, probieren Sie jetzt gleich etwas aus.</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="n"/>
+      <c r="F67" s="11" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
         <is>
           <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
         </is>
       </c>
-      <c r="B67" s="8" t="n"/>
-      <c r="C67" s="8" t="n"/>
-      <c r="D67" s="8" t="n"/>
-      <c r="E67" s="8" t="n"/>
-      <c r="F67" s="8" t="n"/>
-    </row>
-    <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="9" t="inlineStr">
-        <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
-        </is>
-      </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>reading.eyebrow</t>
-        </is>
-      </c>
-      <c r="C68" s="10" t="inlineStr">
-        <is>
-          <t>Try something right now</t>
-        </is>
-      </c>
-      <c r="D68" s="10" t="inlineStr">
-        <is>
-          <t>Probieren Sie jetzt gleich etwas aus</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="n"/>
-      <c r="F68" s="11" t="n"/>
+      <c r="B68" s="8" t="n"/>
+      <c r="C68" s="8" t="n"/>
+      <c r="D68" s="8" t="n"/>
+      <c r="E68" s="8" t="n"/>
+      <c r="F68" s="8" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
@@ -2285,17 +2285,17 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>reading.lead</t>
+          <t>reading.eyebrow</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
+          <t>Try something right now</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
+          <t>Probieren Sie jetzt gleich etwas aus</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B70" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C70" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D70" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihren Kiefer.</t>
+          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
         </is>
       </c>
       <c r="E70" s="11" t="n"/>
@@ -2333,17 +2333,17 @@
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihren Atem.</t>
+          <t>Spüren Sie Ihren Kiefer.</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
@@ -2357,17 +2357,17 @@
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihre Schultern.</t>
+          <t>Spüren Sie Ihren Atem.</t>
         </is>
       </c>
       <c r="E72" s="11" t="n"/>
@@ -2381,23 +2381,23 @@
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Was Sie gefunden haben, ist ein Befund.</t>
+          <t>Spüren Sie Ihre Schultern.</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="60" customHeight="1">
+    <row r="74" ht="30" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
           <t>“Try something right now” — the three instructions, page 13</t>
@@ -2405,23 +2405,23 @@
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>reading.afterResult</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Ein Befund, abgelesen an dem Instrument, das in diesem Moment alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Oder auch nicht. Das können Sie nicht wissen, bevor Sie die Einstellungen gesehen haben.</t>
+          <t>Was Sie gefunden haben, ist ein Befund.</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
     </row>
-    <row r="75" ht="30" customHeight="1">
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="9" t="inlineStr">
         <is>
           <t>“Try something right now” — the three instructions, page 13</t>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="B75" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>reading.afterResult</t>
         </is>
       </c>
       <c r="C75" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
         </is>
       </c>
       <c r="D75" s="10" t="inlineStr">
         <is>
-          <t>Ist das die Situation? Oder ist das der Zustand?</t>
+          <t>Ein Befund, abgelesen an dem Instrument, das in diesem Moment alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Oder auch nicht. Das können Sie nicht wissen, bevor Sie die Einstellungen gesehen haben.</t>
         </is>
       </c>
       <c r="E75" s="11" t="n"/>
       <c r="F75" s="11" t="n"/>
     </row>
-    <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
+    <row r="76" ht="30" customHeight="1">
+      <c r="A76" s="9" t="inlineStr">
+        <is>
+          <t>“Try something right now” — the three instructions, page 13</t>
+        </is>
+      </c>
+      <c r="B76" s="9" t="inlineStr">
+        <is>
+          <t>reading.question</t>
+        </is>
+      </c>
+      <c r="C76" s="10" t="inlineStr">
+        <is>
+          <t>Is this the situation? Or is this the state?</t>
+        </is>
+      </c>
+      <c r="D76" s="10" t="inlineStr">
+        <is>
+          <t>Ist das die Situation? Oder ist das der Zustand?</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="11" t="n"/>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="A77" s="7" t="inlineStr">
         <is>
           <t>THE BOOK — THE PAGE 20 HEADING, THE AUTHOR’S ACCOUNT, WHO IT IS FOR</t>
         </is>
       </c>
-      <c r="B76" s="8" t="n"/>
-      <c r="C76" s="8" t="n"/>
-      <c r="D76" s="8" t="n"/>
-      <c r="E76" s="8" t="n"/>
-      <c r="F76" s="8" t="n"/>
-    </row>
-    <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="9" t="inlineStr">
-        <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
-        </is>
-      </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>book.eyebrow</t>
-        </is>
-      </c>
-      <c r="C77" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D77" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="n"/>
-      <c r="F77" s="11" t="n"/>
+      <c r="B77" s="8" t="n"/>
+      <c r="C77" s="8" t="n"/>
+      <c r="D77" s="8" t="n"/>
+      <c r="E77" s="8" t="n"/>
+      <c r="F77" s="8" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
@@ -2489,17 +2489,17 @@
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>book.heading</t>
+          <t>book.eyebrow</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Derselbe Morgen. Derselbe Absatz. Dieselbe Katrin. Andere Einstellungen am Instrument.</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2513,23 +2513,23 @@
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>book.headingSource</t>
+          <t>book.heading</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Seite 20</t>
+          <t>Derselbe Morgen. Derselbe Absatz. Dieselbe Katrin. Andere Einstellungen am Instrument.</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
       <c r="F79" s="11" t="n"/>
     </row>
-    <row r="80" ht="135" customHeight="1">
+    <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2537,23 +2537,23 @@
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[0]</t>
+          <t>book.headingSource</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
+          <t>Seite 20</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
     </row>
-    <row r="81" ht="30" customHeight="1">
+    <row r="81" ht="135" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2561,17 +2561,17 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[1]</t>
+          <t>book.paragraphs[0]</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
+          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
@@ -2585,23 +2585,23 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>book.readersEyebrow</t>
+          <t>book.paragraphs[1]</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Für wen es ist</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
       <c r="F82" s="11" t="n"/>
     </row>
-    <row r="83" ht="75" customHeight="1">
+    <row r="83" ht="30" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
           <t>The book — the page 20 heading, the author’s account, who it is for</t>
@@ -2609,17 +2609,17 @@
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>book.readersAnchor</t>
+          <t>book.readersEyebrow</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
+          <t>Who it is for</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Dieses Buch ersetzt keine professionelle Hilfe, und es behandelt komplexe Erkrankungen nicht als Fragen des Lebensstils. Es arbeitet in der Lücke zwischen gesund und klinisch, in dem Raum, in dem die meisten Menschen an den meisten Tagen leben.</t>
+          <t>Für wen es ist</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
@@ -2633,57 +2633,57 @@
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>book.readers</t>
+          <t>book.readersAnchor</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
+          <t>Dieses Buch ersetzt keine professionelle Hilfe, und es behandelt komplexe Erkrankungen nicht als Fragen des Lebensstils. Es arbeitet in der Lücke zwischen gesund und klinisch, in dem Raum, in dem die meisten Menschen an den meisten Tagen leben.</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="22" customHeight="1">
-      <c r="A85" s="7" t="inlineStr">
+    <row r="85" ht="75" customHeight="1">
+      <c r="A85" s="9" t="inlineStr">
+        <is>
+          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+        </is>
+      </c>
+      <c r="B85" s="9" t="inlineStr">
+        <is>
+          <t>book.readers</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="n"/>
+      <c r="F85" s="11" t="n"/>
+    </row>
+    <row r="86" ht="22" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
         </is>
       </c>
-      <c r="B85" s="8" t="n"/>
-      <c r="C85" s="8" t="n"/>
-      <c r="D85" s="8" t="n"/>
-      <c r="E85" s="8" t="n"/>
-      <c r="F85" s="8" t="n"/>
-    </row>
-    <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
-        </is>
-      </c>
-      <c r="B86" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.eyebrow</t>
-        </is>
-      </c>
-      <c r="C86" s="10" t="inlineStr">
-        <is>
-          <t>Read</t>
-        </is>
-      </c>
-      <c r="D86" s="10" t="inlineStr">
-        <is>
-          <t>Lesen</t>
-        </is>
-      </c>
-      <c r="E86" s="11" t="n"/>
-      <c r="F86" s="11" t="n"/>
+      <c r="B86" s="8" t="n"/>
+      <c r="C86" s="8" t="n"/>
+      <c r="D86" s="8" t="n"/>
+      <c r="E86" s="8" t="n"/>
+      <c r="F86" s="8" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
@@ -2693,17 +2693,17 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>excerpt.eyebrow</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Vor den Kapiteln</t>
+          <t>Lesen</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
@@ -2717,17 +2717,17 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>excerpt.title</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>Before the chapters</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot</t>
+          <t>Vor den Kapiteln</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
@@ -2741,17 +2741,17 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Der Pilot</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>excerpt.runningHead</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe lesen</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
@@ -2789,17 +2789,17 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>excerpt.cta</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Weiterlesen</t>
+          <t>Leseprobe lesen</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2813,17 +2813,17 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>excerpt.back</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Zurück zum Buch</t>
+          <t>Weiterlesen</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
@@ -2837,23 +2837,23 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Lesemodus</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E93" s="11" t="n"/>
       <c r="F93" s="11" t="n"/>
     </row>
-    <row r="94" ht="105" customHeight="1">
+    <row r="94" ht="30" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2861,23 +2861,23 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
+          <t>Lesemodus</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
     </row>
-    <row r="95" ht="210" customHeight="1">
+    <row r="95" ht="105" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2885,23 +2885,23 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
+          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
     </row>
-    <row r="96" ht="150" customHeight="1">
+    <row r="96" ht="210" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2909,23 +2909,23 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
+          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
     </row>
-    <row r="97" ht="165" customHeight="1">
+    <row r="97" ht="150" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2933,23 +2933,23 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>excerpt.paragraphs[2]</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
+          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
     </row>
-    <row r="98" ht="120" customHeight="1">
+    <row r="98" ht="165" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2957,23 +2957,23 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
+          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
     </row>
-    <row r="99" ht="135" customHeight="1">
+    <row r="99" ht="120" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2981,23 +2981,23 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[5]</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
+          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="75" customHeight="1">
+    <row r="100" ht="135" customHeight="1">
       <c r="A100" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3005,23 +3005,23 @@
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C100" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D100" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
+          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
         </is>
       </c>
       <c r="E100" s="11" t="n"/>
       <c r="F100" s="11" t="n"/>
     </row>
-    <row r="101" ht="240" customHeight="1">
+    <row r="101" ht="75" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3029,23 +3029,23 @@
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
+          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
     </row>
-    <row r="102" ht="30" customHeight="1">
+    <row r="102" ht="240" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3053,23 +3053,23 @@
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
+          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
     </row>
-    <row r="103" ht="135" customHeight="1">
+    <row r="103" ht="30" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3077,23 +3077,23 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closing</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
+          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
         </is>
       </c>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
     </row>
-    <row r="104" ht="30" customHeight="1">
+    <row r="104" ht="135" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -3101,17 +3101,17 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closingSource</t>
+          <t>excerpt.closing</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Seite 26</t>
+          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3125,17 +3125,17 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
+          <t>Seite 26</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
@@ -3149,17 +3149,17 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Die Leseprobe in dieser Sprache folgt.</t>
+          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
@@ -3173,17 +3173,17 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Die Leseprobe in dieser Sprache folgt.</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
@@ -3197,17 +3197,17 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
@@ -3221,57 +3221,57 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
     </row>
-    <row r="110" ht="22" customHeight="1">
-      <c r="A110" s="7" t="inlineStr">
+    <row r="110" ht="30" customHeight="1">
+      <c r="A110" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.folios[2]</t>
+        </is>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D110" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="n"/>
+      <c r="F110" s="11" t="n"/>
+    </row>
+    <row r="111" ht="22" customHeight="1">
+      <c r="A111" s="7" t="inlineStr">
         <is>
           <t>CASE EVIDENCE CARDS</t>
         </is>
       </c>
-      <c r="B110" s="8" t="n"/>
-      <c r="C110" s="8" t="n"/>
-      <c r="D110" s="8" t="n"/>
-      <c r="E110" s="8" t="n"/>
-      <c r="F110" s="8" t="n"/>
-    </row>
-    <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B111" s="9" t="inlineStr">
-        <is>
-          <t>cases.eyebrow</t>
-        </is>
-      </c>
-      <c r="C111" s="10" t="inlineStr">
-        <is>
-          <t>Case evidence</t>
-        </is>
-      </c>
-      <c r="D111" s="10" t="inlineStr">
-        <is>
-          <t>Beweismaterial</t>
-        </is>
-      </c>
-      <c r="E111" s="11" t="n"/>
-      <c r="F111" s="11" t="n"/>
+      <c r="B111" s="8" t="n"/>
+      <c r="C111" s="8" t="n"/>
+      <c r="D111" s="8" t="n"/>
+      <c r="E111" s="8" t="n"/>
+      <c r="F111" s="8" t="n"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
@@ -3281,17 +3281,17 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>cases.eyebrow</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>Beweismaterial</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
@@ -3305,17 +3305,17 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].quote</t>
+          <t>cases.pageLabel</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>“Something is off.”</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>„Irgendetwas stimmt nicht.“</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
@@ -3329,17 +3329,17 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>cases.items[0].quote</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>„Irgendetwas stimmt nicht.“</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
@@ -3353,17 +3353,17 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>cases.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Zwei Minuten vor dem Wecker.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
@@ -3377,17 +3377,17 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verifiedLabel</t>
+          <t>cases.items[0].input</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Verified event</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Bestätigtes Ereignis</t>
+          <t>Zwei Minuten vor dem Wecker.</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
@@ -3401,17 +3401,17 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>cases.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Nichts ist passiert.</t>
+          <t>Bestätigtes Ereignis</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
@@ -3425,17 +3425,17 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>cases.items[0].verified</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>„ok.“</t>
+          <t>Nichts ist passiert.</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
@@ -3449,17 +3449,17 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>cases.items[1].quote</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>„ok.“</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3473,17 +3473,17 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>cases.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Zwei Buchstaben. Ein Punkt.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3497,17 +3497,17 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>cases.items[1].input</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Bestätigter Tonfall</t>
+          <t>Zwei Buchstaben. Ein Punkt.</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3521,17 +3521,17 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>cases.items[1].verifiedLabel</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Verified tone</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Keiner.</t>
+          <t>Bestätigter Tonfall</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>cases.items[1].verified</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
+          <t>Keiner.</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3569,17 +3569,17 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].inputLabel</t>
+          <t>cases.items[2].quote</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
@@ -3593,17 +3593,17 @@
       </c>
       <c r="B125" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].input</t>
+          <t>cases.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C125" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D125" s="10" t="inlineStr">
         <is>
-          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E125" s="11" t="n"/>
@@ -3617,17 +3617,17 @@
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>cases.items[2].input</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Krise</t>
+          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
         </is>
       </c>
       <c r="E126" s="11" t="n"/>
@@ -3641,17 +3641,17 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>cases.items[2].verifiedLabel</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Verified crisis</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Keine.</t>
+          <t>Bestätigte Krise</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>cases.items[2].verified</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>„Das ist Zustand, nicht Situation.“</t>
+          <t>Keine.</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3689,17 +3689,17 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>cases.items[3].quote</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>“This is state, not situation.”</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>„Das ist Zustand, nicht Situation.“</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3713,17 +3713,17 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>cases.items[3].inputLabel</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Wenig Treibstoff. Kaputtes Licht. Ein Geräusch auf Splitt.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3737,17 +3737,17 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>cases.items[3].input</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>Low fuel. Dead light. A sound on grit.</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Bedrohung</t>
+          <t>Wenig Treibstoff. Kaputtes Licht. Ein Geräusch auf Splitt.</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3761,17 +3761,17 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>cases.items[3].verifiedLabel</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>Verified threat</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Noch nicht sichtbar.</t>
+          <t>Bestätigte Bedrohung</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3785,17 +3785,17 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>cases.closing</t>
+          <t>cases.items[3].verified</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>It said I am failing; the data was I am tired.</t>
+          <t>Not yet visible.</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
+          <t>Noch nicht sichtbar.</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3809,57 +3809,57 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>cases.closingSource</t>
+          <t>cases.closing</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Seite 20</t>
+          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Case evidence cards</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>cases.closingSource</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>Page 20</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Seite 20</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
         </is>
       </c>
-      <c r="B135" s="8" t="n"/>
-      <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="8" t="n"/>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>Audio player (hidden until a recording exists)</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>listen.eyebrow</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>Listen</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Hören</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="n"/>
-      <c r="F136" s="11" t="n"/>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="8" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
@@ -3869,17 +3869,17 @@
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>listen.eyebrow</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Hörprobe</t>
+          <t>Hören</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3893,17 +3893,17 @@
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Gelesen von der Autorin</t>
+          <t>Hörprobe</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
@@ -3917,17 +3917,17 @@
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Abspielen</t>
+          <t>Gelesen von der Autorin</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3941,17 +3941,17 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Abspielen</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
@@ -3965,17 +3965,17 @@
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Wiedergabeposition</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3989,17 +3989,17 @@
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Verstrichen</t>
+          <t>Wiedergabeposition</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
@@ -4013,17 +4013,17 @@
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Dauer</t>
+          <t>Verstrichen</t>
         </is>
       </c>
       <c r="E143" s="11" t="n"/>
@@ -4037,77 +4037,77 @@
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>listen.unavailable</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>The recording will be added here.</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Die Aufnahme folgt hier.</t>
+          <t>Dauer</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="22" customHeight="1">
-      <c r="A145" s="7" t="inlineStr">
-        <is>
-          <t>A MAP OF THE BOOK — THE THREE SYSTEMS, THE EVIDENCE MARKERS, THE SIXTEEN CHAPTERS, THE SCIENTIFIC HEARTBEAT</t>
-        </is>
-      </c>
-      <c r="B145" s="8" t="n"/>
-      <c r="C145" s="8" t="n"/>
-      <c r="D145" s="8" t="n"/>
-      <c r="E145" s="8" t="n"/>
-      <c r="F145" s="8" t="n"/>
-    </row>
-    <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="9" t="inlineStr">
-        <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
-        </is>
-      </c>
-      <c r="B146" s="9" t="inlineStr">
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>Audio player (hidden until a recording exists)</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>listen.unavailable</t>
+        </is>
+      </c>
+      <c r="C145" s="10" t="inlineStr">
+        <is>
+          <t>The recording will be added here.</t>
+        </is>
+      </c>
+      <c r="D145" s="10" t="inlineStr">
+        <is>
+          <t>Die Aufnahme folgt hier.</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="11" t="n"/>
+    </row>
+    <row r="146" ht="22" customHeight="1">
+      <c r="A146" s="7" t="inlineStr">
+        <is>
+          <t>“BEFORE WE BEGIN” (PAGE 13 MARKERS) AND THE MAP — THE THREE SYSTEMS, THE SIXTEEN CHAPTERS, PAGE 226</t>
+        </is>
+      </c>
+      <c r="B146" s="8" t="n"/>
+      <c r="C146" s="8" t="n"/>
+      <c r="D146" s="8" t="n"/>
+      <c r="E146" s="8" t="n"/>
+      <c r="F146" s="8" t="n"/>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+        </is>
+      </c>
+      <c r="B147" s="9" t="inlineStr">
         <is>
           <t>map.eyebrow</t>
         </is>
       </c>
-      <c r="C146" s="10" t="inlineStr">
+      <c r="C147" s="10" t="inlineStr">
         <is>
           <t>A map of the book</t>
         </is>
       </c>
-      <c r="D146" s="10" t="inlineStr">
+      <c r="D147" s="10" t="inlineStr">
         <is>
           <t>Eine Karte des Buches</t>
-        </is>
-      </c>
-      <c r="E146" s="11" t="n"/>
-      <c r="F146" s="11" t="n"/>
-    </row>
-    <row r="147" ht="90" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>map.systemsIntro</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>An Katrins Morgen waren drei Systeme am Werk. Zeit fing um 06:38 an und hörte nicht mehr auf. Aufmerksamkeit griff um 06:52 nach dem Handy. Sicherheit schrieb um 07:25, was die E-Mail bedeutete. Sie kann keines davon benennen. Das Einzige, was sie benennen kann, ist David, und David ist der kleinste Teil davon.</t>
         </is>
       </c>
       <c r="E147" s="11" t="n"/>
@@ -4116,262 +4116,262 @@
     <row r="148" ht="90" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>map.sortingTool</t>
+          <t>map.systemsIntro</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
+          <t>An Katrins Morgen waren drei Systeme am Werk. Zeit fing um 06:38 an und hörte nicht mehr auf. Aufmerksamkeit griff um 06:52 nach dem Handy. Sicherheit schrieb um 07:25, was die E-Mail bedeutete. Sie kann keines davon benennen. Das Einzige, was sie benennen kann, ist David, und David ist der kleinste Teil davon.</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
     </row>
-    <row r="149" ht="30" customHeight="1">
+    <row r="149" ht="90" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].name</t>
+          <t>map.sortingTool</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Zeit</t>
+          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
       <c r="F149" s="11" t="n"/>
     </row>
-    <row r="150" ht="45" customHeight="1">
+    <row r="150" ht="30" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].body</t>
+          <t>map.loops[0].name</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
+          <t>Zeit</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
       <c r="F150" s="11" t="n"/>
     </row>
-    <row r="151" ht="30" customHeight="1">
+    <row r="151" ht="45" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].name</t>
+          <t>map.loops[0].body</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Aufmerksamkeit</t>
+          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
       <c r="F151" s="11" t="n"/>
     </row>
-    <row r="152" ht="60" customHeight="1">
+    <row r="152" ht="30" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].body</t>
+          <t>map.loops[1].name</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf das, was gerade da ist und am wenigsten Mühe macht, und die Arbeit, die einem viel abverlangt, fühlt sich schwer an.</t>
+          <t>Aufmerksamkeit</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
       <c r="F152" s="11" t="n"/>
     </row>
-    <row r="153" ht="30" customHeight="1">
+    <row r="153" ht="60" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].name</t>
+          <t>map.loops[1].body</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Sicherheit</t>
+          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf das, was gerade da ist und am wenigsten Mühe macht, und die Arbeit, die einem viel abverlangt, fühlt sich schwer an.</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
       <c r="F153" s="11" t="n"/>
     </row>
-    <row r="154" ht="75" customHeight="1">
+    <row r="154" ht="30" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].body</t>
+          <t>map.loops[2].name</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Auf Dinge wie Bewertung durch andere, Ausgrenzung, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
+          <t>Sicherheit</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
       <c r="F154" s="11" t="n"/>
     </row>
-    <row r="155" ht="30" customHeight="1">
+    <row r="155" ht="75" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceEyebrow</t>
+          <t>map.loops[2].body</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Bevor wir anfangen</t>
+          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Auf Dinge wie Bewertung durch andere, Ausgrenzung, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
       <c r="F155" s="11" t="n"/>
     </row>
-    <row r="156" ht="120" customHeight="1">
+    <row r="156" ht="30" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceIntro</t>
+          <t>map.evidenceEyebrow</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
+          <t>Before we begin</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Dieses Buch macht Aussagen über Gehirn und Körper, und diese Aussagen sind unterschiedlich gut belegt. Manche stützen sich auf Jahrzehnte replizierter Forschung. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche sind plausible Weiterführungen gesicherter Erkenntnisse, die in genau der Form, die dieses Buch beschreibt, noch nicht direkt geprüft wurden. Sie sollten wissen, was davon was ist.</t>
+          <t>Bevor wir anfangen</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
     </row>
-    <row r="157" ht="180" customHeight="1">
+    <row r="157" ht="120" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceMarkers</t>
+          <t>map.evidenceIntro</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Im ganzen Buch tragen wissenschaftliche Aussagen eine Markierung, die zeigt, wie gut sie belegt sind. Stützt sich ein Ergebnis auf solide, replizierte Belege, sehen Sie am Rand eine Grafik, gekennzeichnet als hoch belegt, mit einem tiefroten Herzschlag. Sind die Belege zwar ein Hinweis, aber unvollständig, steht dort mittel belegt, mit einem orangefarbenen Herzschlag. Ist eine Aussage eine plausible Hypothese, die noch strengere Prüfungen braucht, ist sie als niedrig markiert, in verblasstem Grau. Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt. Es will eine plausible Geschichte nicht als gesicherte Wahrheit behandeln. Diese Markierungen sind eine Bremse dagegen.</t>
+          <t>Dieses Buch macht Aussagen über Gehirn und Körper, und diese Aussagen sind unterschiedlich gut belegt. Manche stützen sich auf Jahrzehnte replizierter Forschung. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche sind plausible Weiterführungen gesicherter Erkenntnisse, die in genau der Form, die dieses Buch beschreibt, noch nicht direkt geprüft wurden. Sie sollten wissen, was davon was ist.</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
     </row>
-    <row r="158" ht="30" customHeight="1">
+    <row r="158" ht="180" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>map.grades[0].label</t>
+          <t>map.evidenceMarkers</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Im ganzen Buch tragen wissenschaftliche Aussagen eine Markierung, die zeigt, wie gut sie belegt sind. Stützt sich ein Ergebnis auf solide, replizierte Belege, sehen Sie am Rand eine Grafik, gekennzeichnet als hoch belegt, mit einem tiefroten Herzschlag. Sind die Belege zwar ein Hinweis, aber unvollständig, steht dort mittel belegt, mit einem orangefarbenen Herzschlag. Ist eine Aussage eine plausible Hypothese, die noch strengere Prüfungen braucht, ist sie als niedrig markiert, in verblasstem Grau. Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt. Es will eine plausible Geschichte nicht als gesicherte Wahrheit behandeln. Diese Markierungen sind eine Bremse dagegen.</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4380,22 +4380,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>map.grades[1].label</t>
+          <t>map.grades[0].label</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4404,22 +4404,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>map.grades[2].label</t>
+          <t>map.grades[1].label</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Niedrig</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4428,22 +4428,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>map.investigationTitle</t>
+          <t>map.grades[2].label</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4452,22 +4452,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>map.mapLine</t>
+          <t>map.investigationTitle</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>The Investigation</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Die Untersuchung</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4476,22 +4476,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>map.pageColumn</t>
+          <t>map.mapLine</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4500,22 +4500,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[0].title</t>
+          <t>map.pageColumn</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4524,22 +4524,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[1].title</t>
+          <t>map.chapters[0].title</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Das Radar hatte recht</t>
+          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4548,22 +4548,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[2].title</t>
+          <t>map.chapters[1].title</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
+          <t>Das Radar hatte recht</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4572,22 +4572,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[3].title</t>
+          <t>map.chapters[2].title</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Die Erleichterung, die zum Juckreiz wird</t>
+          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4596,22 +4596,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[4].title</t>
+          <t>map.chapters[3].title</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Der vorhersehbare Auslöser</t>
+          <t>Die Erleichterung, die zum Juckreiz wird</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4620,22 +4620,22 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[5].title</t>
+          <t>map.chapters[4].title</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
+          <t>Der vorhersehbare Auslöser</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
@@ -4644,22 +4644,22 @@
     <row r="170" ht="30" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[6].title</t>
+          <t>map.chapters[5].title</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Warum Ruhe nicht immer erholsam ist</t>
+          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4668,22 +4668,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[7].title</t>
+          <t>map.chapters[6].title</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
+          <t>Warum Ruhe nicht immer erholsam ist</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4692,22 +4692,22 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[8].title</t>
+          <t>map.chapters[7].title</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>The Open File</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Die offene Akte</t>
+          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
@@ -4716,22 +4716,22 @@
     <row r="173" ht="30" customHeight="1">
       <c r="A173" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B173" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[9].title</t>
+          <t>map.chapters[8].title</t>
         </is>
       </c>
       <c r="C173" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D173" s="10" t="inlineStr">
         <is>
-          <t>Kommen zwei Nervensysteme in eine Küche</t>
+          <t>Die offene Akte</t>
         </is>
       </c>
       <c r="E173" s="11" t="n"/>
@@ -4740,22 +4740,22 @@
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[10].title</t>
+          <t>map.chapters[9].title</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Der Streit, der Dienstag war</t>
+          <t>Kommen zwei Nervensysteme in eine Küche</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4764,22 +4764,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[11].title</t>
+          <t>map.chapters[10].title</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Der Donnerstag, der Mittwochabend war</t>
+          <t>Der Streit, der Dienstag war</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4788,22 +4788,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[12].title</t>
+          <t>map.chapters[11].title</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Das saubere Instrumentenbrett</t>
+          <t>Der Donnerstag, der Mittwochabend war</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4812,22 +4812,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[13].title</t>
+          <t>map.chapters[12].title</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Das eine Mal, als der Körper recht hatte</t>
+          <t>Das saubere Instrumentenbrett</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4836,22 +4836,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[14].title</t>
+          <t>map.chapters[13].title</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Es geht nicht um mich</t>
+          <t>Das eine Mal, als der Körper recht hatte</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4860,22 +4860,22 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[15].title</t>
+          <t>map.chapters[14].title</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Die Vorhersage</t>
+          <t>Es geht nicht um mich</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
@@ -4884,70 +4884,70 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>map.mapFooter</t>
+          <t>map.chapters[15].title</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
+          <t>Die Vorhersage</t>
         </is>
       </c>
       <c r="E180" s="11" t="n"/>
       <c r="F180" s="11" t="n"/>
     </row>
-    <row r="181" ht="75" customHeight="1">
+    <row r="181" ht="30" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[0]</t>
+          <t>map.mapFooter</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>The Scientific Heartbeat follows the chapters.</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
+          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
     </row>
-    <row r="182" ht="30" customHeight="1">
+    <row r="182" ht="75" customHeight="1">
       <c r="A182" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B182" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[1]</t>
+          <t>map.heartbeat[0]</t>
         </is>
       </c>
       <c r="C182" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D182" s="10" t="inlineStr">
         <is>
-          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E182" s="11" t="n"/>
@@ -4956,62 +4956,62 @@
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>A map of the book — the three systems, the evidence markers, the sixteen chapters, the Scientific Heartbeat</t>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeatSource</t>
+          <t>map.heartbeat[1]</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Seite 226</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
       <c r="F183" s="11" t="n"/>
     </row>
-    <row r="184" ht="22" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+    <row r="184" ht="30" customHeight="1">
+      <c r="A184" s="9" t="inlineStr">
+        <is>
+          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+        </is>
+      </c>
+      <c r="B184" s="9" t="inlineStr">
+        <is>
+          <t>map.heartbeatSource</t>
+        </is>
+      </c>
+      <c r="C184" s="10" t="inlineStr">
+        <is>
+          <t>Page 226</t>
+        </is>
+      </c>
+      <c r="D184" s="10" t="inlineStr">
+        <is>
+          <t>Seite 226</t>
+        </is>
+      </c>
+      <c r="E184" s="11" t="n"/>
+      <c r="F184" s="11" t="n"/>
+    </row>
+    <row r="185" ht="22" customHeight="1">
+      <c r="A185" s="7" t="inlineStr">
         <is>
           <t>ABOUT THE AUTHOR</t>
         </is>
       </c>
-      <c r="B184" s="8" t="n"/>
-      <c r="C184" s="8" t="n"/>
-      <c r="D184" s="8" t="n"/>
-      <c r="E184" s="8" t="n"/>
-      <c r="F184" s="8" t="n"/>
-    </row>
-    <row r="185" ht="30" customHeight="1">
-      <c r="A185" s="9" t="inlineStr">
-        <is>
-          <t>About the author</t>
-        </is>
-      </c>
-      <c r="B185" s="9" t="inlineStr">
-        <is>
-          <t>author.eyebrow</t>
-        </is>
-      </c>
-      <c r="C185" s="10" t="inlineStr">
-        <is>
-          <t>The author</t>
-        </is>
-      </c>
-      <c r="D185" s="10" t="inlineStr">
-        <is>
-          <t>Die Autorin</t>
-        </is>
-      </c>
-      <c r="E185" s="11" t="n"/>
-      <c r="F185" s="11" t="n"/>
+      <c r="B185" s="8" t="n"/>
+      <c r="C185" s="8" t="n"/>
+      <c r="D185" s="8" t="n"/>
+      <c r="E185" s="8" t="n"/>
+      <c r="F185" s="8" t="n"/>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
@@ -5021,17 +5021,17 @@
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>author.title</t>
+          <t>author.eyebrow</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>The author</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Die Autorin</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
@@ -5045,17 +5045,17 @@
       </c>
       <c r="B187" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C187" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D187" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E187" s="11" t="n"/>
@@ -5069,17 +5069,17 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>author.photoPlaceholder</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Author photograph to follow</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin folgt</t>
+          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
@@ -5093,17 +5093,17 @@
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Foto der Autorin folgt</t>
         </is>
       </c>
       <c r="E189" s="11" t="n"/>
@@ -5117,17 +5117,17 @@
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>author.bio</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Website der Praxis</t>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
@@ -5141,17 +5141,17 @@
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>author.websiteLabel</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Practice website</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Website der Praxis</t>
         </is>
       </c>
       <c r="E191" s="11" t="n"/>
@@ -5165,57 +5165,57 @@
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>author.contactLabel</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
       <c r="F192" s="11" t="n"/>
     </row>
-    <row r="193" ht="22" customHeight="1">
-      <c r="A193" s="7" t="inlineStr">
+    <row r="193" ht="30" customHeight="1">
+      <c r="A193" s="9" t="inlineStr">
+        <is>
+          <t>About the author</t>
+        </is>
+      </c>
+      <c r="B193" s="9" t="inlineStr">
+        <is>
+          <t>author.pressLabel</t>
+        </is>
+      </c>
+      <c r="C193" s="10" t="inlineStr">
+        <is>
+          <t>Press materials</t>
+        </is>
+      </c>
+      <c r="D193" s="10" t="inlineStr">
+        <is>
+          <t>Pressematerial</t>
+        </is>
+      </c>
+      <c r="E193" s="11" t="n"/>
+      <c r="F193" s="11" t="n"/>
+    </row>
+    <row r="194" ht="22" customHeight="1">
+      <c r="A194" s="7" t="inlineStr">
         <is>
           <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
         </is>
       </c>
-      <c r="B193" s="8" t="n"/>
-      <c r="C193" s="8" t="n"/>
-      <c r="D193" s="8" t="n"/>
-      <c r="E193" s="8" t="n"/>
-      <c r="F193" s="8" t="n"/>
-    </row>
-    <row r="194" ht="30" customHeight="1">
-      <c r="A194" s="9" t="inlineStr">
-        <is>
-          <t>The book’s last sentence, above the notify form</t>
-        </is>
-      </c>
-      <c r="B194" s="9" t="inlineStr">
-        <is>
-          <t>closing.question</t>
-        </is>
-      </c>
-      <c r="C194" s="10" t="inlineStr">
-        <is>
-          <t>Is this the situation? Or is this their state?</t>
-        </is>
-      </c>
-      <c r="D194" s="10" t="inlineStr">
-        <is>
-          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
-        </is>
-      </c>
-      <c r="E194" s="11" t="n"/>
-      <c r="F194" s="11" t="n"/>
+      <c r="B194" s="8" t="n"/>
+      <c r="C194" s="8" t="n"/>
+      <c r="D194" s="8" t="n"/>
+      <c r="E194" s="8" t="n"/>
+      <c r="F194" s="8" t="n"/>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
@@ -5225,93 +5225,93 @@
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>closing.source</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Seite 225</t>
+          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
       <c r="F195" s="11" t="n"/>
     </row>
-    <row r="196" ht="22" customHeight="1">
-      <c r="A196" s="7" t="inlineStr">
+    <row r="196" ht="30" customHeight="1">
+      <c r="A196" s="9" t="inlineStr">
+        <is>
+          <t>The book’s last sentence, above the notify form</t>
+        </is>
+      </c>
+      <c r="B196" s="9" t="inlineStr">
+        <is>
+          <t>closing.source</t>
+        </is>
+      </c>
+      <c r="C196" s="10" t="inlineStr">
+        <is>
+          <t>Page 225</t>
+        </is>
+      </c>
+      <c r="D196" s="10" t="inlineStr">
+        <is>
+          <t>Seite 225</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="n"/>
+      <c r="F196" s="11" t="n"/>
+    </row>
+    <row r="197" ht="22" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
         <is>
           <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
         </is>
       </c>
-      <c r="B196" s="8" t="n"/>
-      <c r="C196" s="8" t="n"/>
-      <c r="D196" s="8" t="n"/>
-      <c r="E196" s="8" t="n"/>
-      <c r="F196" s="8" t="n"/>
-    </row>
-    <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="9" t="inlineStr">
+      <c r="B197" s="8" t="n"/>
+      <c r="C197" s="8" t="n"/>
+      <c r="D197" s="8" t="n"/>
+      <c r="E197" s="8" t="n"/>
+      <c r="F197" s="8" t="n"/>
+    </row>
+    <row r="198" ht="30" customHeight="1">
+      <c r="A198" s="9" t="inlineStr">
         <is>
           <t>Companion tool (currently hidden)</t>
         </is>
       </c>
-      <c r="B197" s="9" t="inlineStr">
+      <c r="B198" s="9" t="inlineStr">
         <is>
           <t>companion.eyebrow</t>
         </is>
       </c>
-      <c r="C197" s="10" t="inlineStr">
+      <c r="C198" s="10" t="inlineStr">
         <is>
           <t>Alongside the book</t>
         </is>
       </c>
-      <c r="D197" s="10" t="inlineStr">
+      <c r="D198" s="10" t="inlineStr">
         <is>
           <t>Begleitend zum Buch</t>
         </is>
       </c>
-      <c r="E197" s="11" t="n"/>
-      <c r="F197" s="11" t="n"/>
-    </row>
-    <row r="198" ht="22" customHeight="1">
-      <c r="A198" s="7" t="inlineStr">
+      <c r="E198" s="11" t="n"/>
+      <c r="F198" s="11" t="n"/>
+    </row>
+    <row r="199" ht="22" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t>PRESS PAGE</t>
         </is>
       </c>
-      <c r="B198" s="8" t="n"/>
-      <c r="C198" s="8" t="n"/>
-      <c r="D198" s="8" t="n"/>
-      <c r="E198" s="8" t="n"/>
-      <c r="F198" s="8" t="n"/>
-    </row>
-    <row r="199" ht="30" customHeight="1">
-      <c r="A199" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B199" s="9" t="inlineStr">
-        <is>
-          <t>press.eyebrow</t>
-        </is>
-      </c>
-      <c r="C199" s="10" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="D199" s="10" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="E199" s="11" t="n"/>
-      <c r="F199" s="11" t="n"/>
+      <c r="B199" s="8" t="n"/>
+      <c r="C199" s="8" t="n"/>
+      <c r="D199" s="8" t="n"/>
+      <c r="E199" s="8" t="n"/>
+      <c r="F199" s="8" t="n"/>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="9" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.title</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
@@ -5345,17 +5345,17 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
@@ -5369,17 +5369,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5393,17 +5393,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.assetsHeading</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5417,17 +5417,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>Cover, Vorderseite, hohe Auflösung</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5441,17 +5441,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].note</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px wide</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px breit</t>
+          <t>Cover, Vorderseite, hohe Auflösung</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5465,17 +5465,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.assets[0].note</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>JPEG, 2400 px wide</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin</t>
+          <t>JPEG, 2400 px breit</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5489,17 +5489,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Foto der Autorin</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5513,17 +5513,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>Buchansicht, freigestellt</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5537,17 +5537,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.assets[2].label</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Book render, transparent background</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Buchansicht, freigestellt</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5561,17 +5561,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>Webbanner</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5585,17 +5585,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.assets[3].label</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Web banner</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Webbanner</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5609,17 +5609,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, quadratisch</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5633,17 +5633,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Bild für Social Media, quadratisch</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5657,17 +5657,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, Hochformat</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5681,17 +5681,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Bild für Social Media, Hochformat</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5705,17 +5705,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, Querformat</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5729,17 +5729,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Bild für Social Media, Querformat</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5753,17 +5753,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe, die ersten Seiten</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5777,17 +5777,17 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>PDF, vier Seiten</t>
+          <t>Leseprobe, die ersten Seiten</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
@@ -5801,17 +5801,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin auf Anfrage.</t>
+          <t>PDF, vier Seiten</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5825,17 +5825,17 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Biografie</t>
+          <t>Foto der Autorin auf Anfrage.</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
@@ -5849,17 +5849,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Kurz</t>
+          <t>Biografie</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5873,17 +5873,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Kurz</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5897,17 +5897,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.bios[0].text</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>Lang</t>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5921,17 +5921,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Bibliografische Angaben</t>
+          <t>Lang</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5945,17 +5945,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Titel</t>
+          <t>Bibliografische Angaben</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -5969,17 +5969,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Titel</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -5993,17 +5993,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>Untertitel</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6017,17 +6017,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
+          <t>Untertitel</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6041,17 +6041,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>Autorin</t>
+          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6065,17 +6065,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Autorin</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6089,17 +6089,17 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Verlag</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
@@ -6113,17 +6113,17 @@
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.facts[3].label</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxemburg</t>
+          <t>Verlag</t>
         </is>
       </c>
       <c r="E233" s="11" t="n"/>
@@ -6137,17 +6137,17 @@
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>Erscheinungsjahr</t>
+          <t>Budisin Publishing, Luxemburg</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6161,17 +6161,17 @@
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Erscheinungsjahr</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6185,17 +6185,17 @@
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.facts[4].value</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6209,17 +6209,17 @@
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
@@ -6233,17 +6233,17 @@
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.facts[5].value</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>Paperback, 6 × 9 in</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>Umfang</t>
+          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
         </is>
       </c>
       <c r="E238" s="11" t="n"/>
@@ -6257,17 +6257,17 @@
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>278 Seiten</t>
+          <t>Umfang</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
@@ -6281,17 +6281,17 @@
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>278 Seiten</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6305,17 +6305,17 @@
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
@@ -6329,17 +6329,17 @@
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>Kategorie</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
@@ -6353,17 +6353,17 @@
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Kognitive Psychologie</t>
+          <t>Kategorie</t>
         </is>
       </c>
       <c r="E243" s="11" t="n"/>
@@ -6377,17 +6377,17 @@
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].label</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D244" s="10" t="inlineStr">
         <is>
-          <t>Sprache</t>
+          <t>Psychologie / Kognitive Psychologie</t>
         </is>
       </c>
       <c r="E244" s="11" t="n"/>
@@ -6401,17 +6401,17 @@
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
+          <t>Sprache</t>
         </is>
       </c>
       <c r="E245" s="11" t="n"/>
@@ -6425,17 +6425,17 @@
       </c>
       <c r="B246" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>Pflichtexemplar</t>
+          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
         </is>
       </c>
       <c r="E246" s="11" t="n"/>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>press.facts[10].label</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Ein CIP-Eintrag liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
+          <t>Pflichtexemplar</t>
         </is>
       </c>
       <c r="E247" s="11" t="n"/>
@@ -6473,23 +6473,23 @@
       </c>
       <c r="B248" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>press.facts[10].value</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>Über das Buch</t>
+          <t>Ein CIP-Eintrag liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
         </is>
       </c>
       <c r="E248" s="11" t="n"/>
       <c r="F248" s="11" t="n"/>
     </row>
-    <row r="249" ht="135" customHeight="1">
+    <row r="249" ht="30" customHeight="1">
       <c r="A249" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6497,23 +6497,23 @@
       </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>press.description[0]</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
+          <t>Über das Buch</t>
         </is>
       </c>
       <c r="E249" s="11" t="n"/>
       <c r="F249" s="11" t="n"/>
     </row>
-    <row r="250" ht="30" customHeight="1">
+    <row r="250" ht="135" customHeight="1">
       <c r="A250" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6521,17 +6521,17 @@
       </c>
       <c r="B250" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C250" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
         </is>
       </c>
       <c r="D250" s="10" t="inlineStr">
         <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
+          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
         </is>
       </c>
       <c r="E250" s="11" t="n"/>
@@ -6545,23 +6545,23 @@
       </c>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E251" s="11" t="n"/>
       <c r="F251" s="11" t="n"/>
     </row>
-    <row r="252" ht="75" customHeight="1">
+    <row r="252" ht="30" customHeight="1">
       <c r="A252" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6569,23 +6569,23 @@
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>press.description[2]</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
+          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E252" s="11" t="n"/>
       <c r="F252" s="11" t="n"/>
     </row>
-    <row r="253" ht="30" customHeight="1">
+    <row r="253" ht="75" customHeight="1">
       <c r="A253" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6593,17 +6593,17 @@
       </c>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>press.description[4]</t>
+          <t>press.description[3]</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E253" s="11" t="n"/>
@@ -6617,17 +6617,17 @@
       </c>
       <c r="B254" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>press.description[4]</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>Mitwirkende</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E254" s="11" t="n"/>
@@ -6641,17 +6641,17 @@
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].label</t>
+          <t>press.creditsHeading</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
         <is>
-          <t>Cover design</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>Umschlaggestaltung</t>
+          <t>Mitwirkende</t>
         </is>
       </c>
       <c r="E255" s="11" t="n"/>
@@ -6665,17 +6665,17 @@
       </c>
       <c r="B256" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].value</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Umschlaggestaltung</t>
         </is>
       </c>
       <c r="E256" s="11" t="n"/>
@@ -6689,17 +6689,17 @@
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].label</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
         <is>
-          <t>Book design and typesetting</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>Buchgestaltung und Satz</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E257" s="11" t="n"/>
@@ -6713,17 +6713,17 @@
       </c>
       <c r="B258" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].value</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Buchgestaltung und Satz</t>
         </is>
       </c>
       <c r="E258" s="11" t="n"/>
@@ -6737,17 +6737,17 @@
       </c>
       <c r="B259" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].label</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C259" s="10" t="inlineStr">
         <is>
-          <t>Published by</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D259" s="10" t="inlineStr">
         <is>
-          <t>Erschienen bei</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E259" s="11" t="n"/>
@@ -6761,17 +6761,17 @@
       </c>
       <c r="B260" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].value</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Erschienen bei</t>
         </is>
       </c>
       <c r="E260" s="11" t="n"/>
@@ -6785,57 +6785,57 @@
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>press.back</t>
+          <t>press.credits[2].value</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>Zurück zum Buch</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="E261" s="11" t="n"/>
       <c r="F261" s="11" t="n"/>
     </row>
-    <row r="262" ht="22" customHeight="1">
-      <c r="A262" s="7" t="inlineStr">
+    <row r="262" ht="30" customHeight="1">
+      <c r="A262" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B262" s="9" t="inlineStr">
+        <is>
+          <t>press.back</t>
+        </is>
+      </c>
+      <c r="C262" s="10" t="inlineStr">
+        <is>
+          <t>Back to the book</t>
+        </is>
+      </c>
+      <c r="D262" s="10" t="inlineStr">
+        <is>
+          <t>Zurück zum Buch</t>
+        </is>
+      </c>
+      <c r="E262" s="11" t="n"/>
+      <c r="F262" s="11" t="n"/>
+    </row>
+    <row r="263" ht="22" customHeight="1">
+      <c r="A263" s="7" t="inlineStr">
         <is>
           <t>FOOT OF EVERY PAGE</t>
         </is>
       </c>
-      <c r="B262" s="8" t="n"/>
-      <c r="C262" s="8" t="n"/>
-      <c r="D262" s="8" t="n"/>
-      <c r="E262" s="8" t="n"/>
-      <c r="F262" s="8" t="n"/>
-    </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
-        <is>
-          <t>footer.band</t>
-        </is>
-      </c>
-      <c r="C263" s="10" t="inlineStr">
-        <is>
-          <t>Before you believe the story.</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <t>Bevor Sie der Geschichte glauben.</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="n"/>
-      <c r="F263" s="11" t="n"/>
+      <c r="B263" s="8" t="n"/>
+      <c r="C263" s="8" t="n"/>
+      <c r="D263" s="8" t="n"/>
+      <c r="E263" s="8" t="n"/>
+      <c r="F263" s="8" t="n"/>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="9" t="inlineStr">
@@ -6845,17 +6845,17 @@
       </c>
       <c r="B264" s="9" t="inlineStr">
         <is>
-          <t>footer.method[0]</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
         <is>
-          <t>Read the dashboard.</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D264" s="10" t="inlineStr">
         <is>
-          <t>Lesen Sie die Instrumente ab.</t>
+          <t>Bevor Sie der Geschichte glauben.</t>
         </is>
       </c>
       <c r="E264" s="11" t="n"/>
@@ -6869,17 +6869,17 @@
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>footer.method[1]</t>
+          <t>footer.method[0]</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
         <is>
-          <t>Delay the story.</t>
+          <t>Read the dashboard.</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>Lassen Sie die Geschichte warten.</t>
+          <t>Lesen Sie die Instrumente ab.</t>
         </is>
       </c>
       <c r="E265" s="11" t="n"/>
@@ -6893,17 +6893,17 @@
       </c>
       <c r="B266" s="9" t="inlineStr">
         <is>
-          <t>footer.method[2]</t>
+          <t>footer.method[1]</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
         <is>
-          <t>Take the reading again.</t>
+          <t>Delay the story.</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>Lesen Sie noch einmal ab.</t>
+          <t>Lassen Sie die Geschichte warten.</t>
         </is>
       </c>
       <c r="E266" s="11" t="n"/>
@@ -6917,17 +6917,17 @@
       </c>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>footer.rights</t>
+          <t>footer.method[2]</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Take the reading again.</t>
         </is>
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Lesen Sie noch einmal ab.</t>
         </is>
       </c>
       <c r="E267" s="11" t="n"/>
@@ -6941,17 +6941,17 @@
       </c>
       <c r="B268" s="9" t="inlineStr">
         <is>
-          <t>footer.pressLink</t>
+          <t>footer.rights</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="E268" s="11" t="n"/>
@@ -6965,17 +6965,17 @@
       </c>
       <c r="B269" s="9" t="inlineStr">
         <is>
-          <t>footer.contactLink</t>
+          <t>footer.pressLink</t>
         </is>
       </c>
       <c r="C269" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D269" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E269" s="11" t="n"/>
@@ -6989,57 +6989,57 @@
       </c>
       <c r="B270" s="9" t="inlineStr">
         <is>
-          <t>footer.madeLine</t>
+          <t>footer.contactLink</t>
         </is>
       </c>
       <c r="C270" s="10" t="inlineStr">
         <is>
-          <t>Same life. Different instrument settings.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D270" s="10" t="inlineStr">
         <is>
-          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E270" s="11" t="n"/>
       <c r="F270" s="11" t="n"/>
     </row>
-    <row r="271" ht="22" customHeight="1">
-      <c r="A271" s="7" t="inlineStr">
+    <row r="271" ht="30" customHeight="1">
+      <c r="A271" s="9" t="inlineStr">
+        <is>
+          <t>Foot of every page</t>
+        </is>
+      </c>
+      <c r="B271" s="9" t="inlineStr">
+        <is>
+          <t>footer.madeLine</t>
+        </is>
+      </c>
+      <c r="C271" s="10" t="inlineStr">
+        <is>
+          <t>Same life. Different instrument settings.</t>
+        </is>
+      </c>
+      <c r="D271" s="10" t="inlineStr">
+        <is>
+          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
+        </is>
+      </c>
+      <c r="E271" s="11" t="n"/>
+      <c r="F271" s="11" t="n"/>
+    </row>
+    <row r="272" ht="22" customHeight="1">
+      <c r="A272" s="7" t="inlineStr">
         <is>
           <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
         </is>
       </c>
-      <c r="B271" s="8" t="n"/>
-      <c r="C271" s="8" t="n"/>
-      <c r="D271" s="8" t="n"/>
-      <c r="E271" s="8" t="n"/>
-      <c r="F271" s="8" t="n"/>
-    </row>
-    <row r="272" ht="30" customHeight="1">
-      <c r="A272" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B272" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mainLandmark</t>
-        </is>
-      </c>
-      <c r="C272" s="10" t="inlineStr">
-        <is>
-          <t>Main content</t>
-        </is>
-      </c>
-      <c r="D272" s="10" t="inlineStr">
-        <is>
-          <t>Hauptinhalt</t>
-        </is>
-      </c>
-      <c r="E272" s="11" t="n"/>
-      <c r="F272" s="11" t="n"/>
+      <c r="B272" s="8" t="n"/>
+      <c r="C272" s="8" t="n"/>
+      <c r="D272" s="8" t="n"/>
+      <c r="E272" s="8" t="n"/>
+      <c r="F272" s="8" t="n"/>
     </row>
     <row r="273" ht="30" customHeight="1">
       <c r="A273" s="9" t="inlineStr">
@@ -7049,17 +7049,17 @@
       </c>
       <c r="B273" s="9" t="inlineStr">
         <is>
-          <t>a11y.coverFigure</t>
+          <t>a11y.mainLandmark</t>
         </is>
       </c>
       <c r="C273" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>Main content</t>
         </is>
       </c>
       <c r="D273" s="10" t="inlineStr">
         <is>
-          <t>Das Buch</t>
+          <t>Hauptinhalt</t>
         </is>
       </c>
       <c r="E273" s="11" t="n"/>
@@ -7073,17 +7073,17 @@
       </c>
       <c r="B274" s="9" t="inlineStr">
         <is>
-          <t>a11y.languageSwitcher</t>
+          <t>a11y.coverFigure</t>
         </is>
       </c>
       <c r="C274" s="10" t="inlineStr">
         <is>
-          <t>Choose language</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D274" s="10" t="inlineStr">
         <is>
-          <t>Sprache wählen</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E274" s="11" t="n"/>
@@ -7097,17 +7097,17 @@
       </c>
       <c r="B275" s="9" t="inlineStr">
         <is>
-          <t>a11y.languageComing</t>
+          <t>a11y.languageSwitcher</t>
         </is>
       </c>
       <c r="C275" s="10" t="inlineStr">
         <is>
-          <t>edition to follow</t>
+          <t>Choose language</t>
         </is>
       </c>
       <c r="D275" s="10" t="inlineStr">
         <is>
-          <t>Ausgabe folgt</t>
+          <t>Sprache wählen</t>
         </is>
       </c>
       <c r="E275" s="11" t="n"/>
@@ -7121,17 +7121,17 @@
       </c>
       <c r="B276" s="9" t="inlineStr">
         <is>
-          <t>a11y.casesRegion</t>
+          <t>a11y.languageComing</t>
         </is>
       </c>
       <c r="C276" s="10" t="inlineStr">
         <is>
-          <t>Case evidence pages from the book</t>
+          <t>edition to follow</t>
         </is>
       </c>
       <c r="D276" s="10" t="inlineStr">
         <is>
-          <t>Seiten mit Beweismaterial aus dem Buch</t>
+          <t>Ausgabe folgt</t>
         </is>
       </c>
       <c r="E276" s="11" t="n"/>
@@ -7145,17 +7145,17 @@
       </c>
       <c r="B277" s="9" t="inlineStr">
         <is>
-          <t>a11y.bookOpening</t>
+          <t>a11y.casesRegion</t>
         </is>
       </c>
       <c r="C277" s="10" t="inlineStr">
         <is>
-          <t>The book, opening</t>
+          <t>Case evidence pages from the book</t>
         </is>
       </c>
       <c r="D277" s="10" t="inlineStr">
         <is>
-          <t>Das Buch beim Aufschlagen</t>
+          <t>Seiten mit Beweismaterial aus dem Buch</t>
         </is>
       </c>
       <c r="E277" s="11" t="n"/>
@@ -7169,17 +7169,17 @@
       </c>
       <c r="B278" s="9" t="inlineStr">
         <is>
-          <t>a11y.misreadingRegion</t>
+          <t>a11y.bookOpening</t>
         </is>
       </c>
       <c r="C278" s="10" t="inlineStr">
         <is>
-          <t>Page 10 of the book</t>
+          <t>The book, opening</t>
         </is>
       </c>
       <c r="D278" s="10" t="inlineStr">
         <is>
-          <t>Seite 10 des Buches</t>
+          <t>Das Buch beim Aufschlagen</t>
         </is>
       </c>
       <c r="E278" s="11" t="n"/>
@@ -7193,24 +7193,72 @@
       </c>
       <c r="B279" s="9" t="inlineStr">
         <is>
-          <t>a11y.mapRegion</t>
+          <t>a11y.misreadingRegion</t>
         </is>
       </c>
       <c r="C279" s="10" t="inlineStr">
         <is>
-          <t>A map of the book</t>
+          <t>Page 10 of the book</t>
         </is>
       </c>
       <c r="D279" s="10" t="inlineStr">
         <is>
-          <t>Eine Karte des Buches</t>
+          <t>Seite 10 des Buches</t>
         </is>
       </c>
       <c r="E279" s="11" t="n"/>
       <c r="F279" s="11" t="n"/>
     </row>
+    <row r="280" ht="30" customHeight="1">
+      <c r="A280" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B280" s="9" t="inlineStr">
+        <is>
+          <t>a11y.mapRegion</t>
+        </is>
+      </c>
+      <c r="C280" s="10" t="inlineStr">
+        <is>
+          <t>A map of the book</t>
+        </is>
+      </c>
+      <c r="D280" s="10" t="inlineStr">
+        <is>
+          <t>Eine Karte des Buches</t>
+        </is>
+      </c>
+      <c r="E280" s="11" t="n"/>
+      <c r="F280" s="11" t="n"/>
+    </row>
+    <row r="281" ht="30" customHeight="1">
+      <c r="A281" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B281" s="9" t="inlineStr">
+        <is>
+          <t>a11y.evidenceRegion</t>
+        </is>
+      </c>
+      <c r="C281" s="10" t="inlineStr">
+        <is>
+          <t>Confidence markers, page 13</t>
+        </is>
+      </c>
+      <c r="D281" s="10" t="inlineStr">
+        <is>
+          <t>Markierungen zu den Belegen, Seite 13</t>
+        </is>
+      </c>
+      <c r="E281" s="11" t="n"/>
+      <c r="F281" s="11" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F279"/>
+  <autoFilter ref="A1:F281"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/State-Not-Situation-German-review.xlsx
+++ b/review/State-Not-Situation-German-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="German review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$281</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$268</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F281"/>
+  <dimension ref="A1:F268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2112,7 +2112,7 @@
     <row r="61" ht="22" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>“YOU KNOW THE DAY” — PAGE 12, ABOVE THE THREE INSTRUCTIONS</t>
+          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
         </is>
       </c>
       <c r="B61" s="8" t="n"/>
@@ -2124,22 +2124,22 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B62" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.eyebrow</t>
+          <t>reading.eyebrow</t>
         </is>
       </c>
       <c r="C62" s="10" t="inlineStr">
         <is>
-          <t>You know the day</t>
+          <t>Try something right now</t>
         </is>
       </c>
       <c r="D62" s="10" t="inlineStr">
         <is>
-          <t>Sie kennen diesen Tag</t>
+          <t>Probieren Sie jetzt gleich etwas aus</t>
         </is>
       </c>
       <c r="E62" s="11" t="n"/>
@@ -2148,70 +2148,70 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.moreLabel</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>More from page 12</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Mehr von Seite 12</t>
+          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
       <c r="F63" s="11" t="n"/>
     </row>
-    <row r="64" ht="150" customHeight="1">
+    <row r="64" ht="30" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[0]</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>The day I mean is the other kind. The day where nothing went wrong and everything felt off. It started before you noticed it starting. Somewhere between the alarm and the shower, between the shower and the kitchen, between the kitchen and the first sip of whatever you drink to become the person the morning requires. Something was already there. It felt more like texture. A drag in the limbs, a reluctance in the chest, a faint heaviness that sat behind your thoughts like rainy weather behind glass.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Der Tag, den ich meine, ist von der anderen Art. Der Tag, an dem nichts schiefging und sich alles falsch anfühlte. Er fing an, bevor Sie merkten, dass er anfing. Irgendwo zwischen Wecker und Dusche, zwischen Dusche und Küche, zwischen Küche und dem ersten Schluck von dem, was auch immer Sie trinken, um der Mensch zu werden, den der Morgen verlangt. Etwas war schon da. Es fühlte sich eher an wie eine Textur. Eine Trägheit in den Gliedern, ein Widerstreben in der Brust, eine leise Schwere, die hinter Ihren Gedanken saß wie Regenwetter hinter Glas.</t>
+          <t>Spüren Sie Ihren Kiefer.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
       <c r="F64" s="11" t="n"/>
     </row>
-    <row r="65" ht="75" customHeight="1">
+    <row r="65" ht="30" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[1]</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>You have had this day. Everyone has had this day. You have had it dozens of times and you will have it again and each time the story will feel like the truth and each time the morning after will make the story dissolve.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Sie haben diesen Tag schon erlebt. Jeder hat diesen Tag schon erlebt. Sie haben ihn Dutzende Male erlebt und Sie werden ihn wieder erleben und jedes Mal wird sich die Geschichte anfühlen wie die Wahrheit und jedes Mal wird der Morgen danach die Geschichte auflösen.</t>
+          <t>Spüren Sie Ihren Atem.</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
@@ -2220,62 +2220,74 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[2]</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>The body spoke first. The mind explained second, and this explanation felt like the event.</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Der Körper sprach zuerst. Der Kopf erklärte danach, und diese Erklärung fühlte sich an wie das Ereignis.</t>
+          <t>Spüren Sie Ihre Schultern.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
       <c r="F66" s="11" t="n"/>
     </row>
-    <row r="67" ht="105" customHeight="1">
+    <row r="67" ht="30" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>“You know the day” — page 12, above the three instructions</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>knowTheDay.runs[3]</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>This book is about that mistake. It is about that error as a daily, ambient, invisible feature of being alive in a body that is constantly producing signals, which your mind is constantly reading or misreading. Before any of that, before the science and the mechanism and the reason the instrument was miscalibrated yesterday, try something right now.</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>In diesem Buch geht es um diesen Fehler. Es geht um diesen Irrtum als etwas Tägliches, Beiläufiges, Unsichtbares, das zum Leben in einem Körper dazugehört, der ständig Signale erzeugt, die Ihr Kopf ständig liest oder falsch liest. Vor all dem, vor der Wissenschaft und dem Mechanismus und dem Grund, warum das Instrument gestern falsch kalibriert war, probieren Sie jetzt gleich etwas aus.</t>
+          <t>Was Sie gefunden haben, ist ein Befund.</t>
         </is>
       </c>
       <c r="E67" s="11" t="n"/>
       <c r="F67" s="11" t="n"/>
     </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
-        <is>
-          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
-        </is>
-      </c>
-      <c r="B68" s="8" t="n"/>
-      <c r="C68" s="8" t="n"/>
-      <c r="D68" s="8" t="n"/>
-      <c r="E68" s="8" t="n"/>
-      <c r="F68" s="8" t="n"/>
+    <row r="68" ht="60" customHeight="1">
+      <c r="A68" s="9" t="inlineStr">
+        <is>
+          <t>“Try something right now” — the three instructions, page 13</t>
+        </is>
+      </c>
+      <c r="B68" s="9" t="inlineStr">
+        <is>
+          <t>reading.afterResult</t>
+        </is>
+      </c>
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>Ein Befund, abgelesen an dem Instrument, das in diesem Moment alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Oder auch nicht. Das können Sie nicht wissen, bevor Sie die Einstellungen gesehen haben.</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="n"/>
+      <c r="F68" s="11" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
@@ -2285,65 +2297,53 @@
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>reading.eyebrow</t>
+          <t>reading.question</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Try something right now</t>
+          <t>Is this the situation? Or is this the state?</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Probieren Sie jetzt gleich etwas aus</t>
+          <t>Ist das die Situation? Oder ist das der Zustand?</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
     </row>
-    <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="9" t="inlineStr">
-        <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
-        </is>
-      </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>reading.lead</t>
-        </is>
-      </c>
-      <c r="C70" s="10" t="inlineStr">
-        <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
-        </is>
-      </c>
-      <c r="D70" s="10" t="inlineStr">
-        <is>
-          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="n"/>
-      <c r="F70" s="11" t="n"/>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>THE BOOK — THE AUTHOR’S LINE, WHO IT IS FOR</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="n"/>
+      <c r="C70" s="8" t="n"/>
+      <c r="D70" s="8" t="n"/>
+      <c r="E70" s="8" t="n"/>
+      <c r="F70" s="8" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>book.eyebrow</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihren Kiefer.</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
@@ -2352,22 +2352,22 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B72" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>book.paragraphs[0]</t>
         </is>
       </c>
       <c r="C72" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D72" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihren Atem.</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E72" s="11" t="n"/>
@@ -2376,130 +2376,130 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>book.readersEyebrow</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>Who it is for</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihre Schultern.</t>
+          <t>Für wen es ist</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="30" customHeight="1">
+    <row r="74" ht="75" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The book — the author’s line, who it is for</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>book.readers</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Was Sie gefunden haben, ist ein Befund.</t>
+          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
     </row>
-    <row r="75" ht="60" customHeight="1">
-      <c r="A75" s="9" t="inlineStr">
-        <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
-        </is>
-      </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>reading.afterResult</t>
-        </is>
-      </c>
-      <c r="C75" s="10" t="inlineStr">
-        <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
-        </is>
-      </c>
-      <c r="D75" s="10" t="inlineStr">
-        <is>
-          <t>Ein Befund, abgelesen an dem Instrument, das in diesem Moment alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Oder auch nicht. Das können Sie nicht wissen, bevor Sie die Einstellungen gesehen haben.</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="n"/>
-      <c r="F75" s="11" t="n"/>
+    <row r="75" ht="22" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
+        <is>
+          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
+        </is>
+      </c>
+      <c r="B75" s="8" t="n"/>
+      <c r="C75" s="8" t="n"/>
+      <c r="D75" s="8" t="n"/>
+      <c r="E75" s="8" t="n"/>
+      <c r="F75" s="8" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>excerpt.eyebrow</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>Read</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Ist das die Situation? Oder ist das der Zustand?</t>
+          <t>Lesen</t>
         </is>
       </c>
       <c r="E76" s="11" t="n"/>
       <c r="F76" s="11" t="n"/>
     </row>
-    <row r="77" ht="22" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK — THE PAGE 20 HEADING, THE AUTHOR’S ACCOUNT, WHO IT IS FOR</t>
-        </is>
-      </c>
-      <c r="B77" s="8" t="n"/>
-      <c r="C77" s="8" t="n"/>
-      <c r="D77" s="8" t="n"/>
-      <c r="E77" s="8" t="n"/>
-      <c r="F77" s="8" t="n"/>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B77" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.title</t>
+        </is>
+      </c>
+      <c r="C77" s="10" t="inlineStr">
+        <is>
+          <t>Before the chapters</t>
+        </is>
+      </c>
+      <c r="D77" s="10" t="inlineStr">
+        <is>
+          <t>Vor den Kapiteln</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="11" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>book.eyebrow</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Das Buch</t>
+          <t>Der Pilot</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2508,22 +2508,22 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>book.heading</t>
+          <t>excerpt.runningHead</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>Same morning. Same paragraph. Same Katrin. Different instrument settings.</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>Derselbe Morgen. Derselbe Absatz. Dieselbe Katrin. Andere Einstellungen am Instrument.</t>
+          <t>State. Not Situation</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
@@ -2532,46 +2532,46 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>book.headingSource</t>
+          <t>excerpt.cta</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Seite 20</t>
+          <t>Leseprobe lesen</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
       <c r="F80" s="11" t="n"/>
     </row>
-    <row r="81" ht="135" customHeight="1">
+    <row r="81" ht="30" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[0]</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
+          <t>Weiterlesen</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
@@ -2580,22 +2580,22 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>book.paragraphs[1]</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
@@ -2604,88 +2604,100 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>book.readersEyebrow</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Für wen es ist</t>
+          <t>Lesemodus</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
     </row>
-    <row r="84" ht="75" customHeight="1">
+    <row r="84" ht="105" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>book.readersAnchor</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>This book does not replace professional support and it does not treat complex conditions as lifestyle problems. It works in the gap between fine and clinical, the space where most people live on most days.</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Dieses Buch ersetzt keine professionelle Hilfe, und es behandelt komplexe Erkrankungen nicht als Fragen des Lebensstils. Es arbeitet in der Lücke zwischen gesund und klinisch, in dem Raum, in dem die meisten Menschen an den meisten Tagen leben.</t>
+          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="75" customHeight="1">
+    <row r="85" ht="210" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>The book — the page 20 heading, the author’s account, who it is for</t>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>book.readers</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
+          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
         </is>
       </c>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
     </row>
-    <row r="86" ht="22" customHeight="1">
-      <c r="A86" s="7" t="inlineStr">
-        <is>
-          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
-        </is>
-      </c>
-      <c r="B86" s="8" t="n"/>
-      <c r="C86" s="8" t="n"/>
-      <c r="D86" s="8" t="n"/>
-      <c r="E86" s="8" t="n"/>
-      <c r="F86" s="8" t="n"/>
-    </row>
-    <row r="87" ht="30" customHeight="1">
+    <row r="86" ht="150" customHeight="1">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>The extract — opening pages of the book, and the page 26 line</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.paragraphs[2]</t>
+        </is>
+      </c>
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="n"/>
+      <c r="F86" s="11" t="n"/>
+    </row>
+    <row r="87" ht="165" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2693,23 +2705,23 @@
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>excerpt.eyebrow</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Lesen</t>
+          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
     </row>
-    <row r="88" ht="30" customHeight="1">
+    <row r="88" ht="120" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2717,23 +2729,23 @@
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Vor den Kapiteln</t>
+          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
     </row>
-    <row r="89" ht="30" customHeight="1">
+    <row r="89" ht="135" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2741,23 +2753,23 @@
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot</t>
+          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
     </row>
-    <row r="90" ht="30" customHeight="1">
+    <row r="90" ht="75" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2765,23 +2777,23 @@
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
     </row>
-    <row r="91" ht="30" customHeight="1">
+    <row r="91" ht="240" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2789,17 +2801,17 @@
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe lesen</t>
+          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2813,23 +2825,23 @@
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>Weiterlesen</t>
+          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
     </row>
-    <row r="93" ht="30" customHeight="1">
+    <row r="93" ht="135" customHeight="1">
       <c r="A93" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2837,17 +2849,17 @@
       </c>
       <c r="B93" s="9" t="inlineStr">
         <is>
-          <t>excerpt.back</t>
+          <t>excerpt.closing</t>
         </is>
       </c>
       <c r="C93" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
         </is>
       </c>
       <c r="D93" s="10" t="inlineStr">
         <is>
-          <t>Zurück zum Buch</t>
+          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
         </is>
       </c>
       <c r="E93" s="11" t="n"/>
@@ -2861,23 +2873,23 @@
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Lesemodus</t>
+          <t>Seite 26</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
       <c r="F94" s="11" t="n"/>
     </row>
-    <row r="95" ht="105" customHeight="1">
+    <row r="95" ht="30" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2885,23 +2897,23 @@
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
+          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
       <c r="F95" s="11" t="n"/>
     </row>
-    <row r="96" ht="210" customHeight="1">
+    <row r="96" ht="30" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2909,23 +2921,23 @@
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
+          <t>Die Leseprobe in dieser Sprache folgt.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
       <c r="F96" s="11" t="n"/>
     </row>
-    <row r="97" ht="150" customHeight="1">
+    <row r="97" ht="30" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2933,23 +2945,23 @@
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
       <c r="F97" s="11" t="n"/>
     </row>
-    <row r="98" ht="165" customHeight="1">
+    <row r="98" ht="30" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2957,23 +2969,23 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
       <c r="F98" s="11" t="n"/>
     </row>
-    <row r="99" ht="120" customHeight="1">
+    <row r="99" ht="30" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
           <t>The extract — opening pages of the book, and the page 26 line</t>
@@ -2981,89 +2993,77 @@
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>excerpt.folios[2]</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="135" customHeight="1">
-      <c r="A100" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
-        </is>
-      </c>
-      <c r="B100" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.paragraphs[5]</t>
-        </is>
-      </c>
-      <c r="C100" s="10" t="inlineStr">
-        <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
-        </is>
-      </c>
-      <c r="D100" s="10" t="inlineStr">
-        <is>
-          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
-        </is>
-      </c>
-      <c r="E100" s="11" t="n"/>
-      <c r="F100" s="11" t="n"/>
-    </row>
-    <row r="101" ht="75" customHeight="1">
+    <row r="100" ht="22" customHeight="1">
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>CASE EVIDENCE CARDS</t>
+        </is>
+      </c>
+      <c r="B100" s="8" t="n"/>
+      <c r="C100" s="8" t="n"/>
+      <c r="D100" s="8" t="n"/>
+      <c r="E100" s="8" t="n"/>
+      <c r="F100" s="8" t="n"/>
+    </row>
+    <row r="101" ht="30" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>cases.eyebrow</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
+          <t>Beweismaterial</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
       <c r="F101" s="11" t="n"/>
     </row>
-    <row r="102" ht="240" customHeight="1">
+    <row r="102" ht="30" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>cases.pageLabel</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
@@ -3072,46 +3072,46 @@
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>cases.items[0].quote</t>
         </is>
       </c>
       <c r="C103" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D103" s="10" t="inlineStr">
         <is>
-          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
+          <t>„Irgendetwas stimmt nicht.“</t>
         </is>
       </c>
       <c r="E103" s="11" t="n"/>
       <c r="F103" s="11" t="n"/>
     </row>
-    <row r="104" ht="135" customHeight="1">
+    <row r="104" ht="30" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closing</t>
+          <t>cases.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3120,22 +3120,22 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closingSource</t>
+          <t>cases.items[0].input</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Seite 26</t>
+          <t>Zwei Minuten vor dem Wecker.</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
@@ -3144,22 +3144,22 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>cases.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
+          <t>Bestätigtes Ereignis</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
@@ -3168,22 +3168,22 @@
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>cases.items[0].verified</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Die Leseprobe in dieser Sprache folgt.</t>
+          <t>Nichts ist passiert.</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
@@ -3192,22 +3192,22 @@
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>cases.items[1].quote</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>„ok.“</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
@@ -3216,22 +3216,22 @@
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>cases.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
@@ -3240,38 +3240,50 @@
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Case evidence cards</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>cases.items[1].input</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Zwei Buchstaben. Ein Punkt.</t>
         </is>
       </c>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
     </row>
-    <row r="111" ht="22" customHeight="1">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>CASE EVIDENCE CARDS</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="n"/>
-      <c r="C111" s="8" t="n"/>
-      <c r="D111" s="8" t="n"/>
-      <c r="E111" s="8" t="n"/>
-      <c r="F111" s="8" t="n"/>
+    <row r="111" ht="30" customHeight="1">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>Case evidence cards</t>
+        </is>
+      </c>
+      <c r="B111" s="9" t="inlineStr">
+        <is>
+          <t>cases.items[1].verifiedLabel</t>
+        </is>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
+        <is>
+          <t>Verified tone</t>
+        </is>
+      </c>
+      <c r="D111" s="10" t="inlineStr">
+        <is>
+          <t>Bestätigter Tonfall</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="11" t="n"/>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
@@ -3281,17 +3293,17 @@
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>cases.eyebrow</t>
+          <t>cases.items[1].verified</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>Case evidence</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Beweismaterial</t>
+          <t>Keiner.</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
@@ -3305,17 +3317,17 @@
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>cases.items[2].quote</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
@@ -3329,17 +3341,17 @@
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].quote</t>
+          <t>cases.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>“Something is off.”</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>„Irgendetwas stimmt nicht.“</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
@@ -3353,17 +3365,17 @@
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>cases.items[2].input</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
@@ -3377,17 +3389,17 @@
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>cases.items[2].verifiedLabel</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>Verified crisis</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Zwei Minuten vor dem Wecker.</t>
+          <t>Bestätigte Krise</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
@@ -3401,17 +3413,17 @@
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verifiedLabel</t>
+          <t>cases.items[2].verified</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>Verified event</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Bestätigtes Ereignis</t>
+          <t>Keine.</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
@@ -3425,17 +3437,17 @@
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>cases.items[3].quote</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>“This is state, not situation.”</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>Nichts ist passiert.</t>
+          <t>„Das ist Zustand, nicht Situation.“</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
@@ -3449,17 +3461,17 @@
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>cases.items[3].inputLabel</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>„ok.“</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3473,17 +3485,17 @@
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>cases.items[3].input</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Low fuel. Dead light. A sound on grit.</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Wenig Treibstoff. Kaputtes Licht. Ein Geräusch auf Splitt.</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3497,17 +3509,17 @@
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>cases.items[3].verifiedLabel</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Verified threat</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Zwei Buchstaben. Ein Punkt.</t>
+          <t>Bestätigte Bedrohung</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3521,17 +3533,17 @@
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>cases.items[3].verified</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>Not yet visible.</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Bestätigter Tonfall</t>
+          <t>Noch nicht sichtbar.</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3545,17 +3557,17 @@
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>cases.closing</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Keiner.</t>
+          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3569,65 +3581,53 @@
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>cases.closingSource</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
+          <t>Seite 20</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
     </row>
-    <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B125" s="9" t="inlineStr">
-        <is>
-          <t>cases.items[2].inputLabel</t>
-        </is>
-      </c>
-      <c r="C125" s="10" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="D125" s="10" t="inlineStr">
-        <is>
-          <t>Input</t>
-        </is>
-      </c>
-      <c r="E125" s="11" t="n"/>
-      <c r="F125" s="11" t="n"/>
+    <row r="125" ht="22" customHeight="1">
+      <c r="A125" s="7" t="inlineStr">
+        <is>
+          <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
+        </is>
+      </c>
+      <c r="B125" s="8" t="n"/>
+      <c r="C125" s="8" t="n"/>
+      <c r="D125" s="8" t="n"/>
+      <c r="E125" s="8" t="n"/>
+      <c r="F125" s="8" t="n"/>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B126" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].input</t>
+          <t>listen.eyebrow</t>
         </is>
       </c>
       <c r="C126" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D126" s="10" t="inlineStr">
         <is>
-          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
+          <t>Hören</t>
         </is>
       </c>
       <c r="E126" s="11" t="n"/>
@@ -3636,22 +3636,22 @@
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Krise</t>
+          <t>Hörprobe</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3660,22 +3660,22 @@
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Keine.</t>
+          <t>Gelesen von der Autorin</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3684,22 +3684,22 @@
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>„Das ist Zustand, nicht Situation.“</t>
+          <t>Abspielen</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3708,22 +3708,22 @@
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3732,22 +3732,22 @@
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Wenig Treibstoff. Kaputtes Licht. Ein Geräusch auf Splitt.</t>
+          <t>Wiedergabeposition</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3756,22 +3756,22 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Bedrohung</t>
+          <t>Verstrichen</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3780,22 +3780,22 @@
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Noch nicht sichtbar.</t>
+          <t>Dauer</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3804,82 +3804,82 @@
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Audio player (hidden until a recording exists)</t>
         </is>
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>cases.closing</t>
+          <t>listen.unavailable</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>It said I am failing; the data was I am tired.</t>
+          <t>The recording will be added here.</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
+          <t>Die Aufnahme folgt hier.</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B135" s="9" t="inlineStr">
-        <is>
-          <t>cases.closingSource</t>
-        </is>
-      </c>
-      <c r="C135" s="10" t="inlineStr">
-        <is>
-          <t>Page 20</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>Seite 20</t>
-        </is>
-      </c>
-      <c r="E135" s="11" t="n"/>
-      <c r="F135" s="11" t="n"/>
-    </row>
-    <row r="136" ht="22" customHeight="1">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
-        </is>
-      </c>
-      <c r="B136" s="8" t="n"/>
-      <c r="C136" s="8" t="n"/>
-      <c r="D136" s="8" t="n"/>
-      <c r="E136" s="8" t="n"/>
-      <c r="F136" s="8" t="n"/>
-    </row>
-    <row r="137" ht="30" customHeight="1">
+    <row r="135" ht="22" customHeight="1">
+      <c r="A135" s="7" t="inlineStr">
+        <is>
+          <t>THE INVESTIGATION (PAGE 11), “BEFORE WE BEGIN” (PAGE 13 MARKERS), THE THREE SYSTEMS, PAGE 226</t>
+        </is>
+      </c>
+      <c r="B135" s="8" t="n"/>
+      <c r="C135" s="8" t="n"/>
+      <c r="D135" s="8" t="n"/>
+      <c r="E135" s="8" t="n"/>
+      <c r="F135" s="8" t="n"/>
+    </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="9" t="inlineStr">
+        <is>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+        </is>
+      </c>
+      <c r="B136" s="9" t="inlineStr">
+        <is>
+          <t>map.eyebrow</t>
+        </is>
+      </c>
+      <c r="C136" s="10" t="inlineStr">
+        <is>
+          <t>A map of the book</t>
+        </is>
+      </c>
+      <c r="D136" s="10" t="inlineStr">
+        <is>
+          <t>Eine Karte des Buches</t>
+        </is>
+      </c>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="11" t="n"/>
+    </row>
+    <row r="137" ht="90" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>listen.eyebrow</t>
+          <t>map.sortingTool</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Hören</t>
+          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3888,46 +3888,46 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>map.loops[0].name</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Hörprobe</t>
+          <t>Zeit</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
     </row>
-    <row r="139" ht="30" customHeight="1">
+    <row r="139" ht="45" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>map.loops[0].body</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Gelesen von der Autorin</t>
+          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3936,46 +3936,46 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>map.loops[1].name</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Abspielen</t>
+          <t>Aufmerksamkeit</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
     </row>
-    <row r="141" ht="30" customHeight="1">
+    <row r="141" ht="60" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>map.loops[1].body</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf das, was gerade da ist und am wenigsten Mühe macht, und die Arbeit, die einem viel abverlangt, fühlt sich schwer an.</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3984,46 +3984,46 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>map.loops[2].name</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Wiedergabeposition</t>
+          <t>Sicherheit</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
     </row>
-    <row r="143" ht="30" customHeight="1">
+    <row r="143" ht="75" customHeight="1">
       <c r="A143" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>map.loops[2].body</t>
         </is>
       </c>
       <c r="C143" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
         </is>
       </c>
       <c r="D143" s="10" t="inlineStr">
         <is>
-          <t>Verstrichen</t>
+          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Auf Dinge wie Bewertung durch andere, Ausgrenzung, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
         </is>
       </c>
       <c r="E143" s="11" t="n"/>
@@ -4032,130 +4032,142 @@
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>map.evidenceEyebrow</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Before we begin</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Dauer</t>
+          <t>Bevor wir anfangen</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="30" customHeight="1">
+    <row r="145" ht="120" customHeight="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>Audio player (hidden until a recording exists)</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>listen.unavailable</t>
+          <t>map.evidenceIntro</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>The recording will be added here.</t>
+          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>Die Aufnahme folgt hier.</t>
+          <t>Dieses Buch macht Aussagen über Gehirn und Körper, und diese Aussagen sind unterschiedlich gut belegt. Manche stützen sich auf Jahrzehnte replizierter Forschung. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche sind plausible Weiterführungen gesicherter Erkenntnisse, die in genau der Form, die dieses Buch beschreibt, noch nicht direkt geprüft wurden. Sie sollten wissen, was davon was ist.</t>
         </is>
       </c>
       <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
     </row>
-    <row r="146" ht="22" customHeight="1">
-      <c r="A146" s="7" t="inlineStr">
-        <is>
-          <t>“BEFORE WE BEGIN” (PAGE 13 MARKERS) AND THE MAP — THE THREE SYSTEMS, THE SIXTEEN CHAPTERS, PAGE 226</t>
-        </is>
-      </c>
-      <c r="B146" s="8" t="n"/>
-      <c r="C146" s="8" t="n"/>
-      <c r="D146" s="8" t="n"/>
-      <c r="E146" s="8" t="n"/>
-      <c r="F146" s="8" t="n"/>
+    <row r="146" ht="180" customHeight="1">
+      <c r="A146" s="9" t="inlineStr">
+        <is>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+        </is>
+      </c>
+      <c r="B146" s="9" t="inlineStr">
+        <is>
+          <t>map.evidenceMarkers</t>
+        </is>
+      </c>
+      <c r="C146" s="10" t="inlineStr">
+        <is>
+          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+        </is>
+      </c>
+      <c r="D146" s="10" t="inlineStr">
+        <is>
+          <t>Im ganzen Buch tragen wissenschaftliche Aussagen eine Markierung, die zeigt, wie gut sie belegt sind. Stützt sich ein Ergebnis auf solide, replizierte Belege, sehen Sie am Rand eine Grafik, gekennzeichnet als hoch belegt, mit einem tiefroten Herzschlag. Sind die Belege zwar ein Hinweis, aber unvollständig, steht dort mittel belegt, mit einem orangefarbenen Herzschlag. Ist eine Aussage eine plausible Hypothese, die noch strengere Prüfungen braucht, ist sie als niedrig markiert, in verblasstem Grau. Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt. Es will eine plausible Geschichte nicht als gesicherte Wahrheit behandeln. Diese Markierungen sind eine Bremse dagegen.</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="n"/>
+      <c r="F146" s="11" t="n"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B147" s="9" t="inlineStr">
         <is>
-          <t>map.eyebrow</t>
+          <t>map.grades[0].label</t>
         </is>
       </c>
       <c r="C147" s="10" t="inlineStr">
         <is>
-          <t>A map of the book</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D147" s="10" t="inlineStr">
         <is>
-          <t>Eine Karte des Buches</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="E147" s="11" t="n"/>
       <c r="F147" s="11" t="n"/>
     </row>
-    <row r="148" ht="90" customHeight="1">
+    <row r="148" ht="30" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>map.systemsIntro</t>
+          <t>map.grades[1].label</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Three systems ran through Katrin’s morning. Time started at 06:38 and never stopped. Attention took the phone at 06:52. Safety wrote the email’s meaning at 07:25. She can name none of them. The only thing she can name is David, and David is the smallest part of it.</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>An Katrins Morgen waren drei Systeme am Werk. Zeit fing um 06:38 an und hörte nicht mehr auf. Aufmerksamkeit griff um 06:52 nach dem Handy. Sicherheit schrieb um 07:25, was die E-Mail bedeutete. Sie kann keines davon benennen. Das Einzige, was sie benennen kann, ist David, und David ist der kleinste Teil davon.</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
       <c r="F148" s="11" t="n"/>
     </row>
-    <row r="149" ht="90" customHeight="1">
+    <row r="149" ht="30" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>map.sortingTool</t>
+          <t>map.grades[2].label</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
@@ -4164,46 +4176,46 @@
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].name</t>
+          <t>map.investigationTitle</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>The Investigation</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Zeit</t>
+          <t>Die Untersuchung</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
       <c r="F150" s="11" t="n"/>
     </row>
-    <row r="151" ht="45" customHeight="1">
+    <row r="151" ht="30" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].body</t>
+          <t>map.mapLine</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
+          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
@@ -4212,46 +4224,46 @@
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].name</t>
+          <t>map.pageColumn</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Aufmerksamkeit</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
       <c r="F152" s="11" t="n"/>
     </row>
-    <row r="153" ht="60" customHeight="1">
+    <row r="153" ht="30" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].body</t>
+          <t>map.chapters[0].title</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf das, was gerade da ist und am wenigsten Mühe macht, und die Arbeit, die einem viel abverlangt, fühlt sich schwer an.</t>
+          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
@@ -4260,46 +4272,46 @@
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].name</t>
+          <t>map.chapters[1].title</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Sicherheit</t>
+          <t>Das Radar hatte recht</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
       <c r="F154" s="11" t="n"/>
     </row>
-    <row r="155" ht="75" customHeight="1">
+    <row r="155" ht="30" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].body</t>
+          <t>map.chapters[2].title</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Auf Dinge wie Bewertung durch andere, Ausgrenzung, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
+          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
@@ -4308,70 +4320,70 @@
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceEyebrow</t>
+          <t>map.chapters[3].title</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Bevor wir anfangen</t>
+          <t>Die Erleichterung, die zum Juckreiz wird</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
       <c r="F156" s="11" t="n"/>
     </row>
-    <row r="157" ht="120" customHeight="1">
+    <row r="157" ht="30" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceIntro</t>
+          <t>map.chapters[4].title</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Dieses Buch macht Aussagen über Gehirn und Körper, und diese Aussagen sind unterschiedlich gut belegt. Manche stützen sich auf Jahrzehnte replizierter Forschung. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche sind plausible Weiterführungen gesicherter Erkenntnisse, die in genau der Form, die dieses Buch beschreibt, noch nicht direkt geprüft wurden. Sie sollten wissen, was davon was ist.</t>
+          <t>Der vorhersehbare Auslöser</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
       <c r="F157" s="11" t="n"/>
     </row>
-    <row r="158" ht="180" customHeight="1">
+    <row r="158" ht="30" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceMarkers</t>
+          <t>map.chapters[5].title</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Im ganzen Buch tragen wissenschaftliche Aussagen eine Markierung, die zeigt, wie gut sie belegt sind. Stützt sich ein Ergebnis auf solide, replizierte Belege, sehen Sie am Rand eine Grafik, gekennzeichnet als hoch belegt, mit einem tiefroten Herzschlag. Sind die Belege zwar ein Hinweis, aber unvollständig, steht dort mittel belegt, mit einem orangefarbenen Herzschlag. Ist eine Aussage eine plausible Hypothese, die noch strengere Prüfungen braucht, ist sie als niedrig markiert, in verblasstem Grau. Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt. Es will eine plausible Geschichte nicht als gesicherte Wahrheit behandeln. Diese Markierungen sind eine Bremse dagegen.</t>
+          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4380,22 +4392,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>map.grades[0].label</t>
+          <t>map.chapters[6].title</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Hoch</t>
+          <t>Warum Ruhe nicht immer erholsam ist</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4404,22 +4416,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>map.grades[1].label</t>
+          <t>map.chapters[7].title</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4428,22 +4440,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>map.grades[2].label</t>
+          <t>map.chapters[8].title</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Niedrig</t>
+          <t>Die offene Akte</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4452,22 +4464,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>map.investigationTitle</t>
+          <t>map.chapters[9].title</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung</t>
+          <t>Kommen zwei Nervensysteme in eine Küche</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4476,22 +4488,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>map.mapLine</t>
+          <t>map.chapters[10].title</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Der Streit, der Dienstag war</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4500,22 +4512,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>map.pageColumn</t>
+          <t>map.chapters[11].title</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>Der Donnerstag, der Mittwochabend war</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4524,22 +4536,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[0].title</t>
+          <t>map.chapters[12].title</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
+          <t>Das saubere Instrumentenbrett</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4548,22 +4560,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[1].title</t>
+          <t>map.chapters[13].title</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Das Radar hatte recht</t>
+          <t>Das eine Mal, als der Körper recht hatte</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4572,22 +4584,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[2].title</t>
+          <t>map.chapters[14].title</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
+          <t>Es geht nicht um mich</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4596,22 +4608,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[3].title</t>
+          <t>map.chapters[15].title</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Die Erleichterung, die zum Juckreiz wird</t>
+          <t>Die Vorhersage</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4620,46 +4632,46 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[4].title</t>
+          <t>map.mapFooter</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>The Scientific Heartbeat follows the chapters.</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Der vorhersehbare Auslöser</t>
+          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
     </row>
-    <row r="170" ht="30" customHeight="1">
+    <row r="170" ht="75" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[5].title</t>
+          <t>map.heartbeat[0]</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4668,22 +4680,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[6].title</t>
+          <t>map.heartbeat[1]</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Warum Ruhe nicht immer erholsam ist</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4692,70 +4704,58 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[7].title</t>
+          <t>map.heartbeatSource</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Page 226</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
+          <t>Seite 226</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
     </row>
-    <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="9" t="inlineStr">
-        <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
-        </is>
-      </c>
-      <c r="B173" s="9" t="inlineStr">
-        <is>
-          <t>map.chapters[8].title</t>
-        </is>
-      </c>
-      <c r="C173" s="10" t="inlineStr">
-        <is>
-          <t>The Open File</t>
-        </is>
-      </c>
-      <c r="D173" s="10" t="inlineStr">
-        <is>
-          <t>Die offene Akte</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="n"/>
-      <c r="F173" s="11" t="n"/>
+    <row r="173" ht="22" customHeight="1">
+      <c r="A173" s="7" t="inlineStr">
+        <is>
+          <t>ABOUT THE AUTHOR</t>
+        </is>
+      </c>
+      <c r="B173" s="8" t="n"/>
+      <c r="C173" s="8" t="n"/>
+      <c r="D173" s="8" t="n"/>
+      <c r="E173" s="8" t="n"/>
+      <c r="F173" s="8" t="n"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[9].title</t>
+          <t>author.eyebrow</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>The author</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Kommen zwei Nervensysteme in eine Küche</t>
+          <t>Die Autorin</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4764,22 +4764,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[10].title</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Der Streit, der Dienstag war</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4788,22 +4788,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[11].title</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Der Donnerstag, der Mittwochabend war</t>
+          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4812,22 +4812,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[12].title</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Das saubere Instrumentenbrett</t>
+          <t>Foto der Autorin folgt</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4836,22 +4836,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[13].title</t>
+          <t>author.bio</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Das eine Mal, als der Körper recht hatte</t>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4860,22 +4860,22 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[14].title</t>
+          <t>author.websiteLabel</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>Practice website</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Es geht nicht um mich</t>
+          <t>Website der Praxis</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
@@ -4884,22 +4884,22 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[15].title</t>
+          <t>author.contactLabel</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>Die Vorhersage</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E180" s="11" t="n"/>
@@ -4908,70 +4908,58 @@
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>map.mapFooter</t>
+          <t>author.pressLabel</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
     </row>
-    <row r="182" ht="75" customHeight="1">
-      <c r="A182" s="9" t="inlineStr">
-        <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
-        </is>
-      </c>
-      <c r="B182" s="9" t="inlineStr">
-        <is>
-          <t>map.heartbeat[0]</t>
-        </is>
-      </c>
-      <c r="C182" s="10" t="inlineStr">
-        <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
-        </is>
-      </c>
-      <c r="D182" s="10" t="inlineStr">
-        <is>
-          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
-        </is>
-      </c>
-      <c r="E182" s="11" t="n"/>
-      <c r="F182" s="11" t="n"/>
+    <row r="182" ht="22" customHeight="1">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="n"/>
+      <c r="C182" s="8" t="n"/>
+      <c r="D182" s="8" t="n"/>
+      <c r="E182" s="8" t="n"/>
+      <c r="F182" s="8" t="n"/>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The book’s last sentence, above the notify form</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[1]</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
+          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
@@ -4980,22 +4968,22 @@
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>“Before we begin” (page 13 markers) and the map — the three systems, the sixteen chapters, page 226</t>
+          <t>The book’s last sentence, above the notify form</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeatSource</t>
+          <t>closing.source</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>Seite 226</t>
+          <t>Seite 225</t>
         </is>
       </c>
       <c r="E184" s="11" t="n"/>
@@ -5004,7 +4992,7 @@
     <row r="185" ht="22" customHeight="1">
       <c r="A185" s="7" t="inlineStr">
         <is>
-          <t>ABOUT THE AUTHOR</t>
+          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
         </is>
       </c>
       <c r="B185" s="8" t="n"/>
@@ -5016,70 +5004,58 @@
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Companion tool (currently hidden)</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>author.eyebrow</t>
+          <t>companion.eyebrow</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>The author</t>
+          <t>Alongside the book</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>Die Autorin</t>
+          <t>Begleitend zum Buch</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
     </row>
-    <row r="187" ht="30" customHeight="1">
-      <c r="A187" s="9" t="inlineStr">
-        <is>
-          <t>About the author</t>
-        </is>
-      </c>
-      <c r="B187" s="9" t="inlineStr">
-        <is>
-          <t>author.title</t>
-        </is>
-      </c>
-      <c r="C187" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="D187" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="n"/>
-      <c r="F187" s="11" t="n"/>
+    <row r="187" ht="22" customHeight="1">
+      <c r="A187" s="7" t="inlineStr">
+        <is>
+          <t>PRESS PAGE</t>
+        </is>
+      </c>
+      <c r="B187" s="8" t="n"/>
+      <c r="C187" s="8" t="n"/>
+      <c r="D187" s="8" t="n"/>
+      <c r="E187" s="8" t="n"/>
+      <c r="F187" s="8" t="n"/>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
@@ -5088,22 +5064,22 @@
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>author.photoPlaceholder</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Author photograph to follow</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin folgt</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E189" s="11" t="n"/>
@@ -5112,22 +5088,22 @@
     <row r="190" ht="30" customHeight="1">
       <c r="A190" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
@@ -5136,22 +5112,22 @@
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Website der Praxis</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E191" s="11" t="n"/>
@@ -5160,22 +5136,22 @@
     <row r="192" ht="30" customHeight="1">
       <c r="A192" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
@@ -5184,58 +5160,70 @@
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>Cover, Vorderseite, hohe Auflösung</t>
         </is>
       </c>
       <c r="E193" s="11" t="n"/>
       <c r="F193" s="11" t="n"/>
     </row>
-    <row r="194" ht="22" customHeight="1">
-      <c r="A194" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
-        </is>
-      </c>
-      <c r="B194" s="8" t="n"/>
-      <c r="C194" s="8" t="n"/>
-      <c r="D194" s="8" t="n"/>
-      <c r="E194" s="8" t="n"/>
-      <c r="F194" s="8" t="n"/>
+    <row r="194" ht="30" customHeight="1">
+      <c r="A194" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B194" s="9" t="inlineStr">
+        <is>
+          <t>press.assets[0].note</t>
+        </is>
+      </c>
+      <c r="C194" s="10" t="inlineStr">
+        <is>
+          <t>JPEG, 2400 px wide</t>
+        </is>
+      </c>
+      <c r="D194" s="10" t="inlineStr">
+        <is>
+          <t>JPEG, 2400 px breit</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="n"/>
+      <c r="F194" s="11" t="n"/>
     </row>
     <row r="195" ht="30" customHeight="1">
       <c r="A195" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>closing.question</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this their state?</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
+          <t>Foto der Autorin</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
@@ -5244,74 +5232,98 @@
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B196" s="9" t="inlineStr">
         <is>
-          <t>closing.source</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>Seite 225</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E196" s="11" t="n"/>
       <c r="F196" s="11" t="n"/>
     </row>
-    <row r="197" ht="22" customHeight="1">
-      <c r="A197" s="7" t="inlineStr">
-        <is>
-          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
-        </is>
-      </c>
-      <c r="B197" s="8" t="n"/>
-      <c r="C197" s="8" t="n"/>
-      <c r="D197" s="8" t="n"/>
-      <c r="E197" s="8" t="n"/>
-      <c r="F197" s="8" t="n"/>
+    <row r="197" ht="30" customHeight="1">
+      <c r="A197" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B197" s="9" t="inlineStr">
+        <is>
+          <t>press.assets[2].label</t>
+        </is>
+      </c>
+      <c r="C197" s="10" t="inlineStr">
+        <is>
+          <t>Book render, transparent background</t>
+        </is>
+      </c>
+      <c r="D197" s="10" t="inlineStr">
+        <is>
+          <t>Buchansicht, freigestellt</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="n"/>
+      <c r="F197" s="11" t="n"/>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="9" t="inlineStr">
         <is>
-          <t>Companion tool (currently hidden)</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B198" s="9" t="inlineStr">
         <is>
-          <t>companion.eyebrow</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>Alongside the book</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>Begleitend zum Buch</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E198" s="11" t="n"/>
       <c r="F198" s="11" t="n"/>
     </row>
-    <row r="199" ht="22" customHeight="1">
-      <c r="A199" s="7" t="inlineStr">
-        <is>
-          <t>PRESS PAGE</t>
-        </is>
-      </c>
-      <c r="B199" s="8" t="n"/>
-      <c r="C199" s="8" t="n"/>
-      <c r="D199" s="8" t="n"/>
-      <c r="E199" s="8" t="n"/>
-      <c r="F199" s="8" t="n"/>
+    <row r="199" ht="30" customHeight="1">
+      <c r="A199" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B199" s="9" t="inlineStr">
+        <is>
+          <t>press.assets[3].label</t>
+        </is>
+      </c>
+      <c r="C199" s="10" t="inlineStr">
+        <is>
+          <t>Web banner</t>
+        </is>
+      </c>
+      <c r="D199" s="10" t="inlineStr">
+        <is>
+          <t>Webbanner</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="n"/>
+      <c r="F199" s="11" t="n"/>
     </row>
     <row r="200" ht="30" customHeight="1">
       <c r="A200" s="9" t="inlineStr">
@@ -5321,17 +5333,17 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.eyebrow</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
@@ -5345,17 +5357,17 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.title</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>Bild für Social Media, quadratisch</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
@@ -5369,17 +5381,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5393,17 +5405,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Bild für Social Media, Hochformat</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5417,17 +5429,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assetsHeading</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5441,17 +5453,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>Cover, Vorderseite, hohe Auflösung</t>
+          <t>Bild für Social Media, Querformat</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5465,17 +5477,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].note</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px wide</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px breit</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5489,17 +5501,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin</t>
+          <t>Leseprobe, die ersten Seiten</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5513,17 +5525,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>PDF, vier Seiten</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5537,17 +5549,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>Buchansicht, freigestellt</t>
+          <t>Foto der Autorin auf Anfrage.</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5561,17 +5573,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Biografie</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5585,17 +5597,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>Webbanner</t>
+          <t>Kurz</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5609,17 +5621,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.bios[0].text</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5633,17 +5645,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, quadratisch</t>
+          <t>Lang</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5657,17 +5669,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>Bibliografische Angaben</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5681,17 +5693,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, Hochformat</t>
+          <t>Titel</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5705,17 +5717,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5729,17 +5741,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, Querformat</t>
+          <t>Untertitel</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5753,17 +5765,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5777,17 +5789,17 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe, die ersten Seiten</t>
+          <t>Autorin</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
@@ -5801,17 +5813,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>PDF, vier Seiten</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5825,17 +5837,17 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.facts[3].label</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>Publisher</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin auf Anfrage.</t>
+          <t>Verlag</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
@@ -5849,17 +5861,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Budisin Publishing, Luxembourg</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Biografie</t>
+          <t>Budisin Publishing, Luxemburg</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5873,17 +5885,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Kurz</t>
+          <t>Erscheinungsjahr</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5897,17 +5909,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.facts[4].value</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5921,17 +5933,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Lang</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5945,17 +5957,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.facts[5].value</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Paperback, 6 × 9 in</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Bibliografische Angaben</t>
+          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -5969,17 +5981,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>Titel</t>
+          <t>Umfang</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -5993,17 +6005,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>278 pages</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>278 Seiten</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6017,17 +6029,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>Untertitel</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6041,17 +6053,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6065,17 +6077,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Autorin</t>
+          <t>Kategorie</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6089,17 +6101,17 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Psychologie / Kognitive Psychologie</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
@@ -6113,17 +6125,17 @@
       </c>
       <c r="B233" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C233" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D233" s="10" t="inlineStr">
         <is>
-          <t>Verlag</t>
+          <t>Sprache</t>
         </is>
       </c>
       <c r="E233" s="11" t="n"/>
@@ -6137,17 +6149,17 @@
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxemburg</t>
+          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6161,17 +6173,17 @@
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.facts[10].label</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>Erscheinungsjahr</t>
+          <t>Pflichtexemplar</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6185,17 +6197,17 @@
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.facts[10].value</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Ein CIP-Eintrag liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6209,17 +6221,17 @@
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Über das Buch</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
@@ -6233,17 +6245,17 @@
       </c>
       <c r="B238" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C238" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D238" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E238" s="11" t="n"/>
@@ -6257,23 +6269,23 @@
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>Umfang</t>
+          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
       <c r="F239" s="11" t="n"/>
     </row>
-    <row r="240" ht="30" customHeight="1">
+    <row r="240" ht="75" customHeight="1">
       <c r="A240" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -6281,17 +6293,17 @@
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.description[2]</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>278 Seiten</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6305,17 +6317,17 @@
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.description[3]</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
@@ -6329,17 +6341,17 @@
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.creditsHeading</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Mitwirkende</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
@@ -6353,17 +6365,17 @@
       </c>
       <c r="B243" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C243" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D243" s="10" t="inlineStr">
         <is>
-          <t>Kategorie</t>
+          <t>Umschlaggestaltung</t>
         </is>
       </c>
       <c r="E243" s="11" t="n"/>
@@ -6377,17 +6389,17 @@
       </c>
       <c r="B244" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C244" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D244" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Kognitive Psychologie</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E244" s="11" t="n"/>
@@ -6401,17 +6413,17 @@
       </c>
       <c r="B245" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].label</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C245" s="10" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D245" s="10" t="inlineStr">
         <is>
-          <t>Sprache</t>
+          <t>Buchgestaltung und Satz</t>
         </is>
       </c>
       <c r="E245" s="11" t="n"/>
@@ -6425,17 +6437,17 @@
       </c>
       <c r="B246" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C246" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D246" s="10" t="inlineStr">
         <is>
-          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E246" s="11" t="n"/>
@@ -6449,17 +6461,17 @@
       </c>
       <c r="B247" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C247" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D247" s="10" t="inlineStr">
         <is>
-          <t>Pflichtexemplar</t>
+          <t>Erschienen bei</t>
         </is>
       </c>
       <c r="E247" s="11" t="n"/>
@@ -6473,17 +6485,17 @@
       </c>
       <c r="B248" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>press.credits[2].value</t>
         </is>
       </c>
       <c r="C248" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="D248" s="10" t="inlineStr">
         <is>
-          <t>Ein CIP-Eintrag liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="E248" s="11" t="n"/>
@@ -6497,65 +6509,53 @@
       </c>
       <c r="B249" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>press.back</t>
         </is>
       </c>
       <c r="C249" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D249" s="10" t="inlineStr">
         <is>
-          <t>Über das Buch</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E249" s="11" t="n"/>
       <c r="F249" s="11" t="n"/>
     </row>
-    <row r="250" ht="135" customHeight="1">
-      <c r="A250" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B250" s="9" t="inlineStr">
-        <is>
-          <t>press.description[0]</t>
-        </is>
-      </c>
-      <c r="C250" s="10" t="inlineStr">
-        <is>
-          <t>Over sixteen days, Katrin moves through ordinary situations in which her first reading of what is happening is not always the one that survives a closer look. Each chapter follows one of those moments into the psychology underneath it, from attention and prediction to memory, threat, uncertainty and social inference. The book does not promise better instincts. It asks what becomes possible when we learn where our first reading came from.</t>
-        </is>
-      </c>
-      <c r="D250" s="10" t="inlineStr">
-        <is>
-          <t>Sechzehn Tage lang geht Katrin durch alltägliche Situationen, in denen ihr erster Befund nicht immer der ist, der einem genaueren Blick standhält. Jedes Kapitel verfolgt einen dieser Momente in die Psychologie dahinter, von Aufmerksamkeit und Vorhersage über Gedächtnis, Bedrohung und Ungewissheit bis hin zu den Schlüssen, die wir über andere Menschen ziehen. Das Buch verspricht keine besseren Instinkte. Es fragt, was möglich wird, wenn wir lernen, woher unser erster Befund kam.</t>
-        </is>
-      </c>
-      <c r="E250" s="11" t="n"/>
-      <c r="F250" s="11" t="n"/>
+    <row r="250" ht="22" customHeight="1">
+      <c r="A250" s="7" t="inlineStr">
+        <is>
+          <t>FOOT OF EVERY PAGE</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="n"/>
+      <c r="C250" s="8" t="n"/>
+      <c r="D250" s="8" t="n"/>
+      <c r="E250" s="8" t="n"/>
+      <c r="F250" s="8" t="n"/>
     </row>
     <row r="251" ht="30" customHeight="1">
       <c r="A251" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B251" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C251" s="10" t="inlineStr">
         <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D251" s="10" t="inlineStr">
         <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
+          <t>Bevor Sie der Geschichte glauben.</t>
         </is>
       </c>
       <c r="E251" s="11" t="n"/>
@@ -6564,46 +6564,46 @@
     <row r="252" ht="30" customHeight="1">
       <c r="A252" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B252" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>footer.method[0]</t>
         </is>
       </c>
       <c r="C252" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Read the dashboard.</t>
         </is>
       </c>
       <c r="D252" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Lesen Sie die Instrumente ab.</t>
         </is>
       </c>
       <c r="E252" s="11" t="n"/>
       <c r="F252" s="11" t="n"/>
     </row>
-    <row r="253" ht="75" customHeight="1">
+    <row r="253" ht="30" customHeight="1">
       <c r="A253" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B253" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>footer.method[1]</t>
         </is>
       </c>
       <c r="C253" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>Delay the story.</t>
         </is>
       </c>
       <c r="D253" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
+          <t>Lassen Sie die Geschichte warten.</t>
         </is>
       </c>
       <c r="E253" s="11" t="n"/>
@@ -6612,22 +6612,22 @@
     <row r="254" ht="30" customHeight="1">
       <c r="A254" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B254" s="9" t="inlineStr">
         <is>
-          <t>press.description[4]</t>
+          <t>footer.method[2]</t>
         </is>
       </c>
       <c r="C254" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Take the reading again.</t>
         </is>
       </c>
       <c r="D254" s="10" t="inlineStr">
         <is>
-          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
+          <t>Lesen Sie noch einmal ab.</t>
         </is>
       </c>
       <c r="E254" s="11" t="n"/>
@@ -6636,22 +6636,22 @@
     <row r="255" ht="30" customHeight="1">
       <c r="A255" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B255" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>footer.rights</t>
         </is>
       </c>
       <c r="C255" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="D255" s="10" t="inlineStr">
         <is>
-          <t>Mitwirkende</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="E255" s="11" t="n"/>
@@ -6660,22 +6660,22 @@
     <row r="256" ht="30" customHeight="1">
       <c r="A256" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B256" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].label</t>
+          <t>footer.pressLink</t>
         </is>
       </c>
       <c r="C256" s="10" t="inlineStr">
         <is>
-          <t>Cover design</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D256" s="10" t="inlineStr">
         <is>
-          <t>Umschlaggestaltung</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E256" s="11" t="n"/>
@@ -6684,22 +6684,22 @@
     <row r="257" ht="30" customHeight="1">
       <c r="A257" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B257" s="9" t="inlineStr">
         <is>
-          <t>press.credits[0].value</t>
+          <t>footer.contactLink</t>
         </is>
       </c>
       <c r="C257" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D257" s="10" t="inlineStr">
         <is>
-          <t>Zoe Larusson</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E257" s="11" t="n"/>
@@ -6708,70 +6708,58 @@
     <row r="258" ht="30" customHeight="1">
       <c r="A258" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B258" s="9" t="inlineStr">
         <is>
-          <t>press.credits[1].label</t>
+          <t>footer.madeLine</t>
         </is>
       </c>
       <c r="C258" s="10" t="inlineStr">
         <is>
-          <t>Book design and typesetting</t>
+          <t>Same life. Different instrument settings.</t>
         </is>
       </c>
       <c r="D258" s="10" t="inlineStr">
         <is>
-          <t>Buchgestaltung und Satz</t>
+          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
         </is>
       </c>
       <c r="E258" s="11" t="n"/>
       <c r="F258" s="11" t="n"/>
     </row>
-    <row r="259" ht="30" customHeight="1">
-      <c r="A259" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B259" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[1].value</t>
-        </is>
-      </c>
-      <c r="C259" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="D259" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="E259" s="11" t="n"/>
-      <c r="F259" s="11" t="n"/>
+    <row r="259" ht="22" customHeight="1">
+      <c r="A259" s="7" t="inlineStr">
+        <is>
+          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
+        </is>
+      </c>
+      <c r="B259" s="8" t="n"/>
+      <c r="C259" s="8" t="n"/>
+      <c r="D259" s="8" t="n"/>
+      <c r="E259" s="8" t="n"/>
+      <c r="F259" s="8" t="n"/>
     </row>
     <row r="260" ht="30" customHeight="1">
       <c r="A260" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B260" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].label</t>
+          <t>a11y.mainLandmark</t>
         </is>
       </c>
       <c r="C260" s="10" t="inlineStr">
         <is>
-          <t>Published by</t>
+          <t>Main content</t>
         </is>
       </c>
       <c r="D260" s="10" t="inlineStr">
         <is>
-          <t>Erschienen bei</t>
+          <t>Hauptinhalt</t>
         </is>
       </c>
       <c r="E260" s="11" t="n"/>
@@ -6780,22 +6768,22 @@
     <row r="261" ht="30" customHeight="1">
       <c r="A261" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B261" s="9" t="inlineStr">
         <is>
-          <t>press.credits[2].value</t>
+          <t>a11y.coverFigure</t>
         </is>
       </c>
       <c r="C261" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D261" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E261" s="11" t="n"/>
@@ -6804,58 +6792,70 @@
     <row r="262" ht="30" customHeight="1">
       <c r="A262" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B262" s="9" t="inlineStr">
         <is>
-          <t>press.back</t>
+          <t>a11y.languageSwitcher</t>
         </is>
       </c>
       <c r="C262" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Choose language</t>
         </is>
       </c>
       <c r="D262" s="10" t="inlineStr">
         <is>
-          <t>Zurück zum Buch</t>
+          <t>Sprache wählen</t>
         </is>
       </c>
       <c r="E262" s="11" t="n"/>
       <c r="F262" s="11" t="n"/>
     </row>
-    <row r="263" ht="22" customHeight="1">
-      <c r="A263" s="7" t="inlineStr">
-        <is>
-          <t>FOOT OF EVERY PAGE</t>
-        </is>
-      </c>
-      <c r="B263" s="8" t="n"/>
-      <c r="C263" s="8" t="n"/>
-      <c r="D263" s="8" t="n"/>
-      <c r="E263" s="8" t="n"/>
-      <c r="F263" s="8" t="n"/>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="9" t="inlineStr">
+        <is>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
+        </is>
+      </c>
+      <c r="B263" s="9" t="inlineStr">
+        <is>
+          <t>a11y.languageComing</t>
+        </is>
+      </c>
+      <c r="C263" s="10" t="inlineStr">
+        <is>
+          <t>edition to follow</t>
+        </is>
+      </c>
+      <c r="D263" s="10" t="inlineStr">
+        <is>
+          <t>Ausgabe folgt</t>
+        </is>
+      </c>
+      <c r="E263" s="11" t="n"/>
+      <c r="F263" s="11" t="n"/>
     </row>
     <row r="264" ht="30" customHeight="1">
       <c r="A264" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B264" s="9" t="inlineStr">
         <is>
-          <t>footer.band</t>
+          <t>a11y.casesRegion</t>
         </is>
       </c>
       <c r="C264" s="10" t="inlineStr">
         <is>
-          <t>Before you believe the story.</t>
+          <t>Case evidence pages from the book</t>
         </is>
       </c>
       <c r="D264" s="10" t="inlineStr">
         <is>
-          <t>Bevor Sie der Geschichte glauben.</t>
+          <t>Seiten mit Beweismaterial aus dem Buch</t>
         </is>
       </c>
       <c r="E264" s="11" t="n"/>
@@ -6864,22 +6864,22 @@
     <row r="265" ht="30" customHeight="1">
       <c r="A265" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B265" s="9" t="inlineStr">
         <is>
-          <t>footer.method[0]</t>
+          <t>a11y.bookOpening</t>
         </is>
       </c>
       <c r="C265" s="10" t="inlineStr">
         <is>
-          <t>Read the dashboard.</t>
+          <t>The book, opening</t>
         </is>
       </c>
       <c r="D265" s="10" t="inlineStr">
         <is>
-          <t>Lesen Sie die Instrumente ab.</t>
+          <t>Das Buch beim Aufschlagen</t>
         </is>
       </c>
       <c r="E265" s="11" t="n"/>
@@ -6888,22 +6888,22 @@
     <row r="266" ht="30" customHeight="1">
       <c r="A266" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B266" s="9" t="inlineStr">
         <is>
-          <t>footer.method[1]</t>
+          <t>a11y.misreadingRegion</t>
         </is>
       </c>
       <c r="C266" s="10" t="inlineStr">
         <is>
-          <t>Delay the story.</t>
+          <t>Page 10 of the book</t>
         </is>
       </c>
       <c r="D266" s="10" t="inlineStr">
         <is>
-          <t>Lassen Sie die Geschichte warten.</t>
+          <t>Seite 10 des Buches</t>
         </is>
       </c>
       <c r="E266" s="11" t="n"/>
@@ -6912,22 +6912,22 @@
     <row r="267" ht="30" customHeight="1">
       <c r="A267" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B267" s="9" t="inlineStr">
         <is>
-          <t>footer.method[2]</t>
+          <t>a11y.mapRegion</t>
         </is>
       </c>
       <c r="C267" s="10" t="inlineStr">
         <is>
-          <t>Take the reading again.</t>
+          <t>A map of the book</t>
         </is>
       </c>
       <c r="D267" s="10" t="inlineStr">
         <is>
-          <t>Lesen Sie noch einmal ab.</t>
+          <t>Eine Karte des Buches</t>
         </is>
       </c>
       <c r="E267" s="11" t="n"/>
@@ -6936,329 +6936,29 @@
     <row r="268" ht="30" customHeight="1">
       <c r="A268" s="9" t="inlineStr">
         <is>
-          <t>Foot of every page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B268" s="9" t="inlineStr">
         <is>
-          <t>footer.rights</t>
+          <t>a11y.evidenceRegion</t>
         </is>
       </c>
       <c r="C268" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Confidence markers, page 13</t>
         </is>
       </c>
       <c r="D268" s="10" t="inlineStr">
         <is>
-          <t>© 2026 Budisin Publishing</t>
+          <t>Markierungen zu den Belegen, Seite 13</t>
         </is>
       </c>
       <c r="E268" s="11" t="n"/>
       <c r="F268" s="11" t="n"/>
     </row>
-    <row r="269" ht="30" customHeight="1">
-      <c r="A269" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B269" s="9" t="inlineStr">
-        <is>
-          <t>footer.pressLink</t>
-        </is>
-      </c>
-      <c r="C269" s="10" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="D269" s="10" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="E269" s="11" t="n"/>
-      <c r="F269" s="11" t="n"/>
-    </row>
-    <row r="270" ht="30" customHeight="1">
-      <c r="A270" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B270" s="9" t="inlineStr">
-        <is>
-          <t>footer.contactLink</t>
-        </is>
-      </c>
-      <c r="C270" s="10" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D270" s="10" t="inlineStr">
-        <is>
-          <t>Kontakt</t>
-        </is>
-      </c>
-      <c r="E270" s="11" t="n"/>
-      <c r="F270" s="11" t="n"/>
-    </row>
-    <row r="271" ht="30" customHeight="1">
-      <c r="A271" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B271" s="9" t="inlineStr">
-        <is>
-          <t>footer.madeLine</t>
-        </is>
-      </c>
-      <c r="C271" s="10" t="inlineStr">
-        <is>
-          <t>Same life. Different instrument settings.</t>
-        </is>
-      </c>
-      <c r="D271" s="10" t="inlineStr">
-        <is>
-          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
-        </is>
-      </c>
-      <c r="E271" s="11" t="n"/>
-      <c r="F271" s="11" t="n"/>
-    </row>
-    <row r="272" ht="22" customHeight="1">
-      <c r="A272" s="7" t="inlineStr">
-        <is>
-          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
-        </is>
-      </c>
-      <c r="B272" s="8" t="n"/>
-      <c r="C272" s="8" t="n"/>
-      <c r="D272" s="8" t="n"/>
-      <c r="E272" s="8" t="n"/>
-      <c r="F272" s="8" t="n"/>
-    </row>
-    <row r="273" ht="30" customHeight="1">
-      <c r="A273" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B273" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mainLandmark</t>
-        </is>
-      </c>
-      <c r="C273" s="10" t="inlineStr">
-        <is>
-          <t>Main content</t>
-        </is>
-      </c>
-      <c r="D273" s="10" t="inlineStr">
-        <is>
-          <t>Hauptinhalt</t>
-        </is>
-      </c>
-      <c r="E273" s="11" t="n"/>
-      <c r="F273" s="11" t="n"/>
-    </row>
-    <row r="274" ht="30" customHeight="1">
-      <c r="A274" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B274" s="9" t="inlineStr">
-        <is>
-          <t>a11y.coverFigure</t>
-        </is>
-      </c>
-      <c r="C274" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D274" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch</t>
-        </is>
-      </c>
-      <c r="E274" s="11" t="n"/>
-      <c r="F274" s="11" t="n"/>
-    </row>
-    <row r="275" ht="30" customHeight="1">
-      <c r="A275" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B275" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageSwitcher</t>
-        </is>
-      </c>
-      <c r="C275" s="10" t="inlineStr">
-        <is>
-          <t>Choose language</t>
-        </is>
-      </c>
-      <c r="D275" s="10" t="inlineStr">
-        <is>
-          <t>Sprache wählen</t>
-        </is>
-      </c>
-      <c r="E275" s="11" t="n"/>
-      <c r="F275" s="11" t="n"/>
-    </row>
-    <row r="276" ht="30" customHeight="1">
-      <c r="A276" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B276" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageComing</t>
-        </is>
-      </c>
-      <c r="C276" s="10" t="inlineStr">
-        <is>
-          <t>edition to follow</t>
-        </is>
-      </c>
-      <c r="D276" s="10" t="inlineStr">
-        <is>
-          <t>Ausgabe folgt</t>
-        </is>
-      </c>
-      <c r="E276" s="11" t="n"/>
-      <c r="F276" s="11" t="n"/>
-    </row>
-    <row r="277" ht="30" customHeight="1">
-      <c r="A277" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B277" s="9" t="inlineStr">
-        <is>
-          <t>a11y.casesRegion</t>
-        </is>
-      </c>
-      <c r="C277" s="10" t="inlineStr">
-        <is>
-          <t>Case evidence pages from the book</t>
-        </is>
-      </c>
-      <c r="D277" s="10" t="inlineStr">
-        <is>
-          <t>Seiten mit Beweismaterial aus dem Buch</t>
-        </is>
-      </c>
-      <c r="E277" s="11" t="n"/>
-      <c r="F277" s="11" t="n"/>
-    </row>
-    <row r="278" ht="30" customHeight="1">
-      <c r="A278" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B278" s="9" t="inlineStr">
-        <is>
-          <t>a11y.bookOpening</t>
-        </is>
-      </c>
-      <c r="C278" s="10" t="inlineStr">
-        <is>
-          <t>The book, opening</t>
-        </is>
-      </c>
-      <c r="D278" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch beim Aufschlagen</t>
-        </is>
-      </c>
-      <c r="E278" s="11" t="n"/>
-      <c r="F278" s="11" t="n"/>
-    </row>
-    <row r="279" ht="30" customHeight="1">
-      <c r="A279" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B279" s="9" t="inlineStr">
-        <is>
-          <t>a11y.misreadingRegion</t>
-        </is>
-      </c>
-      <c r="C279" s="10" t="inlineStr">
-        <is>
-          <t>Page 10 of the book</t>
-        </is>
-      </c>
-      <c r="D279" s="10" t="inlineStr">
-        <is>
-          <t>Seite 10 des Buches</t>
-        </is>
-      </c>
-      <c r="E279" s="11" t="n"/>
-      <c r="F279" s="11" t="n"/>
-    </row>
-    <row r="280" ht="30" customHeight="1">
-      <c r="A280" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B280" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mapRegion</t>
-        </is>
-      </c>
-      <c r="C280" s="10" t="inlineStr">
-        <is>
-          <t>A map of the book</t>
-        </is>
-      </c>
-      <c r="D280" s="10" t="inlineStr">
-        <is>
-          <t>Eine Karte des Buches</t>
-        </is>
-      </c>
-      <c r="E280" s="11" t="n"/>
-      <c r="F280" s="11" t="n"/>
-    </row>
-    <row r="281" ht="30" customHeight="1">
-      <c r="A281" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B281" s="9" t="inlineStr">
-        <is>
-          <t>a11y.evidenceRegion</t>
-        </is>
-      </c>
-      <c r="C281" s="10" t="inlineStr">
-        <is>
-          <t>Confidence markers, page 13</t>
-        </is>
-      </c>
-      <c r="D281" s="10" t="inlineStr">
-        <is>
-          <t>Markierungen zu den Belegen, Seite 13</t>
-        </is>
-      </c>
-      <c r="E281" s="11" t="n"/>
-      <c r="F281" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F281"/>
+  <autoFilter ref="A1:F268"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/review/State-Not-Situation-German-review.xlsx
+++ b/review/State-Not-Situation-German-review.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="German review" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$268</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'German review'!$A$1:$F$242</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -710,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F268"/>
+  <dimension ref="A1:F242"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -813,7 +813,7 @@
       <c r="E4" s="11" t="n"/>
       <c r="F4" s="11" t="n"/>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="60" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Browser tab, Google result, link previews</t>
@@ -826,18 +826,18 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality. Sixteen cases. Three readings. One question: state or situation? By Ivana Budišin.</t>
+          <t>A field guide to the moment before interpretation becomes reality. Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr">
         <is>
-          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird. Sechzehn Fälle. Drei Befunde. Eine Frage: Zustand oder Situation? Von Ivana Budišin.</t>
+          <t>Ein Leitfaden für den Moment, bevor aus Deutung Wirklichkeit wird. Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E5" s="11" t="n"/>
       <c r="F5" s="11" t="n"/>
     </row>
-    <row r="6" ht="45" customHeight="1">
+    <row r="6" ht="30" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Browser tab, Google result, link previews</t>
@@ -850,12 +850,12 @@
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>The cover of State. Not Situation. by Ivana Budišin: the word STATE set large in red above NOT SITUATION in black, on cream.</t>
+          <t>State. Not Situation. by Ivana Budišin. A field guide to the moment before interpretation becomes reality.</t>
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr">
         <is>
-          <t>Das Cover von State. Not Situation. von Ivana Budišin: das Wort STATE groß in Rot über NOT SITUATION in Schwarz, auf Cremeweiß.</t>
+          <t>State. Not Situation. von Ivana Budišin. Ein Leitfaden für den Moment, bevor aus Deutung Wirklichkeit wird.</t>
         </is>
       </c>
       <c r="E6" s="11" t="n"/>
@@ -885,7 +885,7 @@
       <c r="E7" s="11" t="n"/>
       <c r="F7" s="11" t="n"/>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="30" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Browser tab, Google result, link previews</t>
@@ -898,12 +898,12 @@
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>The opening pages of State. Not Situation. by Ivana Budišin: a pilot, haze over open water, and one sentence from the Federal Aviation Administration.</t>
+          <t>The opening pages of State. Not Situation. by Ivana Budišin.</t>
         </is>
       </c>
       <c r="D8" s="10" t="inlineStr">
         <is>
-          <t>Die ersten Seiten von State. Not Situation. von Ivana Budišin: ein Pilot, Dunst über offenem Wasser und ein Satz der Federal Aviation Administration.</t>
+          <t>Die ersten Seiten von State. Not Situation. von Ivana Budišin.</t>
         </is>
       </c>
       <c r="E8" s="11" t="n"/>
@@ -933,7 +933,7 @@
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
     </row>
-    <row r="10" ht="45" customHeight="1">
+    <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Browser tab, Google result, link previews</t>
@@ -946,12 +946,12 @@
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Press materials for State. Not Situation. by Ivana Budišin: cover art, author photograph, biography, publication details and contact.</t>
+          <t>Press materials for State. Not Situation. by Ivana Budišin: cover, author photograph, publication details, extract.</t>
         </is>
       </c>
       <c r="D10" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial zu State. Not Situation. von Ivana Budišin: Cover, Foto der Autorin, Biografie, bibliografische Angaben und Kontakt.</t>
+          <t>Pressematerial zu State. Not Situation. von Ivana Budišin: Cover, Foto der Autorin, bibliografische Angaben, Leseprobe.</t>
         </is>
       </c>
       <c r="E10" s="11" t="n"/>
@@ -960,7 +960,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>TOP NAVIGATION BAR</t>
+          <t>TOP NAVIGATION BAR AND THE PHONE MENU</t>
         </is>
       </c>
       <c r="B11" s="8" t="n"/>
@@ -972,22 +972,22 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>nav.book</t>
+          <t>nav.home</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>State. Not Situation., home</t>
         </is>
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>Das Buch</t>
+          <t>State. Not Situation. Startseite</t>
         </is>
       </c>
       <c r="E12" s="11" t="n"/>
@@ -996,22 +996,22 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>nav.read</t>
+          <t>nav.book</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="D13" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E13" s="11" t="n"/>
@@ -1020,22 +1020,22 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>nav.listen</t>
+          <t>nav.read</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
         <is>
-          <t>Listen</t>
+          <t>Extract</t>
         </is>
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>Hören</t>
+          <t>Leseprobe</t>
         </is>
       </c>
       <c r="E14" s="11" t="n"/>
@@ -1044,7 +1044,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1068,7 +1068,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1092,22 +1092,22 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>nav.skipToContent</t>
+          <t>nav.listen</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
         <is>
-          <t>Skip to content</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>Zum Inhalt springen</t>
+          <t>Hören</t>
         </is>
       </c>
       <c r="E17" s="11" t="n"/>
@@ -1116,86 +1116,86 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Top navigation bar</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>nav.home</t>
+          <t>nav.skipToContent</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation. Home</t>
+          <t>Skip to content</t>
         </is>
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation. Startseite</t>
+          <t>Zum Inhalt springen</t>
         </is>
       </c>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="11" t="n"/>
     </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>PUBLICATION STATUS AND THE NOTIFY FORM</t>
-        </is>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Top navigation bar and the phone menu</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="inlineStr">
+        <is>
+          <t>nav.menu</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Menu</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Menü</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Publication status and the notify form</t>
+          <t>Top navigation bar and the phone menu</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>status.forthcoming</t>
+          <t>nav.closeMenu</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Publishing soon</t>
+          <t>Close</t>
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr">
         <is>
-          <t>Erscheint demnächst</t>
+          <t>Schließen</t>
         </is>
       </c>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="11" t="n"/>
     </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Publication status and the notify form</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>status.published</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Out now</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>Jetzt erhältlich</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="n"/>
-      <c r="F21" s="11" t="n"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>PUBLICATION STATUS AND THE NOTIFY FORM</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n"/>
+      <c r="C21" s="8" t="n"/>
+      <c r="D21" s="8" t="n"/>
+      <c r="E21" s="8" t="n"/>
+      <c r="F21" s="8" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="inlineStr">
@@ -1205,17 +1205,17 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>status.publicationDatePrefix</t>
+          <t>status.forthcoming</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Published</t>
+          <t>Publishing soon</t>
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr">
         <is>
-          <t>Erschienen</t>
+          <t>Erscheint demnächst</t>
         </is>
       </c>
       <c r="E22" s="11" t="n"/>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>status.buy</t>
+          <t>status.published</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>Buy on Amazon</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Bei Amazon kaufen</t>
+          <t>Jetzt erhältlich</t>
         </is>
       </c>
       <c r="E23" s="11" t="n"/>
@@ -1253,17 +1253,17 @@
       </c>
       <c r="B24" s="9" t="inlineStr">
         <is>
-          <t>status.notifyHeading</t>
+          <t>status.publicationDatePrefix</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
         <is>
-          <t>Be notified when the book is released.</t>
+          <t>Published</t>
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>Lassen Sie sich benachrichtigen, wenn das Buch erscheint.</t>
+          <t>Erschienen</t>
         </is>
       </c>
       <c r="E24" s="11" t="n"/>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="B25" s="9" t="inlineStr">
         <is>
-          <t>status.notifyCta</t>
+          <t>status.buy</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>Be notified</t>
+          <t>Buy on Amazon</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Benachrichtigen lassen</t>
+          <t>Bei Amazon kaufen</t>
         </is>
       </c>
       <c r="E25" s="11" t="n"/>
@@ -1301,17 +1301,17 @@
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>status.emailLabel</t>
+          <t>status.notifyCta</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>Email address</t>
+          <t>Publication updates</t>
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>E-Mail-Adresse</t>
+          <t>Nachricht zum Erscheinen</t>
         </is>
       </c>
       <c r="E26" s="11" t="n"/>
@@ -1325,17 +1325,17 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>status.emailPlaceholder</t>
+          <t>status.emailLabel</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>your@email.com</t>
+          <t>Email address</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>name@beispiel.de</t>
+          <t>E-Mail-Adresse</t>
         </is>
       </c>
       <c r="E27" s="11" t="n"/>
@@ -1349,17 +1349,17 @@
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>status.submit</t>
+          <t>status.emailPlaceholder</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
         <is>
-          <t>Notify me</t>
+          <t>your@email.com</t>
         </is>
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>Benachrichtigen</t>
+          <t>name@beispiel.de</t>
         </is>
       </c>
       <c r="E28" s="11" t="n"/>
@@ -1373,17 +1373,17 @@
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>status.success</t>
+          <t>status.submit</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>Thank you. You will hear from me when the book is out.</t>
+          <t>Notify me</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Danke. Sie hören von mir, sobald das Buch da ist.</t>
+          <t>Benachrichtigen</t>
         </is>
       </c>
       <c r="E29" s="11" t="n"/>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>status.error</t>
+          <t>status.success</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
         <is>
-          <t>That did not send. Please try again, or write to me directly.</t>
+          <t>Thank you. You will hear once, when the book is out.</t>
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr">
         <is>
-          <t>Das hat nicht geklappt. Bitte versuchen Sie es noch einmal oder schreiben Sie mir direkt.</t>
+          <t>Danke. Sie hören einmal von mir, wenn das Buch da ist.</t>
         </is>
       </c>
       <c r="E30" s="11" t="n"/>
@@ -1421,17 +1421,17 @@
       </c>
       <c r="B31" s="9" t="inlineStr">
         <is>
-          <t>status.privacyNote</t>
+          <t>status.error</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>Used for this notification only.</t>
+          <t>That did not send. Please try again, or email me directly.</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>Wird nur für diese Benachrichtigung verwendet.</t>
+          <t>Das hat nicht geklappt. Bitte versuchen Sie es noch einmal oder schreiben Sie mir direkt.</t>
         </is>
       </c>
       <c r="E31" s="11" t="n"/>
@@ -1445,17 +1445,17 @@
       </c>
       <c r="B32" s="9" t="inlineStr">
         <is>
-          <t>status.mailtoLabel</t>
+          <t>status.privacyNote</t>
         </is>
       </c>
       <c r="C32" s="10" t="inlineStr">
         <is>
-          <t>Email me to be notified</t>
+          <t>Used for this notification only.</t>
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>Per E-Mail benachrichtigen lassen</t>
+          <t>Wird nur für diese Benachrichtigung verwendet.</t>
         </is>
       </c>
       <c r="E32" s="11" t="n"/>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>Tell me when State. Not Situation. is out</t>
+          <t>State. Not Situation. — publication updates</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="C34" s="10" t="inlineStr">
         <is>
-          <t>Please let me know when State. Not Situation. is available.</t>
+          <t>Please let me know when the book is published.</t>
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>Bitte geben Sie mir Bescheid, wenn State. Not Situation. erhältlich ist.</t>
+          <t>Bitte geben Sie mir Bescheid, wenn das Buch erscheint.</t>
         </is>
       </c>
       <c r="E34" s="11" t="n"/>
@@ -1512,7 +1512,7 @@
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>FIRST SCREEN — THE BOOK AND TITLE</t>
+          <t>FIRST SCREEN — THE COVER AND THE TITLE</t>
         </is>
       </c>
       <c r="B35" s="8" t="n"/>
@@ -1524,22 +1524,22 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
         <is>
-          <t>hero.eyebrow</t>
+          <t>hero.titleA</t>
         </is>
       </c>
       <c r="C36" s="10" t="inlineStr">
         <is>
-          <t>Time · Attention · Safety</t>
+          <t>State.</t>
         </is>
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>Zeit · Aufmerksamkeit · Sicherheit</t>
+          <t>State.</t>
         </is>
       </c>
       <c r="E36" s="11" t="n"/>
@@ -1548,22 +1548,22 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
         <is>
-          <t>hero.titleA</t>
+          <t>hero.titleB</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>State.</t>
+          <t>Not Situation</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>State.</t>
+          <t>Not Situation</t>
         </is>
       </c>
       <c r="E37" s="11" t="n"/>
@@ -1572,22 +1572,22 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
         <is>
-          <t>hero.titleB</t>
+          <t>hero.subtitle</t>
         </is>
       </c>
       <c r="C38" s="10" t="inlineStr">
         <is>
-          <t>Not Situation</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>Not Situation</t>
+          <t>Ein Leitfaden für den Moment, bevor aus Deutung Wirklichkeit wird</t>
         </is>
       </c>
       <c r="E38" s="11" t="n"/>
@@ -1596,22 +1596,22 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
         <is>
-          <t>hero.subtitle</t>
+          <t>hero.strap</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Your first reading is not the whole story.</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
+          <t>Ihre erste Lesart ist nicht die ganze Geschichte.</t>
         </is>
       </c>
       <c r="E39" s="11" t="n"/>
@@ -1620,118 +1620,106 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
         <is>
-          <t>hero.strap</t>
+          <t>hero.authorPrefix</t>
         </is>
       </c>
       <c r="C40" s="10" t="inlineStr">
         <is>
-          <t>Your first reading is not the whole story.</t>
+          <t>by</t>
         </is>
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Ihr erster Befund ist nicht die ganze Geschichte.</t>
+          <t>von</t>
         </is>
       </c>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="11" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
         <is>
-          <t>hero.authorPrefix</t>
+          <t>hero.coverAlt</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>by</t>
+          <t>Front cover of State. Not Situation. The word STATE set large in red above NOT SITUATION in black, on a cream ground printed with faint struck-through sentences and small instrument readings.</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>von</t>
+          <t>Vorderseite des Covers von State. Not Situation. Das Wort STATE groß in Rot über NOT SITUATION in Schwarz, auf cremefarbenem Grund, bedruckt mit blassen, durchgestrichenen Sätzen und kleinen Instrumentenanzeigen.</t>
         </is>
       </c>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="11" t="n"/>
     </row>
-    <row r="42" ht="60" customHeight="1">
+    <row r="42" ht="30" customHeight="1">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>First screen — the cover and the title</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
         <is>
-          <t>hero.coverAlt</t>
+          <t>hero.readCta</t>
         </is>
       </c>
       <c r="C42" s="10" t="inlineStr">
         <is>
-          <t>Front cover of State. Not Situation. The word STATE set large in red above NOT SITUATION in black, on a cream ground printed with faint struck-through sentences and small instrument readings.</t>
+          <t>Read an extract</t>
         </is>
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Vorderseite des Covers von State. Not Situation. Das Wort STATE groß in Rot über NOT SITUATION in Schwarz, auf cremefarbenem Grund, bedruckt mit blassen, durchgestrichenen Sätzen und kleinen Instrumentenanzeigen.</t>
+          <t>Leseprobe lesen</t>
         </is>
       </c>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="11" t="n"/>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="9" t="inlineStr">
-        <is>
-          <t>First screen — the book and title</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>hero.openAlt</t>
-        </is>
-      </c>
-      <c r="C43" s="10" t="inlineStr">
-        <is>
-          <t>The book open at its title page, which reads State. Not Situation.</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch, aufgeschlagen auf der Titelseite, auf der State. Not Situation. steht.</t>
-        </is>
-      </c>
-      <c r="E43" s="11" t="n"/>
-      <c r="F43" s="11" t="n"/>
+    <row r="43" ht="22" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>THE PREMISE — PAGE 181, PAGE 10 AND THE BACK COVER</t>
+        </is>
+      </c>
+      <c r="B43" s="8" t="n"/>
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="8" t="n"/>
+      <c r="E43" s="8" t="n"/>
+      <c r="F43" s="8" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B44" s="9" t="inlineStr">
         <is>
-          <t>hero.readCta</t>
+          <t>premise.eyebrow</t>
         </is>
       </c>
       <c r="C44" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>The first misreading</t>
         </is>
       </c>
       <c r="D44" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe lesen</t>
+          <t>Die erste Fehldeutung</t>
         </is>
       </c>
       <c r="E44" s="11" t="n"/>
@@ -1740,58 +1728,70 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="9" t="inlineStr">
         <is>
-          <t>First screen — the book and title</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>hero.scrollHint</t>
+          <t>premise.sensorLine</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>Scroll</t>
+          <t>The body is a sensor before it is a narrator.</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Scrollen</t>
+          <t>Der Körper ist erst Sensor, dann Erzähler.</t>
         </is>
       </c>
       <c r="E45" s="11" t="n"/>
       <c r="F45" s="11" t="n"/>
     </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>“THE FIRST MISREADING” — PAGE 10, THE FIVE READINGS</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="n"/>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
+    <row r="46" ht="30" customHeight="1">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>The premise — page 181, page 10 and the back cover</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>premise.lines[0]</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>Nothing went wrong on this day.</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>An diesem Tag ging nichts schief.</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B47" s="9" t="inlineStr">
         <is>
-          <t>misreading.eyebrow</t>
+          <t>premise.lines[1]</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>The first misreading</t>
+          <t>The instruments were working.</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Die erste Fehldeutung</t>
+          <t>Die Instrumente funktionierten.</t>
         </is>
       </c>
       <c r="E47" s="11" t="n"/>
@@ -1800,22 +1800,22 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B48" s="9" t="inlineStr">
         <is>
-          <t>misreading.lines[0]</t>
+          <t>premise.lines[2]</t>
         </is>
       </c>
       <c r="C48" s="10" t="inlineStr">
         <is>
-          <t>Nothing went wrong on this day.</t>
+          <t>The data was there the whole time.</t>
         </is>
       </c>
       <c r="D48" s="10" t="inlineStr">
         <is>
-          <t>An diesem Tag ging nichts schief.</t>
+          <t>Die Daten waren die ganze Zeit da.</t>
         </is>
       </c>
       <c r="E48" s="11" t="n"/>
@@ -1824,22 +1824,22 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B49" s="9" t="inlineStr">
         <is>
-          <t>misreading.lines[1]</t>
+          <t>premise.mechanism[0]</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>The instruments were working.</t>
+          <t>We usually treat these moments as information about life: the person, the task, the relationship, the day.</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Die Instrumente funktionierten.</t>
+          <t>Normalerweise nehmen wir diese Momente als Auskunft über das Leben: die Person, die Aufgabe, die Beziehung, den Tag.</t>
         </is>
       </c>
       <c r="E49" s="11" t="n"/>
@@ -1848,46 +1848,46 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B50" s="9" t="inlineStr">
         <is>
-          <t>misreading.lines[2]</t>
+          <t>premise.mechanism[1]</t>
         </is>
       </c>
       <c r="C50" s="10" t="inlineStr">
         <is>
-          <t>The data was there the whole time.</t>
+          <t>But the first reading is often not the whole story.</t>
         </is>
       </c>
       <c r="D50" s="10" t="inlineStr">
         <is>
-          <t>Die Daten waren die ganze Zeit da.</t>
+          <t>Aber die erste Lesart ist oft nicht die ganze Geschichte.</t>
         </is>
       </c>
       <c r="E50" s="11" t="n"/>
       <c r="F50" s="11" t="n"/>
     </row>
-    <row r="51" ht="30" customHeight="1">
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B51" s="9" t="inlineStr">
         <is>
-          <t>misreading.investigationLabel</t>
+          <t>premise.mechanism[2]</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>This book is the</t>
+          <t>Before the mind explains, the body has already voted. Sleep pressure, hunger, timing, attention, threat detection, memory, and prediction quietly shape what feels true.</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Dieses Buch ist die</t>
+          <t>Bevor der Kopf erklärt, hat der Körper schon abgestimmt. Schlafdruck, Hunger, Timing, Aufmerksamkeit, Bedrohungserkennung, Gedächtnis und Vorhersage prägen unbemerkt, was sich wahr anfühlt.</t>
         </is>
       </c>
       <c r="E51" s="11" t="n"/>
@@ -1896,22 +1896,22 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B52" s="9" t="inlineStr">
         <is>
-          <t>misreading.investigation</t>
+          <t>premise.mechanism[3]</t>
         </is>
       </c>
       <c r="C52" s="10" t="inlineStr">
         <is>
-          <t>Investigation.</t>
+          <t>Then the mind arrives second and gives that feeling a reason.</t>
         </is>
       </c>
       <c r="D52" s="10" t="inlineStr">
         <is>
-          <t>Untersuchung.</t>
+          <t>Dann kommt der Kopf als Zweiter und liefert dem Gefühl einen Grund.</t>
         </is>
       </c>
       <c r="E52" s="11" t="n"/>
@@ -1920,70 +1920,58 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>The premise — page 181, page 10 and the back cover</t>
         </is>
       </c>
       <c r="B53" s="9" t="inlineStr">
         <is>
-          <t>misreading.readingsLabel</t>
+          <t>premise.folio</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>The same day, five readings</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Derselbe Tag, fünf Befunde</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E53" s="11" t="n"/>
       <c r="F53" s="11" t="n"/>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="9" t="inlineStr">
-        <is>
-          <t>“The first misreading” — page 10, the five readings</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>misreading.readings[0].text</t>
-        </is>
-      </c>
-      <c r="C54" s="10" t="inlineStr">
-        <is>
-          <t>A heaviness arrives before the day does.</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>Eine Schwere ist da, bevor der Tag da ist.</t>
-        </is>
-      </c>
-      <c r="E54" s="11" t="n"/>
-      <c r="F54" s="11" t="n"/>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="n"/>
+      <c r="C54" s="8" t="n"/>
+      <c r="D54" s="8" t="n"/>
+      <c r="E54" s="8" t="n"/>
+      <c r="F54" s="8" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B55" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[1].text</t>
+          <t>reading.eyebrow</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>A two-line email reads like a verdict.</t>
+          <t>Try something right now</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Eine zweizeilige E-Mail liest sich wie ein Urteil.</t>
+          <t>Probieren Sie jetzt gleich etwas aus</t>
         </is>
       </c>
       <c r="E55" s="11" t="n"/>
@@ -1992,22 +1980,22 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B56" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[2].text</t>
+          <t>reading.lead</t>
         </is>
       </c>
       <c r="C56" s="10" t="inlineStr">
         <is>
-          <t>Five neutral words tighten a jaw.</t>
+          <t>Whatever you are feeling as you read this sentence.</t>
         </is>
       </c>
       <c r="D56" s="10" t="inlineStr">
         <is>
-          <t>Fünf neutrale Wörter spannen einen Kiefer an.</t>
+          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
         </is>
       </c>
       <c r="E56" s="11" t="n"/>
@@ -2016,22 +2004,22 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B57" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[3].text</t>
+          <t>reading.steps[0]</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>An unanswered message starts charging rent.</t>
+          <t>Check your jaw.</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Eine unbeantwortete Nachricht fängt an, Miete zu verlangen.</t>
+          <t>Spüren Sie Ihren Kiefer.</t>
         </is>
       </c>
       <c r="E57" s="11" t="n"/>
@@ -2040,22 +2028,22 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B58" s="9" t="inlineStr">
         <is>
-          <t>misreading.readings[4].text</t>
+          <t>reading.steps[1]</t>
         </is>
       </c>
       <c r="C58" s="10" t="inlineStr">
         <is>
-          <t>Two letters and a full stop feel hostile.</t>
+          <t>Check your breath.</t>
         </is>
       </c>
       <c r="D58" s="10" t="inlineStr">
         <is>
-          <t>Zwei Buchstaben und ein Punkt fühlen sich feindselig an.</t>
+          <t>Spüren Sie Ihren Atem.</t>
         </is>
       </c>
       <c r="E58" s="11" t="n"/>
@@ -2064,22 +2052,22 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B59" s="9" t="inlineStr">
         <is>
-          <t>misreading.closing[0]</t>
+          <t>reading.steps[2]</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>The body speaks first.</t>
+          <t>Check your shoulders.</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Der Körper spricht zuerst.</t>
+          <t>Spüren Sie Ihre Schultern.</t>
         </is>
       </c>
       <c r="E59" s="11" t="n"/>
@@ -2088,82 +2076,82 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="9" t="inlineStr">
         <is>
-          <t>“The first misreading” — page 10, the five readings</t>
+          <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
       <c r="B60" s="9" t="inlineStr">
         <is>
-          <t>misreading.closing[1]</t>
+          <t>reading.result</t>
         </is>
       </c>
       <c r="C60" s="10" t="inlineStr">
         <is>
-          <t>The mind explains second.</t>
+          <t>What you found is a reading.</t>
         </is>
       </c>
       <c r="D60" s="10" t="inlineStr">
         <is>
-          <t>Der Kopf erklärt danach.</t>
+          <t>Was Sie gefunden haben, ist ein Befund.</t>
         </is>
       </c>
       <c r="E60" s="11" t="n"/>
       <c r="F60" s="11" t="n"/>
     </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="7" t="inlineStr">
-        <is>
-          <t>“TRY SOMETHING RIGHT NOW” — THE THREE INSTRUCTIONS, PAGE 13</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="n"/>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-    </row>
-    <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="9" t="inlineStr">
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="9" t="inlineStr">
         <is>
           <t>“Try something right now” — the three instructions, page 13</t>
         </is>
       </c>
-      <c r="B62" s="9" t="inlineStr">
-        <is>
-          <t>reading.eyebrow</t>
-        </is>
-      </c>
-      <c r="C62" s="10" t="inlineStr">
-        <is>
-          <t>Try something right now</t>
-        </is>
-      </c>
-      <c r="D62" s="10" t="inlineStr">
-        <is>
-          <t>Probieren Sie jetzt gleich etwas aus</t>
-        </is>
-      </c>
-      <c r="E62" s="11" t="n"/>
-      <c r="F62" s="11" t="n"/>
+      <c r="B61" s="9" t="inlineStr">
+        <is>
+          <t>reading.folio</t>
+        </is>
+      </c>
+      <c r="C61" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D61" s="10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n"/>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>TIME. ATTENTION. SAFETY. — THE THREE VARIABLES</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="n"/>
+      <c r="C62" s="8" t="n"/>
+      <c r="D62" s="8" t="n"/>
+      <c r="E62" s="8" t="n"/>
+      <c r="F62" s="8" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B63" s="9" t="inlineStr">
         <is>
-          <t>reading.lead</t>
+          <t>variables.sortingLines[0]</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>Whatever you are feeling as you read this sentence.</t>
+          <t>They are not brain regions or neural pathways.</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Was auch immer Sie gerade fühlen, während Sie diesen Satz lesen.</t>
+          <t>Das sind keine Hirnregionen und keine Nervenbahnen.</t>
         </is>
       </c>
       <c r="E63" s="11" t="n"/>
@@ -2172,22 +2160,22 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B64" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[0]</t>
+          <t>variables.sortingLines[1]</t>
         </is>
       </c>
       <c r="C64" s="10" t="inlineStr">
         <is>
-          <t>Check your jaw.</t>
+          <t>They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D64" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihren Kiefer.</t>
+          <t>Das ist ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
         </is>
       </c>
       <c r="E64" s="11" t="n"/>
@@ -2196,46 +2184,46 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B65" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[1]</t>
+          <t>variables.loops[0].name</t>
         </is>
       </c>
       <c r="C65" s="10" t="inlineStr">
         <is>
-          <t>Check your breath.</t>
+          <t>Time</t>
         </is>
       </c>
       <c r="D65" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihren Atem.</t>
+          <t>Zeit</t>
         </is>
       </c>
       <c r="E65" s="11" t="n"/>
       <c r="F65" s="11" t="n"/>
     </row>
-    <row r="66" ht="30" customHeight="1">
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B66" s="9" t="inlineStr">
         <is>
-          <t>reading.steps[2]</t>
+          <t>variables.loops[0].body</t>
         </is>
       </c>
       <c r="C66" s="10" t="inlineStr">
         <is>
-          <t>Check your shoulders.</t>
+          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
         </is>
       </c>
       <c r="D66" s="10" t="inlineStr">
         <is>
-          <t>Spüren Sie Ihre Schultern.</t>
+          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
         </is>
       </c>
       <c r="E66" s="11" t="n"/>
@@ -2244,22 +2232,22 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B67" s="9" t="inlineStr">
         <is>
-          <t>reading.result</t>
+          <t>variables.loops[1].name</t>
         </is>
       </c>
       <c r="C67" s="10" t="inlineStr">
         <is>
-          <t>What you found is a reading.</t>
+          <t>Attention</t>
         </is>
       </c>
       <c r="D67" s="10" t="inlineStr">
         <is>
-          <t>Was Sie gefunden haben, ist ein Befund.</t>
+          <t>Aufmerksamkeit</t>
         </is>
       </c>
       <c r="E67" s="11" t="n"/>
@@ -2268,22 +2256,22 @@
     <row r="68" ht="60" customHeight="1">
       <c r="A68" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B68" s="9" t="inlineStr">
         <is>
-          <t>reading.afterResult</t>
+          <t>variables.loops[1].body</t>
         </is>
       </c>
       <c r="C68" s="10" t="inlineStr">
         <is>
-          <t>A reading of the instrument that is interpreting everything around you, in this moment, including these words. The reading may be accurate. It may not. You cannot know until you have seen the settings.</t>
+          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
         </is>
       </c>
       <c r="D68" s="10" t="inlineStr">
         <is>
-          <t>Ein Befund, abgelesen an dem Instrument, das in diesem Moment alles um Sie herum deutet, auch diese Worte. Der Befund kann stimmen. Oder auch nicht. Das können Sie nicht wissen, bevor Sie die Einstellungen gesehen haben.</t>
+          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf den Reiz, der am wenigsten Aufwand verlangt, und anspruchsvollere Arbeit fühlt sich schwer an.</t>
         </is>
       </c>
       <c r="E68" s="11" t="n"/>
@@ -2292,166 +2280,178 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="9" t="inlineStr">
         <is>
-          <t>“Try something right now” — the three instructions, page 13</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B69" s="9" t="inlineStr">
         <is>
-          <t>reading.question</t>
+          <t>variables.loops[2].name</t>
         </is>
       </c>
       <c r="C69" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this the state?</t>
+          <t>Safety</t>
         </is>
       </c>
       <c r="D69" s="10" t="inlineStr">
         <is>
-          <t>Ist das die Situation? Oder ist das der Zustand?</t>
+          <t>Sicherheit</t>
         </is>
       </c>
       <c r="E69" s="11" t="n"/>
       <c r="F69" s="11" t="n"/>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK — THE AUTHOR’S LINE, WHO IT IS FOR</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="n"/>
-      <c r="C70" s="8" t="n"/>
-      <c r="D70" s="8" t="n"/>
-      <c r="E70" s="8" t="n"/>
-      <c r="F70" s="8" t="n"/>
+    <row r="70" ht="60" customHeight="1">
+      <c r="A70" s="9" t="inlineStr">
+        <is>
+          <t>Time. Attention. Safety. — the three variables</t>
+        </is>
+      </c>
+      <c r="B70" s="9" t="inlineStr">
+        <is>
+          <t>variables.loops[2].body</t>
+        </is>
+      </c>
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>The system that monitors threat, and especially social threat. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="n"/>
+      <c r="F70" s="11" t="n"/>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="9" t="inlineStr">
         <is>
-          <t>The book — the author’s line, who it is for</t>
+          <t>Time. Attention. Safety. — the three variables</t>
         </is>
       </c>
       <c r="B71" s="9" t="inlineStr">
         <is>
-          <t>book.eyebrow</t>
+          <t>variables.folio</t>
         </is>
       </c>
       <c r="C71" s="10" t="inlineStr">
         <is>
-          <t>The book</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D71" s="10" t="inlineStr">
         <is>
-          <t>Das Buch</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E71" s="11" t="n"/>
       <c r="F71" s="11" t="n"/>
     </row>
-    <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="9" t="inlineStr">
-        <is>
-          <t>The book — the author’s line, who it is for</t>
-        </is>
-      </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>book.paragraphs[0]</t>
-        </is>
-      </c>
-      <c r="C72" s="10" t="inlineStr">
-        <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="n"/>
-      <c r="F72" s="11" t="n"/>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>THREE MOMENTS — THE PRINTED CASE PAGES</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="n"/>
+      <c r="C72" s="8" t="n"/>
+      <c r="D72" s="8" t="n"/>
+      <c r="E72" s="8" t="n"/>
+      <c r="F72" s="8" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="9" t="inlineStr">
         <is>
-          <t>The book — the author’s line, who it is for</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B73" s="9" t="inlineStr">
         <is>
-          <t>book.readersEyebrow</t>
+          <t>moments.line</t>
         </is>
       </c>
       <c r="C73" s="10" t="inlineStr">
         <is>
-          <t>Who it is for</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D73" s="10" t="inlineStr">
         <is>
-          <t>Für wen es ist</t>
+          <t>16 Fälle. Drei Lesarten. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E73" s="11" t="n"/>
       <c r="F73" s="11" t="n"/>
     </row>
-    <row r="74" ht="75" customHeight="1">
+    <row r="74" ht="30" customHeight="1">
       <c r="A74" s="9" t="inlineStr">
         <is>
-          <t>The book — the author’s line, who it is for</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B74" s="9" t="inlineStr">
         <is>
-          <t>book.readers</t>
+          <t>moments.label</t>
         </is>
       </c>
       <c r="C74" s="10" t="inlineStr">
         <is>
-          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
+          <t>Case evidence</t>
         </is>
       </c>
       <c r="D74" s="10" t="inlineStr">
         <is>
-          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
+          <t>Beweismaterial</t>
         </is>
       </c>
       <c r="E74" s="11" t="n"/>
       <c r="F74" s="11" t="n"/>
     </row>
-    <row r="75" ht="22" customHeight="1">
-      <c r="A75" s="7" t="inlineStr">
-        <is>
-          <t>THE EXTRACT — OPENING PAGES OF THE BOOK, AND THE PAGE 26 LINE</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="n"/>
-      <c r="C75" s="8" t="n"/>
-      <c r="D75" s="8" t="n"/>
-      <c r="E75" s="8" t="n"/>
-      <c r="F75" s="8" t="n"/>
+    <row r="75" ht="30" customHeight="1">
+      <c r="A75" s="9" t="inlineStr">
+        <is>
+          <t>Three moments — the printed case pages</t>
+        </is>
+      </c>
+      <c r="B75" s="9" t="inlineStr">
+        <is>
+          <t>moments.pageLabel</t>
+        </is>
+      </c>
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>Page</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>Seite</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B76" s="9" t="inlineStr">
         <is>
-          <t>excerpt.eyebrow</t>
+          <t>moments.items[0].quote</t>
         </is>
       </c>
       <c r="C76" s="10" t="inlineStr">
         <is>
-          <t>Read</t>
+          <t>“Something is off.”</t>
         </is>
       </c>
       <c r="D76" s="10" t="inlineStr">
         <is>
-          <t>Lesen</t>
+          <t>„Irgendetwas stimmt nicht.“</t>
         </is>
       </c>
       <c r="E76" s="11" t="n"/>
@@ -2460,22 +2460,22 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B77" s="9" t="inlineStr">
         <is>
-          <t>excerpt.title</t>
+          <t>moments.items[0].inputLabel</t>
         </is>
       </c>
       <c r="C77" s="10" t="inlineStr">
         <is>
-          <t>Before the chapters</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D77" s="10" t="inlineStr">
         <is>
-          <t>Vor den Kapiteln</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E77" s="11" t="n"/>
@@ -2484,22 +2484,22 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B78" s="9" t="inlineStr">
         <is>
-          <t>excerpt.sectionLabel</t>
+          <t>moments.items[0].input</t>
         </is>
       </c>
       <c r="C78" s="10" t="inlineStr">
         <is>
-          <t>The pilot</t>
+          <t>Two minutes before the alarm.</t>
         </is>
       </c>
       <c r="D78" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot</t>
+          <t>Zwei Minuten vor dem Wecker.</t>
         </is>
       </c>
       <c r="E78" s="11" t="n"/>
@@ -2508,22 +2508,22 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B79" s="9" t="inlineStr">
         <is>
-          <t>excerpt.runningHead</t>
+          <t>moments.items[0].verifiedLabel</t>
         </is>
       </c>
       <c r="C79" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Verified event</t>
         </is>
       </c>
       <c r="D79" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation</t>
+          <t>Bestätigtes Ereignis</t>
         </is>
       </c>
       <c r="E79" s="11" t="n"/>
@@ -2532,22 +2532,22 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B80" s="9" t="inlineStr">
         <is>
-          <t>excerpt.cta</t>
+          <t>moments.items[0].verified</t>
         </is>
       </c>
       <c r="C80" s="10" t="inlineStr">
         <is>
-          <t>Read an extract</t>
+          <t>Nothing has happened.</t>
         </is>
       </c>
       <c r="D80" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe lesen</t>
+          <t>Nichts ist passiert.</t>
         </is>
       </c>
       <c r="E80" s="11" t="n"/>
@@ -2556,22 +2556,22 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>excerpt.continueCta</t>
+          <t>moments.items[1].quote</t>
         </is>
       </c>
       <c r="C81" s="10" t="inlineStr">
         <is>
-          <t>Continue reading</t>
+          <t>“ok.”</t>
         </is>
       </c>
       <c r="D81" s="10" t="inlineStr">
         <is>
-          <t>Weiterlesen</t>
+          <t>„ok.“</t>
         </is>
       </c>
       <c r="E81" s="11" t="n"/>
@@ -2580,22 +2580,22 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>excerpt.back</t>
+          <t>moments.items[1].inputLabel</t>
         </is>
       </c>
       <c r="C82" s="10" t="inlineStr">
         <is>
-          <t>Back to the book</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D82" s="10" t="inlineStr">
         <is>
-          <t>Zurück zum Buch</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E82" s="11" t="n"/>
@@ -2604,214 +2604,214 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>excerpt.readingModeLabel</t>
+          <t>moments.items[1].input</t>
         </is>
       </c>
       <c r="C83" s="10" t="inlineStr">
         <is>
-          <t>Reading mode</t>
+          <t>Two letters. One full stop.</t>
         </is>
       </c>
       <c r="D83" s="10" t="inlineStr">
         <is>
-          <t>Lesemodus</t>
+          <t>Zwei Buchstaben. Ein Punkt.</t>
         </is>
       </c>
       <c r="E83" s="11" t="n"/>
       <c r="F83" s="11" t="n"/>
     </row>
-    <row r="84" ht="105" customHeight="1">
+    <row r="84" ht="30" customHeight="1">
       <c r="A84" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[0]</t>
+          <t>moments.items[1].verifiedLabel</t>
         </is>
       </c>
       <c r="C84" s="10" t="inlineStr">
         <is>
-          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
+          <t>Verified tone</t>
         </is>
       </c>
       <c r="D84" s="10" t="inlineStr">
         <is>
-          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
+          <t>Bestätigter Tonfall</t>
         </is>
       </c>
       <c r="E84" s="11" t="n"/>
       <c r="F84" s="11" t="n"/>
     </row>
-    <row r="85" ht="210" customHeight="1">
+    <row r="85" ht="30" customHeight="1">
       <c r="A85" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[1]</t>
+          <t>moments.items[1].verified</t>
         </is>
       </c>
       <c r="C85" s="10" t="inlineStr">
         <is>
-          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D85" s="10" t="inlineStr">
         <is>
-          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
+          <t>Keiner.</t>
         </is>
       </c>
       <c r="E85" s="11" t="n"/>
       <c r="F85" s="11" t="n"/>
     </row>
-    <row r="86" ht="150" customHeight="1">
+    <row r="86" ht="30" customHeight="1">
       <c r="A86" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[2]</t>
+          <t>moments.items[2].quote</t>
         </is>
       </c>
       <c r="C86" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
+          <t>“Something is wrong with my life.”</t>
         </is>
       </c>
       <c r="D86" s="10" t="inlineStr">
         <is>
-          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
+          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
         </is>
       </c>
       <c r="E86" s="11" t="n"/>
       <c r="F86" s="11" t="n"/>
     </row>
-    <row r="87" ht="165" customHeight="1">
+    <row r="87" ht="30" customHeight="1">
       <c r="A87" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B87" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[3]</t>
+          <t>moments.items[2].inputLabel</t>
         </is>
       </c>
       <c r="C87" s="10" t="inlineStr">
         <is>
-          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="D87" s="10" t="inlineStr">
         <is>
-          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
+          <t>Input</t>
         </is>
       </c>
       <c r="E87" s="11" t="n"/>
       <c r="F87" s="11" t="n"/>
     </row>
-    <row r="88" ht="120" customHeight="1">
+    <row r="88" ht="30" customHeight="1">
       <c r="A88" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B88" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[4]</t>
+          <t>moments.items[2].input</t>
         </is>
       </c>
       <c r="C88" s="10" t="inlineStr">
         <is>
-          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
+          <t>Six ordinary events. One depleted day.</t>
         </is>
       </c>
       <c r="D88" s="10" t="inlineStr">
         <is>
-          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
+          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
         </is>
       </c>
       <c r="E88" s="11" t="n"/>
       <c r="F88" s="11" t="n"/>
     </row>
-    <row r="89" ht="135" customHeight="1">
+    <row r="89" ht="30" customHeight="1">
       <c r="A89" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B89" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[5]</t>
+          <t>moments.items[2].verifiedLabel</t>
         </is>
       </c>
       <c r="C89" s="10" t="inlineStr">
         <is>
-          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
+          <t>Verified crisis</t>
         </is>
       </c>
       <c r="D89" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
+          <t>Bestätigte Krise</t>
         </is>
       </c>
       <c r="E89" s="11" t="n"/>
       <c r="F89" s="11" t="n"/>
     </row>
-    <row r="90" ht="75" customHeight="1">
+    <row r="90" ht="30" customHeight="1">
       <c r="A90" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B90" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[6]</t>
+          <t>moments.items[2].verified</t>
         </is>
       </c>
       <c r="C90" s="10" t="inlineStr">
         <is>
-          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
+          <t>None.</t>
         </is>
       </c>
       <c r="D90" s="10" t="inlineStr">
         <is>
-          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
+          <t>Keine.</t>
         </is>
       </c>
       <c r="E90" s="11" t="n"/>
       <c r="F90" s="11" t="n"/>
     </row>
-    <row r="91" ht="240" customHeight="1">
+    <row r="91" ht="30" customHeight="1">
       <c r="A91" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B91" s="9" t="inlineStr">
         <is>
-          <t>excerpt.paragraphs[7]</t>
+          <t>moments.closing</t>
         </is>
       </c>
       <c r="C91" s="10" t="inlineStr">
         <is>
-          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
+          <t>It said I am failing; the data was I am tired.</t>
         </is>
       </c>
       <c r="D91" s="10" t="inlineStr">
         <is>
-          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
+          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
         </is>
       </c>
       <c r="E91" s="11" t="n"/>
@@ -2820,70 +2820,58 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Three moments — the printed case pages</t>
         </is>
       </c>
       <c r="B92" s="9" t="inlineStr">
         <is>
-          <t>excerpt.quote</t>
+          <t>moments.closingSource</t>
         </is>
       </c>
       <c r="C92" s="10" t="inlineStr">
         <is>
-          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
+          <t>Page 20</t>
         </is>
       </c>
       <c r="D92" s="10" t="inlineStr">
         <is>
-          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
+          <t>Seite 20</t>
         </is>
       </c>
       <c r="E92" s="11" t="n"/>
       <c r="F92" s="11" t="n"/>
     </row>
-    <row r="93" ht="135" customHeight="1">
-      <c r="A93" s="9" t="inlineStr">
-        <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
-        </is>
-      </c>
-      <c r="B93" s="9" t="inlineStr">
-        <is>
-          <t>excerpt.closing</t>
-        </is>
-      </c>
-      <c r="C93" s="10" t="inlineStr">
-        <is>
-          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
-        </is>
-      </c>
-      <c r="D93" s="10" t="inlineStr">
-        <is>
-          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
-        </is>
-      </c>
-      <c r="E93" s="11" t="n"/>
-      <c r="F93" s="11" t="n"/>
+    <row r="93" ht="22" customHeight="1">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>EVIDENCE — THE BOOK'S CONFIDENCE MARKERS</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n"/>
+      <c r="C93" s="8" t="n"/>
+      <c r="D93" s="8" t="n"/>
+      <c r="E93" s="8" t="n"/>
+      <c r="F93" s="8" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B94" s="9" t="inlineStr">
         <is>
-          <t>excerpt.closingSource</t>
+          <t>evidence.title</t>
         </is>
       </c>
       <c r="C94" s="10" t="inlineStr">
         <is>
-          <t>Page 26</t>
+          <t>Evidence</t>
         </is>
       </c>
       <c r="D94" s="10" t="inlineStr">
         <is>
-          <t>Seite 26</t>
+          <t>Belege</t>
         </is>
       </c>
       <c r="E94" s="11" t="n"/>
@@ -2892,22 +2880,22 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B95" s="9" t="inlineStr">
         <is>
-          <t>excerpt.endNote</t>
+          <t>evidence.grades[0].label</t>
         </is>
       </c>
       <c r="C95" s="10" t="inlineStr">
         <is>
-          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
+          <t>High</t>
         </is>
       </c>
       <c r="D95" s="10" t="inlineStr">
         <is>
-          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
+          <t>Hoch</t>
         </is>
       </c>
       <c r="E95" s="11" t="n"/>
@@ -2916,22 +2904,22 @@
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B96" s="9" t="inlineStr">
         <is>
-          <t>excerpt.unavailable</t>
+          <t>evidence.grades[0].description</t>
         </is>
       </c>
       <c r="C96" s="10" t="inlineStr">
         <is>
-          <t>The extract in this language will follow.</t>
+          <t>Replicated or robust evidence.</t>
         </is>
       </c>
       <c r="D96" s="10" t="inlineStr">
         <is>
-          <t>Die Leseprobe in dieser Sprache folgt.</t>
+          <t>Wiederholt bestätigte oder belastbare Belege.</t>
         </is>
       </c>
       <c r="E96" s="11" t="n"/>
@@ -2940,22 +2928,22 @@
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B97" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[0]</t>
+          <t>evidence.grades[1].label</t>
         </is>
       </c>
       <c r="C97" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="D97" s="10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>Mittel</t>
         </is>
       </c>
       <c r="E97" s="11" t="n"/>
@@ -2964,22 +2952,22 @@
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[1]</t>
+          <t>evidence.grades[1].description</t>
         </is>
       </c>
       <c r="C98" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Suggestive evidence with meaningful uncertainty.</t>
         </is>
       </c>
       <c r="D98" s="10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Hinweise, deren Unsicherheit ins Gewicht fällt.</t>
         </is>
       </c>
       <c r="E98" s="11" t="n"/>
@@ -2988,58 +2976,70 @@
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="9" t="inlineStr">
         <is>
-          <t>The extract — opening pages of the book, and the page 26 line</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>excerpt.folios[2]</t>
+          <t>evidence.grades[2].label</t>
         </is>
       </c>
       <c r="C99" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="D99" s="10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>Niedrig</t>
         </is>
       </c>
       <c r="E99" s="11" t="n"/>
       <c r="F99" s="11" t="n"/>
     </row>
-    <row r="100" ht="22" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
-        <is>
-          <t>CASE EVIDENCE CARDS</t>
-        </is>
-      </c>
-      <c r="B100" s="8" t="n"/>
-      <c r="C100" s="8" t="n"/>
-      <c r="D100" s="8" t="n"/>
-      <c r="E100" s="8" t="n"/>
-      <c r="F100" s="8" t="n"/>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="9" t="inlineStr">
+        <is>
+          <t>Evidence — the book's confidence markers</t>
+        </is>
+      </c>
+      <c r="B100" s="9" t="inlineStr">
+        <is>
+          <t>evidence.grades[2].description</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>Plausible hypothesis or emerging evidence.</t>
+        </is>
+      </c>
+      <c r="D100" s="10" t="inlineStr">
+        <is>
+          <t>Plausible Hypothese oder erste Belege.</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>cases.eyebrow</t>
+          <t>evidence.closing</t>
         </is>
       </c>
       <c r="C101" s="10" t="inlineStr">
         <is>
-          <t>Case evidence</t>
+          <t>These markers exist because the book’s own risk is the same risk it describes.</t>
         </is>
       </c>
       <c r="D101" s="10" t="inlineStr">
         <is>
-          <t>Beweismaterial</t>
+          <t>Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt.</t>
         </is>
       </c>
       <c r="E101" s="11" t="n"/>
@@ -3048,70 +3048,58 @@
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>Evidence — the book's confidence markers</t>
         </is>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>cases.pageLabel</t>
+          <t>evidence.folio</t>
         </is>
       </c>
       <c r="C102" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D102" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E102" s="11" t="n"/>
       <c r="F102" s="11" t="n"/>
     </row>
-    <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="9" t="inlineStr">
-        <is>
-          <t>Case evidence cards</t>
-        </is>
-      </c>
-      <c r="B103" s="9" t="inlineStr">
-        <is>
-          <t>cases.items[0].quote</t>
-        </is>
-      </c>
-      <c r="C103" s="10" t="inlineStr">
-        <is>
-          <t>“Something is off.”</t>
-        </is>
-      </c>
-      <c r="D103" s="10" t="inlineStr">
-        <is>
-          <t>„Irgendetwas stimmt nicht.“</t>
-        </is>
-      </c>
-      <c r="E103" s="11" t="n"/>
-      <c r="F103" s="11" t="n"/>
+    <row r="103" ht="22" customHeight="1">
+      <c r="A103" s="7" t="inlineStr">
+        <is>
+          <t>THE EXTRACT — THE OPENING PAGES OF THE BOOK</t>
+        </is>
+      </c>
+      <c r="B103" s="8" t="n"/>
+      <c r="C103" s="8" t="n"/>
+      <c r="D103" s="8" t="n"/>
+      <c r="E103" s="8" t="n"/>
+      <c r="F103" s="8" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].inputLabel</t>
+          <t>excerpt.title</t>
         </is>
       </c>
       <c r="C104" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Before the chapters</t>
         </is>
       </c>
       <c r="D104" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Vor den Kapiteln</t>
         </is>
       </c>
       <c r="E104" s="11" t="n"/>
@@ -3120,22 +3108,22 @@
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].input</t>
+          <t>excerpt.sectionLabel</t>
         </is>
       </c>
       <c r="C105" s="10" t="inlineStr">
         <is>
-          <t>Two minutes before the alarm.</t>
+          <t>The pilot</t>
         </is>
       </c>
       <c r="D105" s="10" t="inlineStr">
         <is>
-          <t>Zwei Minuten vor dem Wecker.</t>
+          <t>Der Pilot</t>
         </is>
       </c>
       <c r="E105" s="11" t="n"/>
@@ -3144,214 +3132,214 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verifiedLabel</t>
+          <t>excerpt.lead</t>
         </is>
       </c>
       <c r="C106" s="10" t="inlineStr">
         <is>
-          <t>Verified event</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D106" s="10" t="inlineStr">
         <is>
-          <t>Bestätigtes Ereignis</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E106" s="11" t="n"/>
       <c r="F106" s="11" t="n"/>
     </row>
-    <row r="107" ht="30" customHeight="1">
+    <row r="107" ht="105" customHeight="1">
       <c r="A107" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>cases.items[0].verified</t>
+          <t>excerpt.paragraphs[0]</t>
         </is>
       </c>
       <c r="C107" s="10" t="inlineStr">
         <is>
-          <t>Nothing has happened.</t>
+          <t>On the evening of 16 July 1999, a small single engine plane took off from New Jersey. It was heading for Martha’s Vineyard. The pilot was experienced enough to be confident and new enough to be wrong about what that confidence was worth. He had about 300 hours in the air. He had not finished the training that would qualify him to fly using only his instruments.</t>
         </is>
       </c>
       <c r="D107" s="10" t="inlineStr">
         <is>
-          <t>Nichts ist passiert.</t>
+          <t>Am Abend des 16. Juli 1999 startete in New Jersey ein kleines einmotoriges Flugzeug. Es war unterwegs nach Martha’s Vineyard. Der Pilot war erfahren genug, um sich seiner Sache sicher zu sein, und neu genug, um sich darin zu irren, was diese Sicherheit wert war. Er hatte rund 300 Flugstunden. Die Ausbildung, die ihn berechtigt hätte, nur nach seinen Instrumenten zu fliegen, hatte er nicht abgeschlossen.</t>
         </is>
       </c>
       <c r="E107" s="11" t="n"/>
       <c r="F107" s="11" t="n"/>
     </row>
-    <row r="108" ht="30" customHeight="1">
+    <row r="108" ht="210" customHeight="1">
       <c r="A108" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].quote</t>
+          <t>excerpt.paragraphs[1]</t>
         </is>
       </c>
       <c r="C108" s="10" t="inlineStr">
         <is>
-          <t>“ok.”</t>
+          <t>The sky was clear when he departed so he concluded that he did not need instruments. By the time he reached the coast, it was not. Haze had settled over the water. The sort of haze that erases the line between sea and sky so gradually that you do not notice the horizon is gone until you look for it and it is not there. Over land, this does not matter. There are lights below. You see roads, buildings, a geometry that tells your eyes which way is down. Over open water at night, with haze sitting on the surface like a second darkness, there is nothing. The world outside the cockpit becomes a uniform grey in every direction. Up looks like down. A gentle turn feels like level flight. A slow descent feels like holding steady.</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
         <is>
-          <t>„ok.“</t>
+          <t>Beim Start war der Himmel klar, also schloss er daraus, dass er keine Instrumente brauchte. Als er die Küste erreichte, war der Himmel es nicht mehr. Dunst hatte sich über das Wasser gelegt. Die Art von Dunst, die die Linie zwischen Meer und Himmel so allmählich auslöscht, dass man nicht merkt, dass der Horizont weg ist, bis man ihn sucht und er nicht da ist. Über Land macht das nichts. Unten sind Lichter. Man sieht Straßen, Gebäude, eine Geometrie, die den Augen sagt, wo unten ist. Über offenem Wasser bei Nacht, mit Dunst, der auf der Oberfläche liegt wie eine zweite Dunkelheit, ist da nichts. Die Welt außerhalb des Cockpits wird in alle Richtungen zu einem einzigen Grau. Oben sieht aus wie unten. Eine sanfte Kurve fühlt sich an wie Geradeausflug. Ein langsames Sinken fühlt sich an, als hielte man die Höhe.</t>
         </is>
       </c>
       <c r="E108" s="11" t="n"/>
       <c r="F108" s="11" t="n"/>
     </row>
-    <row r="109" ht="30" customHeight="1">
+    <row r="109" ht="150" customHeight="1">
       <c r="A109" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].inputLabel</t>
+          <t>excerpt.paragraphs[2]</t>
         </is>
       </c>
       <c r="C109" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>The pilot’s inner ear, the organ that tells the brain which way the body is oriented in space, works by detecting changes in motion. When you enter a turn, the fluid inside the ear shifts, and the brain registers rotation. But if the turn holds steady for fifteen or twenty seconds, the fluid in the inner ear settles. It stops moving. The brain, which tracks movement, not position, concludes that the turn has ended. You feel level, but you are not.</t>
         </is>
       </c>
       <c r="D109" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Das Innenohr des Piloten, das Organ, das dem Gehirn meldet, wie der Körper im Raum liegt, funktioniert, indem es Veränderungen der Bewegung wahrnimmt. Geht man in eine Kurve, verschiebt sich die Flüssigkeit im Ohr, und das Gehirn registriert die Drehung. Hält die Kurve aber fünfzehn oder zwanzig Sekunden lang an, kommt die Flüssigkeit im Innenohr zur Ruhe. Sie bewegt sich nicht mehr. Das Gehirn, das Bewegung verfolgt, nicht Lage, schließt daraus, dass die Kurve zu Ende ist. Man hat das Gefühl, waagerecht zu fliegen, tut es aber nicht.</t>
         </is>
       </c>
       <c r="E109" s="11" t="n"/>
       <c r="F109" s="11" t="n"/>
     </row>
-    <row r="110" ht="30" customHeight="1">
+    <row r="110" ht="165" customHeight="1">
       <c r="A110" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].input</t>
+          <t>excerpt.paragraphs[3]</t>
         </is>
       </c>
       <c r="C110" s="10" t="inlineStr">
         <is>
-          <t>Two letters. One full stop.</t>
+          <t>Somewhere over the dark water, the plane entered a gentle left turn. The pilot’s instruments, the dials on the panel in front of him, showed the turn. The artificial horizon, a small gyroscope display that shows the aircraft’s angle relative to the earth, was telling him he was banking. The altimeter was telling him he was descending. The airspeed indicator was telling him he was accelerating. His body was telling him something different. His body was telling him he was flying straight and level. His body felt right. His instruments felt wrong. He trusted his body.</t>
         </is>
       </c>
       <c r="D110" s="10" t="inlineStr">
         <is>
-          <t>Zwei Buchstaben. Ein Punkt.</t>
+          <t>Irgendwo über dem dunklen Wasser ging das Flugzeug in eine sanfte Linkskurve. Die Instrumente des Piloten, die Anzeigen auf dem Instrumentenbrett vor ihm, zeigten die Kurve. Der künstliche Horizont, eine kleine Kreiselanzeige, die den Winkel des Flugzeugs zur Erde zeigt, sagte ihm, dass er in Schräglage war. Der Höhenmesser sagte ihm, dass er sank. Der Fahrtmesser sagte ihm, dass er schneller wurde. Sein Körper sagte ihm etwas anderes. Sein Körper sagte ihm, dass er geradeaus und waagerecht flog. Sein Körper fühlte sich richtig an. Seine Instrumente fühlten sich falsch an. Er vertraute seinem Körper.</t>
         </is>
       </c>
       <c r="E110" s="11" t="n"/>
       <c r="F110" s="11" t="n"/>
     </row>
-    <row r="111" ht="30" customHeight="1">
+    <row r="111" ht="120" customHeight="1">
       <c r="A111" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verifiedLabel</t>
+          <t>excerpt.paragraphs[4]</t>
         </is>
       </c>
       <c r="C111" s="10" t="inlineStr">
         <is>
-          <t>Verified tone</t>
+          <t>The turn tightened. The nose dropped. The airspeed built. In the final seconds, the plane was descending at more than 4,700 feet per minute, nearly a mile every sixty seconds, in a tightening spiral that pilots call, with the grim precision of a profession that has named the ways it loses people, a graveyard spiral. He hit the water at full speed. He and his two passengers were killed on impact.</t>
         </is>
       </c>
       <c r="D111" s="10" t="inlineStr">
         <is>
-          <t>Bestätigter Tonfall</t>
+          <t>Die Kurve wurde enger. Die Nase senkte sich. Die Fahrt nahm zu. In den letzten Sekunden sank das Flugzeug mit mehr als 4.700 Fuß pro Minute, fast anderthalb Kilometer alle sechzig Sekunden, in einer immer engeren Spirale. Piloten nennen sie, mit der düsteren Präzision eines Berufs, der die Arten benannt hat, auf die er Menschen verliert, Friedhofsspirale. Er schlug mit voller Geschwindigkeit auf dem Wasser auf. Er und seine beiden Passagiere starben beim Aufprall.</t>
         </is>
       </c>
       <c r="E111" s="11" t="n"/>
       <c r="F111" s="11" t="n"/>
     </row>
-    <row r="112" ht="30" customHeight="1">
+    <row r="112" ht="135" customHeight="1">
       <c r="A112" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>cases.items[1].verified</t>
+          <t>excerpt.paragraphs[5]</t>
         </is>
       </c>
       <c r="C112" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>The investigation found no mechanical failure. The engine was running. The instruments were working. The data was right there, on the panel, six inches from his eyes, the whole time, but he did not read it. He read his body instead. The American Federal Aviation Administration’s instruction to pilots who find themselves in this situation is one sentence long. It is a literal instruction that applies to your life as directly as it applies to a cockpit:</t>
         </is>
       </c>
       <c r="D112" s="10" t="inlineStr">
         <is>
-          <t>Keiner.</t>
+          <t>Die Untersuchung fand keinen mechanischen Defekt. Der Motor lief. Die Instrumente funktionierten. Die Daten waren die ganze Zeit da, auf dem Instrumentenbrett, fünfzehn Zentimeter vor seinen Augen, aber er las sie nicht ab. Er las stattdessen seinen Körper. Die amerikanische Luftfahrtbehörde, die Federal Aviation Administration, hat eine Anweisung für Piloten, die in diese Situation geraten. Sie ist einen Satz lang. Die Anweisung ist wörtlich gemeint, und sie gilt für Ihr Leben so unmittelbar wie für ein Cockpit:</t>
         </is>
       </c>
       <c r="E112" s="11" t="n"/>
       <c r="F112" s="11" t="n"/>
     </row>
-    <row r="113" ht="30" customHeight="1">
+    <row r="113" ht="75" customHeight="1">
       <c r="A113" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B113" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].quote</t>
+          <t>excerpt.paragraphs[6]</t>
         </is>
       </c>
       <c r="C113" s="10" t="inlineStr">
         <is>
-          <t>“Something is wrong with my life.”</t>
+          <t>The pilot’s name was John F. Kennedy Jr. He was the son of an American president. He had been advised not to fly that night without his instructor. He told his instructor he wanted to do it alone. He was thirty-eight years old.</t>
         </is>
       </c>
       <c r="D113" s="10" t="inlineStr">
         <is>
-          <t>„Mit meinem Leben stimmt etwas nicht.“</t>
+          <t>Der Pilot hieß John F. Kennedy Jr. Er war der Sohn eines amerikanischen Präsidenten. Man hatte ihm geraten, in dieser Nacht nicht ohne seinen Fluglehrer zu fliegen. Er sagte seinem Fluglehrer, er wolle es allein machen. Er war achtunddreißig Jahre alt.</t>
         </is>
       </c>
       <c r="E113" s="11" t="n"/>
       <c r="F113" s="11" t="n"/>
     </row>
-    <row r="114" ht="30" customHeight="1">
+    <row r="114" ht="240" customHeight="1">
       <c r="A114" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B114" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].inputLabel</t>
+          <t>excerpt.paragraphs[7]</t>
         </is>
       </c>
       <c r="C114" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>You operate a body that produces signals and your mind often treats those signals as truth. The signals are sometimes as wrong as the inner ear’s vestibular system over dark water. The tiredness that presents itself as a question about your career. The caffeine spike that presents itself as anxiety about an email. The low blood sugar that presents itself as evidence that your relationship is failing. Your body speaks first and your mind explains second. The explanation, because it arrives with the full weight of physical conviction, the tight jaw, the fast heartbeat, the heat behind the ears, feels like deep knowledge. It feels like you are reading the situation. But you are only reading the instrument that is reading the situation, and the instrument’s settings were off before the situation arrived. These instruments exist. You have them. Heart rate, jaw tension, breathing depth, shoulder position, the speed of your thoughts. They are producing data right now, as you read this sentence. But the body’s confident weather report about the world is only a draft.</t>
         </is>
       </c>
       <c r="D114" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>Sie steuern einen Körper, der Signale erzeugt, und Ihr Kopf hält diese Signale oft für die Wahrheit. Manchmal liegen die Signale so falsch wie das Gleichgewichtsorgan im Innenohr über dunklem Wasser. Die Müdigkeit, die als Frage nach Ihrer Karriere daherkommt. Der Koffeinschub, der als Angst wegen einer E-Mail daherkommt. Der niedrige Blutzucker, der als Beleg dafür daherkommt, dass Ihre Beziehung scheitert. Ihr Körper spricht zuerst, und Ihr Kopf erklärt danach. Weil die Erklärung mit dem ganzen Gewicht körperlicher Überzeugung kommt, dem angespannten Kiefer, dem schnellen Herzschlag, der Hitze hinter den Ohren, fühlt sie sich an wie tiefes Wissen. Es fühlt sich an, als würden Sie die Situation lesen. Aber Sie lesen nur das Instrument ab, das die Situation liest, und die Einstellungen des Instruments waren schon verstellt, bevor die Situation da war. Diese Instrumente gibt es. Sie haben sie. Puls, Kieferspannung, Atemtiefe, Schulterhaltung, das Tempo Ihrer Gedanken. In diesem Moment liefern sie Daten, während Sie diesen Satz lesen. Aber der selbstsichere Wetterbericht, den der Körper über die Welt abgibt, ist nur ein Entwurf.</t>
         </is>
       </c>
       <c r="E114" s="11" t="n"/>
@@ -3360,22 +3348,22 @@
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B115" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].input</t>
+          <t>excerpt.quote</t>
         </is>
       </c>
       <c r="C115" s="10" t="inlineStr">
         <is>
-          <t>Six ordinary events. One depleted day.</t>
+          <t>“have confidence in your instruments and ignore all conflicting signals your body gives you.”</t>
         </is>
       </c>
       <c r="D115" s="10" t="inlineStr">
         <is>
-          <t>Sechs gewöhnliche Ereignisse. Ein erschöpfter Tag.</t>
+          <t>„vertrauen Sie Ihren Instrumenten und ignorieren Sie alle Signale Ihres Körpers, die dem widersprechen.“</t>
         </is>
       </c>
       <c r="E115" s="11" t="n"/>
@@ -3384,22 +3372,22 @@
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B116" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verifiedLabel</t>
+          <t>excerpt.continueCta</t>
         </is>
       </c>
       <c r="C116" s="10" t="inlineStr">
         <is>
-          <t>Verified crisis</t>
+          <t>Continue reading</t>
         </is>
       </c>
       <c r="D116" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Krise</t>
+          <t>Weiterlesen</t>
         </is>
       </c>
       <c r="E116" s="11" t="n"/>
@@ -3408,22 +3396,22 @@
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B117" s="9" t="inlineStr">
         <is>
-          <t>cases.items[2].verified</t>
+          <t>excerpt.back</t>
         </is>
       </c>
       <c r="C117" s="10" t="inlineStr">
         <is>
-          <t>None.</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D117" s="10" t="inlineStr">
         <is>
-          <t>Keine.</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E117" s="11" t="n"/>
@@ -3432,46 +3420,46 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B118" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].quote</t>
+          <t>excerpt.readingModeLabel</t>
         </is>
       </c>
       <c r="C118" s="10" t="inlineStr">
         <is>
-          <t>“This is state, not situation.”</t>
+          <t>Reading mode</t>
         </is>
       </c>
       <c r="D118" s="10" t="inlineStr">
         <is>
-          <t>„Das ist Zustand, nicht Situation.“</t>
+          <t>Lesemodus</t>
         </is>
       </c>
       <c r="E118" s="11" t="n"/>
       <c r="F118" s="11" t="n"/>
     </row>
-    <row r="119" ht="30" customHeight="1">
+    <row r="119" ht="135" customHeight="1">
       <c r="A119" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B119" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].inputLabel</t>
+          <t>excerpt.closing</t>
         </is>
       </c>
       <c r="C119" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>This book is about the same error at kitchen scale. The version that happens every Tuesday. The version where your body writes a story about a message, a silence, a look, and your mind edits that story under the supervision of whatever your body is feeling at the time. Nobody dies, but decisions get made. Relationships change. Self-assessments form. And none of it had to happen the way it did, because the data was right there the whole time.</t>
         </is>
       </c>
       <c r="D119" s="10" t="inlineStr">
         <is>
-          <t>Input</t>
+          <t>In diesem Buch geht es um denselben Fehler, im Maßstab einer Küche. Die Version, die jeden Dienstag passiert. Die Version, in der Ihr Körper eine Geschichte über eine Nachricht, ein Schweigen, einen Blick schreibt und Ihr Kopf diese Geschichte redigiert, unter der Aufsicht dessen, was Ihr Körper gerade fühlt. Niemand stirbt, aber Entscheidungen fallen. Beziehungen verändern sich. Selbsteinschätzungen entstehen. Und nichts davon musste so kommen, wie es kam, denn die Daten waren die ganze Zeit da.</t>
         </is>
       </c>
       <c r="E119" s="11" t="n"/>
@@ -3480,22 +3468,22 @@
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B120" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].input</t>
+          <t>excerpt.closingSource</t>
         </is>
       </c>
       <c r="C120" s="10" t="inlineStr">
         <is>
-          <t>Low fuel. Dead light. A sound on grit.</t>
+          <t>Page 26</t>
         </is>
       </c>
       <c r="D120" s="10" t="inlineStr">
         <is>
-          <t>Wenig Treibstoff. Kaputtes Licht. Ein Geräusch auf Splitt.</t>
+          <t>Seite 26</t>
         </is>
       </c>
       <c r="E120" s="11" t="n"/>
@@ -3504,22 +3492,22 @@
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B121" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verifiedLabel</t>
+          <t>excerpt.endNote</t>
         </is>
       </c>
       <c r="C121" s="10" t="inlineStr">
         <is>
-          <t>Verified threat</t>
+          <t>Chapter Zero follows: A Day That Should Have Been Fine.</t>
         </is>
       </c>
       <c r="D121" s="10" t="inlineStr">
         <is>
-          <t>Bestätigte Bedrohung</t>
+          <t>Es folgt Kapitel Null: Ein Tag, der in Ordnung hätte sein sollen.</t>
         </is>
       </c>
       <c r="E121" s="11" t="n"/>
@@ -3528,22 +3516,22 @@
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B122" s="9" t="inlineStr">
         <is>
-          <t>cases.items[3].verified</t>
+          <t>excerpt.unavailable</t>
         </is>
       </c>
       <c r="C122" s="10" t="inlineStr">
         <is>
-          <t>Not yet visible.</t>
+          <t>The extract in this language will follow.</t>
         </is>
       </c>
       <c r="D122" s="10" t="inlineStr">
         <is>
-          <t>Noch nicht sichtbar.</t>
+          <t>Die Leseprobe in dieser Sprache folgt.</t>
         </is>
       </c>
       <c r="E122" s="11" t="n"/>
@@ -3552,22 +3540,22 @@
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B123" s="9" t="inlineStr">
         <is>
-          <t>cases.closing</t>
+          <t>excerpt.folios[0]</t>
         </is>
       </c>
       <c r="C123" s="10" t="inlineStr">
         <is>
-          <t>It said I am failing; the data was I am tired.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="D123" s="10" t="inlineStr">
         <is>
-          <t>Es hieß: Ich versage. Die Daten waren: Ich bin müde.</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E123" s="11" t="n"/>
@@ -3576,62 +3564,62 @@
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="9" t="inlineStr">
         <is>
-          <t>Case evidence cards</t>
+          <t>The extract — the opening pages of the book</t>
         </is>
       </c>
       <c r="B124" s="9" t="inlineStr">
         <is>
-          <t>cases.closingSource</t>
+          <t>excerpt.folios[1]</t>
         </is>
       </c>
       <c r="C124" s="10" t="inlineStr">
         <is>
-          <t>Page 20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D124" s="10" t="inlineStr">
         <is>
-          <t>Seite 20</t>
+          <t>8</t>
         </is>
       </c>
       <c r="E124" s="11" t="n"/>
       <c r="F124" s="11" t="n"/>
     </row>
-    <row r="125" ht="22" customHeight="1">
-      <c r="A125" s="7" t="inlineStr">
+    <row r="125" ht="30" customHeight="1">
+      <c r="A125" s="9" t="inlineStr">
+        <is>
+          <t>The extract — the opening pages of the book</t>
+        </is>
+      </c>
+      <c r="B125" s="9" t="inlineStr">
+        <is>
+          <t>excerpt.folios[2]</t>
+        </is>
+      </c>
+      <c r="C125" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E125" s="11" t="n"/>
+      <c r="F125" s="11" t="n"/>
+    </row>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="7" t="inlineStr">
         <is>
           <t>AUDIO PLAYER (HIDDEN UNTIL A RECORDING EXISTS)</t>
         </is>
       </c>
-      <c r="B125" s="8" t="n"/>
-      <c r="C125" s="8" t="n"/>
-      <c r="D125" s="8" t="n"/>
-      <c r="E125" s="8" t="n"/>
-      <c r="F125" s="8" t="n"/>
-    </row>
-    <row r="126" ht="30" customHeight="1">
-      <c r="A126" s="9" t="inlineStr">
-        <is>
-          <t>Audio player (hidden until a recording exists)</t>
-        </is>
-      </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>listen.eyebrow</t>
-        </is>
-      </c>
-      <c r="C126" s="10" t="inlineStr">
-        <is>
-          <t>Listen</t>
-        </is>
-      </c>
-      <c r="D126" s="10" t="inlineStr">
-        <is>
-          <t>Hören</t>
-        </is>
-      </c>
-      <c r="E126" s="11" t="n"/>
-      <c r="F126" s="11" t="n"/>
+      <c r="B126" s="8" t="n"/>
+      <c r="C126" s="8" t="n"/>
+      <c r="D126" s="8" t="n"/>
+      <c r="E126" s="8" t="n"/>
+      <c r="F126" s="8" t="n"/>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="9" t="inlineStr">
@@ -3641,17 +3629,17 @@
       </c>
       <c r="B127" s="9" t="inlineStr">
         <is>
-          <t>listen.title</t>
+          <t>listen.eyebrow</t>
         </is>
       </c>
       <c r="C127" s="10" t="inlineStr">
         <is>
-          <t>Listen to an extract</t>
+          <t>Listen</t>
         </is>
       </c>
       <c r="D127" s="10" t="inlineStr">
         <is>
-          <t>Hörprobe</t>
+          <t>Hören</t>
         </is>
       </c>
       <c r="E127" s="11" t="n"/>
@@ -3665,17 +3653,17 @@
       </c>
       <c r="B128" s="9" t="inlineStr">
         <is>
-          <t>listen.subtitle</t>
+          <t>listen.title</t>
         </is>
       </c>
       <c r="C128" s="10" t="inlineStr">
         <is>
-          <t>Read by the author</t>
+          <t>Listen to an extract</t>
         </is>
       </c>
       <c r="D128" s="10" t="inlineStr">
         <is>
-          <t>Gelesen von der Autorin</t>
+          <t>Hörprobe</t>
         </is>
       </c>
       <c r="E128" s="11" t="n"/>
@@ -3689,17 +3677,17 @@
       </c>
       <c r="B129" s="9" t="inlineStr">
         <is>
-          <t>listen.play</t>
+          <t>listen.subtitle</t>
         </is>
       </c>
       <c r="C129" s="10" t="inlineStr">
         <is>
-          <t>Play</t>
+          <t>Read by the author</t>
         </is>
       </c>
       <c r="D129" s="10" t="inlineStr">
         <is>
-          <t>Abspielen</t>
+          <t>Gelesen von der Autorin</t>
         </is>
       </c>
       <c r="E129" s="11" t="n"/>
@@ -3713,17 +3701,17 @@
       </c>
       <c r="B130" s="9" t="inlineStr">
         <is>
-          <t>listen.pause</t>
+          <t>listen.play</t>
         </is>
       </c>
       <c r="C130" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Play</t>
         </is>
       </c>
       <c r="D130" s="10" t="inlineStr">
         <is>
-          <t>Pause</t>
+          <t>Abspielen</t>
         </is>
       </c>
       <c r="E130" s="11" t="n"/>
@@ -3737,17 +3725,17 @@
       </c>
       <c r="B131" s="9" t="inlineStr">
         <is>
-          <t>listen.progress</t>
+          <t>listen.pause</t>
         </is>
       </c>
       <c r="C131" s="10" t="inlineStr">
         <is>
-          <t>Playback position</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="D131" s="10" t="inlineStr">
         <is>
-          <t>Wiedergabeposition</t>
+          <t>Pause</t>
         </is>
       </c>
       <c r="E131" s="11" t="n"/>
@@ -3761,17 +3749,17 @@
       </c>
       <c r="B132" s="9" t="inlineStr">
         <is>
-          <t>listen.elapsed</t>
+          <t>listen.progress</t>
         </is>
       </c>
       <c r="C132" s="10" t="inlineStr">
         <is>
-          <t>Elapsed</t>
+          <t>Playback position</t>
         </is>
       </c>
       <c r="D132" s="10" t="inlineStr">
         <is>
-          <t>Verstrichen</t>
+          <t>Wiedergabeposition</t>
         </is>
       </c>
       <c r="E132" s="11" t="n"/>
@@ -3785,17 +3773,17 @@
       </c>
       <c r="B133" s="9" t="inlineStr">
         <is>
-          <t>listen.duration</t>
+          <t>listen.elapsed</t>
         </is>
       </c>
       <c r="C133" s="10" t="inlineStr">
         <is>
-          <t>Duration</t>
+          <t>Elapsed</t>
         </is>
       </c>
       <c r="D133" s="10" t="inlineStr">
         <is>
-          <t>Dauer</t>
+          <t>Verstrichen</t>
         </is>
       </c>
       <c r="E133" s="11" t="n"/>
@@ -3809,77 +3797,77 @@
       </c>
       <c r="B134" s="9" t="inlineStr">
         <is>
-          <t>listen.unavailable</t>
+          <t>listen.duration</t>
         </is>
       </c>
       <c r="C134" s="10" t="inlineStr">
         <is>
-          <t>The recording will be added here.</t>
+          <t>Duration</t>
         </is>
       </c>
       <c r="D134" s="10" t="inlineStr">
         <is>
-          <t>Die Aufnahme folgt hier.</t>
+          <t>Dauer</t>
         </is>
       </c>
       <c r="E134" s="11" t="n"/>
       <c r="F134" s="11" t="n"/>
     </row>
-    <row r="135" ht="22" customHeight="1">
-      <c r="A135" s="7" t="inlineStr">
-        <is>
-          <t>THE INVESTIGATION (PAGE 11), “BEFORE WE BEGIN” (PAGE 13 MARKERS), THE THREE SYSTEMS, PAGE 226</t>
-        </is>
-      </c>
-      <c r="B135" s="8" t="n"/>
-      <c r="C135" s="8" t="n"/>
-      <c r="D135" s="8" t="n"/>
-      <c r="E135" s="8" t="n"/>
-      <c r="F135" s="8" t="n"/>
-    </row>
-    <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="9" t="inlineStr">
-        <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
-        </is>
-      </c>
-      <c r="B136" s="9" t="inlineStr">
-        <is>
-          <t>map.eyebrow</t>
-        </is>
-      </c>
-      <c r="C136" s="10" t="inlineStr">
-        <is>
-          <t>A map of the book</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>Eine Karte des Buches</t>
-        </is>
-      </c>
-      <c r="E136" s="11" t="n"/>
-      <c r="F136" s="11" t="n"/>
-    </row>
-    <row r="137" ht="90" customHeight="1">
+    <row r="135" ht="30" customHeight="1">
+      <c r="A135" s="9" t="inlineStr">
+        <is>
+          <t>Audio player (hidden until a recording exists)</t>
+        </is>
+      </c>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>listen.unavailable</t>
+        </is>
+      </c>
+      <c r="C135" s="10" t="inlineStr">
+        <is>
+          <t>The recording will be added here.</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>Die Aufnahme folgt hier.</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+    </row>
+    <row r="136" ht="22" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
+        <is>
+          <t>ABOUT THE AUTHOR</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="n"/>
+      <c r="C136" s="8" t="n"/>
+      <c r="D136" s="8" t="n"/>
+      <c r="E136" s="8" t="n"/>
+      <c r="F136" s="8" t="n"/>
+    </row>
+    <row r="137" ht="30" customHeight="1">
       <c r="A137" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>map.sortingTool</t>
+          <t>author.title</t>
         </is>
       </c>
       <c r="C137" s="10" t="inlineStr">
         <is>
-          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
         <is>
-          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E137" s="11" t="n"/>
@@ -3888,46 +3876,46 @@
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].name</t>
+          <t>author.photoAlt</t>
         </is>
       </c>
       <c r="C138" s="10" t="inlineStr">
         <is>
-          <t>Time</t>
+          <t>Ivana Budišin, photographed against a dark grey background.</t>
         </is>
       </c>
       <c r="D138" s="10" t="inlineStr">
         <is>
-          <t>Zeit</t>
+          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
         </is>
       </c>
       <c r="E138" s="11" t="n"/>
       <c r="F138" s="11" t="n"/>
     </row>
-    <row r="139" ht="45" customHeight="1">
+    <row r="139" ht="30" customHeight="1">
       <c r="A139" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>map.loops[0].body</t>
+          <t>author.photoPlaceholder</t>
         </is>
       </c>
       <c r="C139" s="10" t="inlineStr">
         <is>
-          <t>Sleep, food, caffeine, circadian phase, recovery. When the timing is off, baseline sensitivity rises. The same world feels harsher.</t>
+          <t>Author photograph to follow</t>
         </is>
       </c>
       <c r="D139" s="10" t="inlineStr">
         <is>
-          <t>Schlaf, Essen, Koffein, zirkadiane Phase, Erholung. Stimmt das Timing nicht, steigt das Grundniveau der Empfindlichkeit. Dieselbe Welt fühlt sich härter an.</t>
+          <t>Foto der Autorin folgt</t>
         </is>
       </c>
       <c r="E139" s="11" t="n"/>
@@ -3936,46 +3924,46 @@
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].name</t>
+          <t>author.bio</t>
         </is>
       </c>
       <c r="C140" s="10" t="inlineStr">
         <is>
-          <t>Attention</t>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
         </is>
       </c>
       <c r="D140" s="10" t="inlineStr">
         <is>
-          <t>Aufmerksamkeit</t>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
         </is>
       </c>
       <c r="E140" s="11" t="n"/>
       <c r="F140" s="11" t="n"/>
     </row>
-    <row r="141" ht="60" customHeight="1">
+    <row r="141" ht="75" customHeight="1">
       <c r="A141" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>map.loops[1].body</t>
+          <t>author.readers</t>
         </is>
       </c>
       <c r="C141" s="10" t="inlineStr">
         <is>
-          <t>The system that tracks reward, novelty, and the next cue. When it is captured, focus narrows to the cheapest available input, and the expensive work feels hard.</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D141" s="10" t="inlineStr">
         <is>
-          <t>Das System, das Belohnung, Neues und den nächsten Auslöser verfolgt. Ist es eingefangen, verengt sich der Fokus auf das, was gerade da ist und am wenigsten Mühe macht, und die Arbeit, die einem viel abverlangt, fühlt sich schwer an.</t>
+          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
         </is>
       </c>
       <c r="E141" s="11" t="n"/>
@@ -3984,166 +3972,142 @@
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>About the author</t>
         </is>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>map.loops[2].name</t>
+          <t>author.pressLabel</t>
         </is>
       </c>
       <c r="C142" s="10" t="inlineStr">
         <is>
-          <t>Safety</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D142" s="10" t="inlineStr">
         <is>
-          <t>Sicherheit</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E142" s="11" t="n"/>
       <c r="F142" s="11" t="n"/>
     </row>
-    <row r="143" ht="75" customHeight="1">
-      <c r="A143" s="9" t="inlineStr">
-        <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
-        </is>
-      </c>
-      <c r="B143" s="9" t="inlineStr">
-        <is>
-          <t>map.loops[2].body</t>
-        </is>
-      </c>
-      <c r="C143" s="10" t="inlineStr">
-        <is>
-          <t>The system that monitors threat, and especially social threat. Things like social evaluation, exclusion, ambiguity, status. It is fast, it is old, and it is biased toward false alarms. It produces interpretations that feel like facts.</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>Das System, das auf Bedrohung achtet, vor allem auf soziale Bedrohung. Auf Dinge wie Bewertung durch andere, Ausgrenzung, Mehrdeutigkeit, Status. Es ist schnell, es ist alt, und es neigt zu Fehlalarmen. Es erzeugt Deutungen, die sich wie Tatsachen anfühlen.</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="n"/>
-      <c r="F143" s="11" t="n"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="7" t="inlineStr">
+        <is>
+          <t>THE CLOSING QUESTION AND THE PUBLICATION UPDATES FORM</t>
+        </is>
+      </c>
+      <c r="B143" s="8" t="n"/>
+      <c r="C143" s="8" t="n"/>
+      <c r="D143" s="8" t="n"/>
+      <c r="E143" s="8" t="n"/>
+      <c r="F143" s="8" t="n"/>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>The closing question and the publication updates form</t>
         </is>
       </c>
       <c r="B144" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceEyebrow</t>
+          <t>closing.question</t>
         </is>
       </c>
       <c r="C144" s="10" t="inlineStr">
         <is>
-          <t>Before we begin</t>
+          <t>Is this the situation? Or is this their state?</t>
         </is>
       </c>
       <c r="D144" s="10" t="inlineStr">
         <is>
-          <t>Bevor wir anfangen</t>
+          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
         </is>
       </c>
       <c r="E144" s="11" t="n"/>
       <c r="F144" s="11" t="n"/>
     </row>
-    <row r="145" ht="120" customHeight="1">
+    <row r="145" ht="30" customHeight="1">
       <c r="A145" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>The closing question and the publication updates form</t>
         </is>
       </c>
       <c r="B145" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceIntro</t>
+          <t>closing.source</t>
         </is>
       </c>
       <c r="C145" s="10" t="inlineStr">
         <is>
-          <t>This book makes claims about the brain and the body and those claims carry different amounts of evidence. Some rest on decades of replicated research. Some rest on newer findings that are promising but not yet settled. Some claims are plausible extensions of established science that have not been directly tested in the specific form this book describes. You should know which is which.</t>
+          <t>Page 225</t>
         </is>
       </c>
       <c r="D145" s="10" t="inlineStr">
         <is>
-          <t>Dieses Buch macht Aussagen über Gehirn und Körper, und diese Aussagen sind unterschiedlich gut belegt. Manche stützen sich auf Jahrzehnte replizierter Forschung. Manche stützen sich auf neuere Ergebnisse, die vielversprechend, aber noch nicht gesichert sind. Manche sind plausible Weiterführungen gesicherter Erkenntnisse, die in genau der Form, die dieses Buch beschreibt, noch nicht direkt geprüft wurden. Sie sollten wissen, was davon was ist.</t>
+          <t>Seite 225</t>
         </is>
       </c>
       <c r="E145" s="11" t="n"/>
       <c r="F145" s="11" t="n"/>
     </row>
-    <row r="146" ht="180" customHeight="1">
+    <row r="146" ht="30" customHeight="1">
       <c r="A146" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>The closing question and the publication updates form</t>
         </is>
       </c>
       <c r="B146" s="9" t="inlineStr">
         <is>
-          <t>map.evidenceMarkers</t>
+          <t>closing.line</t>
         </is>
       </c>
       <c r="C146" s="10" t="inlineStr">
         <is>
-          <t>Throughout the book scientific claims carry a confidence marker. When a finding rests on solid, replicated evidence, you will see a graphic marked as high evidence and illustrated with a deep red heartbeat on the margin. When the evidence is suggestive but incomplete it is noted as medium evidence with an orange heartbeat. When a claim is a plausible hypothesis that needs stronger tests, it is marked as low in faded grey. These markers exist because the book’s own risk is the same risk it describes. It does not want to treat a plausible story as settled truth. These markers are a brake on that.</t>
+          <t>Same life. Different instrument settings.</t>
         </is>
       </c>
       <c r="D146" s="10" t="inlineStr">
         <is>
-          <t>Im ganzen Buch tragen wissenschaftliche Aussagen eine Markierung, die zeigt, wie gut sie belegt sind. Stützt sich ein Ergebnis auf solide, replizierte Belege, sehen Sie am Rand eine Grafik, gekennzeichnet als hoch belegt, mit einem tiefroten Herzschlag. Sind die Belege zwar ein Hinweis, aber unvollständig, steht dort mittel belegt, mit einem orangefarbenen Herzschlag. Ist eine Aussage eine plausible Hypothese, die noch strengere Prüfungen braucht, ist sie als niedrig markiert, in verblasstem Grau. Diese Markierungen gibt es, weil das Buch selbst dasselbe Risiko trägt, das es beschreibt. Es will eine plausible Geschichte nicht als gesicherte Wahrheit behandeln. Diese Markierungen sind eine Bremse dagegen.</t>
+          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
         </is>
       </c>
       <c r="E146" s="11" t="n"/>
       <c r="F146" s="11" t="n"/>
     </row>
-    <row r="147" ht="30" customHeight="1">
-      <c r="A147" s="9" t="inlineStr">
-        <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
-        </is>
-      </c>
-      <c r="B147" s="9" t="inlineStr">
-        <is>
-          <t>map.grades[0].label</t>
-        </is>
-      </c>
-      <c r="C147" s="10" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="D147" s="10" t="inlineStr">
-        <is>
-          <t>Hoch</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="n"/>
-      <c r="F147" s="11" t="n"/>
+    <row r="147" ht="22" customHeight="1">
+      <c r="A147" s="7" t="inlineStr">
+        <is>
+          <t>PRESS PAGE</t>
+        </is>
+      </c>
+      <c r="B147" s="8" t="n"/>
+      <c r="C147" s="8" t="n"/>
+      <c r="D147" s="8" t="n"/>
+      <c r="E147" s="8" t="n"/>
+      <c r="F147" s="8" t="n"/>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B148" s="9" t="inlineStr">
         <is>
-          <t>map.grades[1].label</t>
+          <t>press.eyebrow</t>
         </is>
       </c>
       <c r="C148" s="10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D148" s="10" t="inlineStr">
         <is>
-          <t>Mittel</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E148" s="11" t="n"/>
@@ -4152,22 +4116,22 @@
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B149" s="9" t="inlineStr">
         <is>
-          <t>map.grades[2].label</t>
+          <t>press.title</t>
         </is>
       </c>
       <c r="C149" s="10" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Press materials</t>
         </is>
       </c>
       <c r="D149" s="10" t="inlineStr">
         <is>
-          <t>Niedrig</t>
+          <t>Pressematerial</t>
         </is>
       </c>
       <c r="E149" s="11" t="n"/>
@@ -4176,22 +4140,22 @@
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B150" s="9" t="inlineStr">
         <is>
-          <t>map.investigationTitle</t>
+          <t>press.intro</t>
         </is>
       </c>
       <c r="C150" s="10" t="inlineStr">
         <is>
-          <t>The Investigation</t>
+          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
         </is>
       </c>
       <c r="D150" s="10" t="inlineStr">
         <is>
-          <t>Die Untersuchung</t>
+          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
         </is>
       </c>
       <c r="E150" s="11" t="n"/>
@@ -4200,22 +4164,22 @@
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B151" s="9" t="inlineStr">
         <is>
-          <t>map.mapLine</t>
+          <t>press.contactHeading</t>
         </is>
       </c>
       <c r="C151" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D151" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E151" s="11" t="n"/>
@@ -4224,22 +4188,22 @@
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B152" s="9" t="inlineStr">
         <is>
-          <t>map.pageColumn</t>
+          <t>press.assetsHeading</t>
         </is>
       </c>
       <c r="C152" s="10" t="inlineStr">
         <is>
-          <t>Page</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="D152" s="10" t="inlineStr">
         <is>
-          <t>Seite</t>
+          <t>Downloads</t>
         </is>
       </c>
       <c r="E152" s="11" t="n"/>
@@ -4248,22 +4212,22 @@
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B153" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[0].title</t>
+          <t>press.kitLabel</t>
         </is>
       </c>
       <c r="C153" s="10" t="inlineStr">
         <is>
-          <t>A Day That Should Have Been Fine</t>
+          <t>Download complete press kit</t>
         </is>
       </c>
       <c r="D153" s="10" t="inlineStr">
         <is>
-          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
+          <t>Vollständige Pressemappe herunterladen</t>
         </is>
       </c>
       <c r="E153" s="11" t="n"/>
@@ -4272,22 +4236,22 @@
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B154" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[1].title</t>
+          <t>press.assets[0].label</t>
         </is>
       </c>
       <c r="C154" s="10" t="inlineStr">
         <is>
-          <t>The Radar Was Right</t>
+          <t>Front cover, high resolution</t>
         </is>
       </c>
       <c r="D154" s="10" t="inlineStr">
         <is>
-          <t>Das Radar hatte recht</t>
+          <t>Cover, Vorderseite, hohe Auflösung</t>
         </is>
       </c>
       <c r="E154" s="11" t="n"/>
@@ -4296,22 +4260,22 @@
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B155" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[2].title</t>
+          <t>press.assets[0].note</t>
         </is>
       </c>
       <c r="C155" s="10" t="inlineStr">
         <is>
-          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
+          <t>JPEG, 2400 px wide</t>
         </is>
       </c>
       <c r="D155" s="10" t="inlineStr">
         <is>
-          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
+          <t>JPEG, 2400 px breit</t>
         </is>
       </c>
       <c r="E155" s="11" t="n"/>
@@ -4320,22 +4284,22 @@
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B156" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[3].title</t>
+          <t>press.assets[1].label</t>
         </is>
       </c>
       <c r="C156" s="10" t="inlineStr">
         <is>
-          <t>The Relief That Becomes Itch</t>
+          <t>Author photograph</t>
         </is>
       </c>
       <c r="D156" s="10" t="inlineStr">
         <is>
-          <t>Die Erleichterung, die zum Juckreiz wird</t>
+          <t>Foto der Autorin</t>
         </is>
       </c>
       <c r="E156" s="11" t="n"/>
@@ -4344,22 +4308,22 @@
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B157" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[4].title</t>
+          <t>press.assets[1].note</t>
         </is>
       </c>
       <c r="C157" s="10" t="inlineStr">
         <is>
-          <t>The Predictable Cue</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="D157" s="10" t="inlineStr">
         <is>
-          <t>Der vorhersehbare Auslöser</t>
+          <t>JPEG, 1600 × 1600</t>
         </is>
       </c>
       <c r="E157" s="11" t="n"/>
@@ -4368,22 +4332,22 @@
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B158" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[5].title</t>
+          <t>press.assets[2].label</t>
         </is>
       </c>
       <c r="C158" s="10" t="inlineStr">
         <is>
-          <t>Why Evenings Stretch and Mornings Shrink</t>
+          <t>Book render, transparent background</t>
         </is>
       </c>
       <c r="D158" s="10" t="inlineStr">
         <is>
-          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
+          <t>Buchansicht, freigestellt</t>
         </is>
       </c>
       <c r="E158" s="11" t="n"/>
@@ -4392,22 +4356,22 @@
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B159" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[6].title</t>
+          <t>press.assets[2].note</t>
         </is>
       </c>
       <c r="C159" s="10" t="inlineStr">
         <is>
-          <t>Why Rest Doesn’t Always Restore</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="D159" s="10" t="inlineStr">
         <is>
-          <t>Warum Ruhe nicht immer erholsam ist</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="E159" s="11" t="n"/>
@@ -4416,22 +4380,22 @@
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B160" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[7].title</t>
+          <t>press.assets[3].label</t>
         </is>
       </c>
       <c r="C160" s="10" t="inlineStr">
         <is>
-          <t>Why You Cannot Start the Thing That Matters</t>
+          <t>Web banner</t>
         </is>
       </c>
       <c r="D160" s="10" t="inlineStr">
         <is>
-          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
+          <t>Webbanner</t>
         </is>
       </c>
       <c r="E160" s="11" t="n"/>
@@ -4440,22 +4404,22 @@
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B161" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[8].title</t>
+          <t>press.assets[3].note</t>
         </is>
       </c>
       <c r="C161" s="10" t="inlineStr">
         <is>
-          <t>The Open File</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="D161" s="10" t="inlineStr">
         <is>
-          <t>Die offene Akte</t>
+          <t>JPEG, 2400 × 1000</t>
         </is>
       </c>
       <c r="E161" s="11" t="n"/>
@@ -4464,22 +4428,22 @@
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B162" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[9].title</t>
+          <t>press.assets[4].label</t>
         </is>
       </c>
       <c r="C162" s="10" t="inlineStr">
         <is>
-          <t>Two Nervous Systems Walk Into a Kitchen</t>
+          <t>Social image, square</t>
         </is>
       </c>
       <c r="D162" s="10" t="inlineStr">
         <is>
-          <t>Kommen zwei Nervensysteme in eine Küche</t>
+          <t>Bild für Social Media, quadratisch</t>
         </is>
       </c>
       <c r="E162" s="11" t="n"/>
@@ -4488,22 +4452,22 @@
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B163" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[10].title</t>
+          <t>press.assets[4].note</t>
         </is>
       </c>
       <c r="C163" s="10" t="inlineStr">
         <is>
-          <t>The Argument That Was Tuesday</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="D163" s="10" t="inlineStr">
         <is>
-          <t>Der Streit, der Dienstag war</t>
+          <t>JPEG, 1080 × 1080</t>
         </is>
       </c>
       <c r="E163" s="11" t="n"/>
@@ -4512,22 +4476,22 @@
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B164" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[11].title</t>
+          <t>press.assets[5].label</t>
         </is>
       </c>
       <c r="C164" s="10" t="inlineStr">
         <is>
-          <t>The Thursday That Was Wednesday Night</t>
+          <t>Social image, portrait</t>
         </is>
       </c>
       <c r="D164" s="10" t="inlineStr">
         <is>
-          <t>Der Donnerstag, der Mittwochabend war</t>
+          <t>Bild für Social Media, Hochformat</t>
         </is>
       </c>
       <c r="E164" s="11" t="n"/>
@@ -4536,22 +4500,22 @@
     <row r="165" ht="30" customHeight="1">
       <c r="A165" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B165" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[12].title</t>
+          <t>press.assets[5].note</t>
         </is>
       </c>
       <c r="C165" s="10" t="inlineStr">
         <is>
-          <t>The Clean Panel</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="D165" s="10" t="inlineStr">
         <is>
-          <t>Das saubere Instrumentenbrett</t>
+          <t>JPEG, 1080 × 1350</t>
         </is>
       </c>
       <c r="E165" s="11" t="n"/>
@@ -4560,22 +4524,22 @@
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B166" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[13].title</t>
+          <t>press.assets[6].label</t>
         </is>
       </c>
       <c r="C166" s="10" t="inlineStr">
         <is>
-          <t>The Time the Body Was Right</t>
+          <t>Social image, landscape</t>
         </is>
       </c>
       <c r="D166" s="10" t="inlineStr">
         <is>
-          <t>Das eine Mal, als der Körper recht hatte</t>
+          <t>Bild für Social Media, Querformat</t>
         </is>
       </c>
       <c r="E166" s="11" t="n"/>
@@ -4584,22 +4548,22 @@
     <row r="167" ht="30" customHeight="1">
       <c r="A167" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B167" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[14].title</t>
+          <t>press.assets[6].note</t>
         </is>
       </c>
       <c r="C167" s="10" t="inlineStr">
         <is>
-          <t>Not About Me</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="D167" s="10" t="inlineStr">
         <is>
-          <t>Es geht nicht um mich</t>
+          <t>JPEG, 1920 × 1080</t>
         </is>
       </c>
       <c r="E167" s="11" t="n"/>
@@ -4608,22 +4572,22 @@
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B168" s="9" t="inlineStr">
         <is>
-          <t>map.chapters[15].title</t>
+          <t>press.assets[7].label</t>
         </is>
       </c>
       <c r="C168" s="10" t="inlineStr">
         <is>
-          <t>The Forecast</t>
+          <t>The opening extract</t>
         </is>
       </c>
       <c r="D168" s="10" t="inlineStr">
         <is>
-          <t>Die Vorhersage</t>
+          <t>Leseprobe, die ersten Seiten</t>
         </is>
       </c>
       <c r="E168" s="11" t="n"/>
@@ -4632,46 +4596,46 @@
     <row r="169" ht="30" customHeight="1">
       <c r="A169" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B169" s="9" t="inlineStr">
         <is>
-          <t>map.mapFooter</t>
+          <t>press.assets[7].note</t>
         </is>
       </c>
       <c r="C169" s="10" t="inlineStr">
         <is>
-          <t>The Scientific Heartbeat follows the chapters.</t>
+          <t>PDF, four pages</t>
         </is>
       </c>
       <c r="D169" s="10" t="inlineStr">
         <is>
-          <t>Nach den Kapiteln folgt „Der wissenschaftliche Herzschlag“.</t>
+          <t>PDF, vier Seiten</t>
         </is>
       </c>
       <c r="E169" s="11" t="n"/>
       <c r="F169" s="11" t="n"/>
     </row>
-    <row r="170" ht="75" customHeight="1">
+    <row r="170" ht="30" customHeight="1">
       <c r="A170" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B170" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[0]</t>
+          <t>press.photoUnavailable</t>
         </is>
       </c>
       <c r="C170" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>Author photograph available on request.</t>
         </is>
       </c>
       <c r="D170" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
+          <t>Foto der Autorin auf Anfrage.</t>
         </is>
       </c>
       <c r="E170" s="11" t="n"/>
@@ -4680,22 +4644,22 @@
     <row r="171" ht="30" customHeight="1">
       <c r="A171" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B171" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeat[1]</t>
+          <t>press.bioHeading</t>
         </is>
       </c>
       <c r="C171" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="D171" s="10" t="inlineStr">
         <is>
-          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
+          <t>Biografie</t>
         </is>
       </c>
       <c r="E171" s="11" t="n"/>
@@ -4704,58 +4668,70 @@
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="9" t="inlineStr">
         <is>
-          <t>The Investigation (page 11), “Before we begin” (page 13 markers), the three systems, page 226</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B172" s="9" t="inlineStr">
         <is>
-          <t>map.heartbeatSource</t>
+          <t>press.bios[0].label</t>
         </is>
       </c>
       <c r="C172" s="10" t="inlineStr">
         <is>
-          <t>Page 226</t>
+          <t>Short</t>
         </is>
       </c>
       <c r="D172" s="10" t="inlineStr">
         <is>
-          <t>Seite 226</t>
+          <t>Kurz</t>
         </is>
       </c>
       <c r="E172" s="11" t="n"/>
       <c r="F172" s="11" t="n"/>
     </row>
-    <row r="173" ht="22" customHeight="1">
-      <c r="A173" s="7" t="inlineStr">
-        <is>
-          <t>ABOUT THE AUTHOR</t>
-        </is>
-      </c>
-      <c r="B173" s="8" t="n"/>
-      <c r="C173" s="8" t="n"/>
-      <c r="D173" s="8" t="n"/>
-      <c r="E173" s="8" t="n"/>
-      <c r="F173" s="8" t="n"/>
+    <row r="173" ht="30" customHeight="1">
+      <c r="A173" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B173" s="9" t="inlineStr">
+        <is>
+          <t>press.bios[0].text</t>
+        </is>
+      </c>
+      <c r="C173" s="10" t="inlineStr">
+        <is>
+          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+        </is>
+      </c>
+      <c r="D173" s="10" t="inlineStr">
+        <is>
+          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+        </is>
+      </c>
+      <c r="E173" s="11" t="n"/>
+      <c r="F173" s="11" t="n"/>
     </row>
     <row r="174" ht="30" customHeight="1">
       <c r="A174" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B174" s="9" t="inlineStr">
         <is>
-          <t>author.eyebrow</t>
+          <t>press.bios[1].label</t>
         </is>
       </c>
       <c r="C174" s="10" t="inlineStr">
         <is>
-          <t>The author</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D174" s="10" t="inlineStr">
         <is>
-          <t>Die Autorin</t>
+          <t>Lang</t>
         </is>
       </c>
       <c r="E174" s="11" t="n"/>
@@ -4764,22 +4740,22 @@
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B175" s="9" t="inlineStr">
         <is>
-          <t>author.title</t>
+          <t>press.factsHeading</t>
         </is>
       </c>
       <c r="C175" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Publication</t>
         </is>
       </c>
       <c r="D175" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Bibliografische Angaben</t>
         </is>
       </c>
       <c r="E175" s="11" t="n"/>
@@ -4788,22 +4764,22 @@
     <row r="176" ht="30" customHeight="1">
       <c r="A176" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B176" s="9" t="inlineStr">
         <is>
-          <t>author.photoAlt</t>
+          <t>press.facts[0].label</t>
         </is>
       </c>
       <c r="C176" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, photographed against a dark grey background.</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="D176" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin, fotografiert vor dunkelgrauem Hintergrund.</t>
+          <t>Titel</t>
         </is>
       </c>
       <c r="E176" s="11" t="n"/>
@@ -4812,22 +4788,22 @@
     <row r="177" ht="30" customHeight="1">
       <c r="A177" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B177" s="9" t="inlineStr">
         <is>
-          <t>author.photoPlaceholder</t>
+          <t>press.facts[0].value</t>
         </is>
       </c>
       <c r="C177" s="10" t="inlineStr">
         <is>
-          <t>Author photograph to follow</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="D177" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin folgt</t>
+          <t>State. Not Situation.</t>
         </is>
       </c>
       <c r="E177" s="11" t="n"/>
@@ -4836,22 +4812,22 @@
     <row r="178" ht="30" customHeight="1">
       <c r="A178" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B178" s="9" t="inlineStr">
         <is>
-          <t>author.bio</t>
+          <t>press.facts[1].label</t>
         </is>
       </c>
       <c r="C178" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>Subtitle</t>
         </is>
       </c>
       <c r="D178" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Untertitel</t>
         </is>
       </c>
       <c r="E178" s="11" t="n"/>
@@ -4860,22 +4836,22 @@
     <row r="179" ht="30" customHeight="1">
       <c r="A179" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B179" s="9" t="inlineStr">
         <is>
-          <t>author.websiteLabel</t>
+          <t>press.facts[1].value</t>
         </is>
       </c>
       <c r="C179" s="10" t="inlineStr">
         <is>
-          <t>Practice website</t>
+          <t>A field guide to the moment before interpretation becomes reality</t>
         </is>
       </c>
       <c r="D179" s="10" t="inlineStr">
         <is>
-          <t>Website der Praxis</t>
+          <t>Ein Leitfaden für den Moment, bevor aus Deutung Wirklichkeit wird</t>
         </is>
       </c>
       <c r="E179" s="11" t="n"/>
@@ -4884,22 +4860,22 @@
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B180" s="9" t="inlineStr">
         <is>
-          <t>author.contactLabel</t>
+          <t>press.facts[2].label</t>
         </is>
       </c>
       <c r="C180" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Author</t>
         </is>
       </c>
       <c r="D180" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Autorin</t>
         </is>
       </c>
       <c r="E180" s="11" t="n"/>
@@ -4908,58 +4884,70 @@
     <row r="181" ht="30" customHeight="1">
       <c r="A181" s="9" t="inlineStr">
         <is>
-          <t>About the author</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B181" s="9" t="inlineStr">
         <is>
-          <t>author.pressLabel</t>
+          <t>press.facts[2].value</t>
         </is>
       </c>
       <c r="C181" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D181" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E181" s="11" t="n"/>
       <c r="F181" s="11" t="n"/>
     </row>
-    <row r="182" ht="22" customHeight="1">
-      <c r="A182" s="7" t="inlineStr">
-        <is>
-          <t>THE BOOK’S LAST SENTENCE, ABOVE THE NOTIFY FORM</t>
-        </is>
-      </c>
-      <c r="B182" s="8" t="n"/>
-      <c r="C182" s="8" t="n"/>
-      <c r="D182" s="8" t="n"/>
-      <c r="E182" s="8" t="n"/>
-      <c r="F182" s="8" t="n"/>
+    <row r="182" ht="30" customHeight="1">
+      <c r="A182" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B182" s="9" t="inlineStr">
+        <is>
+          <t>press.facts[3].label</t>
+        </is>
+      </c>
+      <c r="C182" s="10" t="inlineStr">
+        <is>
+          <t>Publication</t>
+        </is>
+      </c>
+      <c r="D182" s="10" t="inlineStr">
+        <is>
+          <t>Erscheinungsjahr</t>
+        </is>
+      </c>
+      <c r="E182" s="11" t="n"/>
+      <c r="F182" s="11" t="n"/>
     </row>
     <row r="183" ht="30" customHeight="1">
       <c r="A183" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B183" s="9" t="inlineStr">
         <is>
-          <t>closing.question</t>
+          <t>press.facts[3].value</t>
         </is>
       </c>
       <c r="C183" s="10" t="inlineStr">
         <is>
-          <t>Is this the situation? Or is this their state?</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D183" s="10" t="inlineStr">
         <is>
-          <t>Ist das die Situation? Oder ist das ihr Zustand?</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E183" s="11" t="n"/>
@@ -4968,74 +4956,98 @@
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="9" t="inlineStr">
         <is>
-          <t>The book’s last sentence, above the notify form</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B184" s="9" t="inlineStr">
         <is>
-          <t>closing.source</t>
+          <t>press.facts[4].label</t>
         </is>
       </c>
       <c r="C184" s="10" t="inlineStr">
         <is>
-          <t>Page 225</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="D184" s="10" t="inlineStr">
         <is>
-          <t>Seite 225</t>
+          <t>Format</t>
         </is>
       </c>
       <c r="E184" s="11" t="n"/>
       <c r="F184" s="11" t="n"/>
     </row>
-    <row r="185" ht="22" customHeight="1">
-      <c r="A185" s="7" t="inlineStr">
-        <is>
-          <t>COMPANION TOOL (CURRENTLY HIDDEN)</t>
-        </is>
-      </c>
-      <c r="B185" s="8" t="n"/>
-      <c r="C185" s="8" t="n"/>
-      <c r="D185" s="8" t="n"/>
-      <c r="E185" s="8" t="n"/>
-      <c r="F185" s="8" t="n"/>
+    <row r="185" ht="30" customHeight="1">
+      <c r="A185" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B185" s="9" t="inlineStr">
+        <is>
+          <t>press.facts[4].value</t>
+        </is>
+      </c>
+      <c r="C185" s="10" t="inlineStr">
+        <is>
+          <t>Paperback, 6 × 9 in</t>
+        </is>
+      </c>
+      <c r="D185" s="10" t="inlineStr">
+        <is>
+          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
+        </is>
+      </c>
+      <c r="E185" s="11" t="n"/>
+      <c r="F185" s="11" t="n"/>
     </row>
     <row r="186" ht="30" customHeight="1">
       <c r="A186" s="9" t="inlineStr">
         <is>
-          <t>Companion tool (currently hidden)</t>
+          <t>Press page</t>
         </is>
       </c>
       <c r="B186" s="9" t="inlineStr">
         <is>
-          <t>companion.eyebrow</t>
+          <t>press.facts[5].label</t>
         </is>
       </c>
       <c r="C186" s="10" t="inlineStr">
         <is>
-          <t>Alongside the book</t>
+          <t>Extent</t>
         </is>
       </c>
       <c r="D186" s="10" t="inlineStr">
         <is>
-          <t>Begleitend zum Buch</t>
+          <t>Umfang</t>
         </is>
       </c>
       <c r="E186" s="11" t="n"/>
       <c r="F186" s="11" t="n"/>
     </row>
-    <row r="187" ht="22" customHeight="1">
-      <c r="A187" s="7" t="inlineStr">
-        <is>
-          <t>PRESS PAGE</t>
-        </is>
-      </c>
-      <c r="B187" s="8" t="n"/>
-      <c r="C187" s="8" t="n"/>
-      <c r="D187" s="8" t="n"/>
-      <c r="E187" s="8" t="n"/>
-      <c r="F187" s="8" t="n"/>
+    <row r="187" ht="30" customHeight="1">
+      <c r="A187" s="9" t="inlineStr">
+        <is>
+          <t>Press page</t>
+        </is>
+      </c>
+      <c r="B187" s="9" t="inlineStr">
+        <is>
+          <t>press.facts[5].value</t>
+        </is>
+      </c>
+      <c r="C187" s="10" t="inlineStr">
+        <is>
+          <t>278 pages</t>
+        </is>
+      </c>
+      <c r="D187" s="10" t="inlineStr">
+        <is>
+          <t>278 Seiten</t>
+        </is>
+      </c>
+      <c r="E187" s="11" t="n"/>
+      <c r="F187" s="11" t="n"/>
     </row>
     <row r="188" ht="30" customHeight="1">
       <c r="A188" s="9" t="inlineStr">
@@ -5045,17 +5057,17 @@
       </c>
       <c r="B188" s="9" t="inlineStr">
         <is>
-          <t>press.eyebrow</t>
+          <t>press.facts[6].label</t>
         </is>
       </c>
       <c r="C188" s="10" t="inlineStr">
         <is>
-          <t>Press</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="D188" s="10" t="inlineStr">
         <is>
-          <t>Presse</t>
+          <t>ISBN-13</t>
         </is>
       </c>
       <c r="E188" s="11" t="n"/>
@@ -5069,17 +5081,17 @@
       </c>
       <c r="B189" s="9" t="inlineStr">
         <is>
-          <t>press.title</t>
+          <t>press.facts[6].value</t>
         </is>
       </c>
       <c r="C189" s="10" t="inlineStr">
         <is>
-          <t>Press materials</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="D189" s="10" t="inlineStr">
         <is>
-          <t>Pressematerial</t>
+          <t>978-2-87996-258-0</t>
         </is>
       </c>
       <c r="E189" s="11" t="n"/>
@@ -5093,17 +5105,17 @@
       </c>
       <c r="B190" s="9" t="inlineStr">
         <is>
-          <t>press.intro</t>
+          <t>press.facts[7].label</t>
         </is>
       </c>
       <c r="C190" s="10" t="inlineStr">
         <is>
-          <t>Review copies, print and digital, are available on request. Extract licensing, interviews and events by arrangement.</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="D190" s="10" t="inlineStr">
         <is>
-          <t>Rezensionsexemplare, gedruckt und digital, auf Anfrage. Abdruckrechte, Interviews und Veranstaltungen nach Absprache.</t>
+          <t>Kategorie</t>
         </is>
       </c>
       <c r="E190" s="11" t="n"/>
@@ -5117,17 +5129,17 @@
       </c>
       <c r="B191" s="9" t="inlineStr">
         <is>
-          <t>press.contactHeading</t>
+          <t>press.facts[7].value</t>
         </is>
       </c>
       <c r="C191" s="10" t="inlineStr">
         <is>
-          <t>Contact</t>
+          <t>Psychology / Cognitive psychology</t>
         </is>
       </c>
       <c r="D191" s="10" t="inlineStr">
         <is>
-          <t>Kontakt</t>
+          <t>Psychologie / Kognitive Psychologie</t>
         </is>
       </c>
       <c r="E191" s="11" t="n"/>
@@ -5141,17 +5153,17 @@
       </c>
       <c r="B192" s="9" t="inlineStr">
         <is>
-          <t>press.assetsHeading</t>
+          <t>press.facts[8].label</t>
         </is>
       </c>
       <c r="C192" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="D192" s="10" t="inlineStr">
         <is>
-          <t>Downloads</t>
+          <t>Sprache</t>
         </is>
       </c>
       <c r="E192" s="11" t="n"/>
@@ -5165,17 +5177,17 @@
       </c>
       <c r="B193" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].label</t>
+          <t>press.facts[8].value</t>
         </is>
       </c>
       <c r="C193" s="10" t="inlineStr">
         <is>
-          <t>Front cover, high resolution</t>
+          <t>English. French and German editions to follow.</t>
         </is>
       </c>
       <c r="D193" s="10" t="inlineStr">
         <is>
-          <t>Cover, Vorderseite, hohe Auflösung</t>
+          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
         </is>
       </c>
       <c r="E193" s="11" t="n"/>
@@ -5189,17 +5201,17 @@
       </c>
       <c r="B194" s="9" t="inlineStr">
         <is>
-          <t>press.assets[0].note</t>
+          <t>press.facts[9].label</t>
         </is>
       </c>
       <c r="C194" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px wide</t>
+          <t>Legal deposit</t>
         </is>
       </c>
       <c r="D194" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 px breit</t>
+          <t>Pflichtexemplar</t>
         </is>
       </c>
       <c r="E194" s="11" t="n"/>
@@ -5213,17 +5225,17 @@
       </c>
       <c r="B195" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].label</t>
+          <t>press.facts[9].value</t>
         </is>
       </c>
       <c r="C195" s="10" t="inlineStr">
         <is>
-          <t>Author photograph</t>
+          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
         </is>
       </c>
       <c r="D195" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin</t>
+          <t>Eine CIP-Aufnahme liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
         </is>
       </c>
       <c r="E195" s="11" t="n"/>
@@ -5237,17 +5249,17 @@
       </c>
       <c r="B196" s="9" t="inlineStr">
         <is>
-          <t>press.assets[1].note</t>
+          <t>press.descriptionHeading</t>
         </is>
       </c>
       <c r="C196" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>About the book</t>
         </is>
       </c>
       <c r="D196" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1600 × 1600</t>
+          <t>Über das Buch</t>
         </is>
       </c>
       <c r="E196" s="11" t="n"/>
@@ -5261,23 +5273,23 @@
       </c>
       <c r="B197" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].label</t>
+          <t>press.description[0]</t>
         </is>
       </c>
       <c r="C197" s="10" t="inlineStr">
         <is>
-          <t>Book render, transparent background</t>
+          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
         </is>
       </c>
       <c r="D197" s="10" t="inlineStr">
         <is>
-          <t>Buchansicht, freigestellt</t>
+          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
         </is>
       </c>
       <c r="E197" s="11" t="n"/>
       <c r="F197" s="11" t="n"/>
     </row>
-    <row r="198" ht="30" customHeight="1">
+    <row r="198" ht="75" customHeight="1">
       <c r="A198" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5285,17 +5297,17 @@
       </c>
       <c r="B198" s="9" t="inlineStr">
         <is>
-          <t>press.assets[2].note</t>
+          <t>press.description[1]</t>
         </is>
       </c>
       <c r="C198" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>For anyone who has ever been certain about what a situation meant, then discovered that something else was happening. And for readers interested in the psychology of how we notice, interpret and revise the world around us.</t>
         </is>
       </c>
       <c r="D198" s="10" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>Für alle, die sich schon einmal sicher waren, was eine Situation bedeutete, und dann entdeckt haben, dass etwas anderes im Gange war. Und für Leserinnen und Leser, die sich für die Psychologie interessieren: dafür, wie wir die Welt um uns herum wahrnehmen, deuten und unsere Deutung revidieren.</t>
         </is>
       </c>
       <c r="E198" s="11" t="n"/>
@@ -5309,17 +5321,17 @@
       </c>
       <c r="B199" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].label</t>
+          <t>press.mapHeading</t>
         </is>
       </c>
       <c r="C199" s="10" t="inlineStr">
         <is>
-          <t>Web banner</t>
+          <t>The chapters</t>
         </is>
       </c>
       <c r="D199" s="10" t="inlineStr">
         <is>
-          <t>Webbanner</t>
+          <t>Die Kapitel</t>
         </is>
       </c>
       <c r="E199" s="11" t="n"/>
@@ -5333,17 +5345,17 @@
       </c>
       <c r="B200" s="9" t="inlineStr">
         <is>
-          <t>press.assets[3].note</t>
+          <t>press.mapLabel</t>
         </is>
       </c>
       <c r="C200" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>This book is the</t>
         </is>
       </c>
       <c r="D200" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 2400 × 1000</t>
+          <t>Dieses Buch ist die</t>
         </is>
       </c>
       <c r="E200" s="11" t="n"/>
@@ -5357,17 +5369,17 @@
       </c>
       <c r="B201" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].label</t>
+          <t>press.mapTitle</t>
         </is>
       </c>
       <c r="C201" s="10" t="inlineStr">
         <is>
-          <t>Social image, square</t>
+          <t>Investigation.</t>
         </is>
       </c>
       <c r="D201" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, quadratisch</t>
+          <t>Untersuchung.</t>
         </is>
       </c>
       <c r="E201" s="11" t="n"/>
@@ -5381,17 +5393,17 @@
       </c>
       <c r="B202" s="9" t="inlineStr">
         <is>
-          <t>press.assets[4].note</t>
+          <t>press.mapLine</t>
         </is>
       </c>
       <c r="C202" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>16 cases. Three readings. One question: state or situation?</t>
         </is>
       </c>
       <c r="D202" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1080</t>
+          <t>16 Fälle. Drei Lesarten. Eine Frage: Zustand oder Situation?</t>
         </is>
       </c>
       <c r="E202" s="11" t="n"/>
@@ -5405,17 +5417,17 @@
       </c>
       <c r="B203" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].label</t>
+          <t>press.pageColumn</t>
         </is>
       </c>
       <c r="C203" s="10" t="inlineStr">
         <is>
-          <t>Social image, portrait</t>
+          <t>Page</t>
         </is>
       </c>
       <c r="D203" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, Hochformat</t>
+          <t>Seite</t>
         </is>
       </c>
       <c r="E203" s="11" t="n"/>
@@ -5429,17 +5441,17 @@
       </c>
       <c r="B204" s="9" t="inlineStr">
         <is>
-          <t>press.assets[5].note</t>
+          <t>press.chapters[0].title</t>
         </is>
       </c>
       <c r="C204" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>A Day That Should Have Been Fine</t>
         </is>
       </c>
       <c r="D204" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1080 × 1350</t>
+          <t>Ein Tag, der in Ordnung hätte sein sollen</t>
         </is>
       </c>
       <c r="E204" s="11" t="n"/>
@@ -5453,17 +5465,17 @@
       </c>
       <c r="B205" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].label</t>
+          <t>press.chapters[1].title</t>
         </is>
       </c>
       <c r="C205" s="10" t="inlineStr">
         <is>
-          <t>Social image, landscape</t>
+          <t>The Radar Was Right</t>
         </is>
       </c>
       <c r="D205" s="10" t="inlineStr">
         <is>
-          <t>Bild für Social Media, Querformat</t>
+          <t>Das Radar hatte recht</t>
         </is>
       </c>
       <c r="E205" s="11" t="n"/>
@@ -5477,17 +5489,17 @@
       </c>
       <c r="B206" s="9" t="inlineStr">
         <is>
-          <t>press.assets[6].note</t>
+          <t>press.chapters[2].title</t>
         </is>
       </c>
       <c r="C206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Why Sleep Loss Makes Neutral Input Feel Hostile</t>
         </is>
       </c>
       <c r="D206" s="10" t="inlineStr">
         <is>
-          <t>JPEG, 1920 × 1080</t>
+          <t>Warum sich neutraler Input bei Schlafmangel feindselig anfühlt</t>
         </is>
       </c>
       <c r="E206" s="11" t="n"/>
@@ -5501,17 +5513,17 @@
       </c>
       <c r="B207" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].label</t>
+          <t>press.chapters[3].title</t>
         </is>
       </c>
       <c r="C207" s="10" t="inlineStr">
         <is>
-          <t>The opening extract</t>
+          <t>The Relief That Becomes Itch</t>
         </is>
       </c>
       <c r="D207" s="10" t="inlineStr">
         <is>
-          <t>Leseprobe, die ersten Seiten</t>
+          <t>Die Erleichterung, die zum Juckreiz wird</t>
         </is>
       </c>
       <c r="E207" s="11" t="n"/>
@@ -5525,17 +5537,17 @@
       </c>
       <c r="B208" s="9" t="inlineStr">
         <is>
-          <t>press.assets[7].note</t>
+          <t>press.chapters[4].title</t>
         </is>
       </c>
       <c r="C208" s="10" t="inlineStr">
         <is>
-          <t>PDF, four pages</t>
+          <t>The Predictable Cue</t>
         </is>
       </c>
       <c r="D208" s="10" t="inlineStr">
         <is>
-          <t>PDF, vier Seiten</t>
+          <t>Der vorhersehbare Auslöser</t>
         </is>
       </c>
       <c r="E208" s="11" t="n"/>
@@ -5549,17 +5561,17 @@
       </c>
       <c r="B209" s="9" t="inlineStr">
         <is>
-          <t>press.photoUnavailable</t>
+          <t>press.chapters[5].title</t>
         </is>
       </c>
       <c r="C209" s="10" t="inlineStr">
         <is>
-          <t>Author photograph available on request.</t>
+          <t>Why Evenings Stretch and Mornings Shrink</t>
         </is>
       </c>
       <c r="D209" s="10" t="inlineStr">
         <is>
-          <t>Foto der Autorin auf Anfrage.</t>
+          <t>Warum sich der Abend dehnt und der Morgen schrumpft</t>
         </is>
       </c>
       <c r="E209" s="11" t="n"/>
@@ -5573,17 +5585,17 @@
       </c>
       <c r="B210" s="9" t="inlineStr">
         <is>
-          <t>press.bioHeading</t>
+          <t>press.chapters[6].title</t>
         </is>
       </c>
       <c r="C210" s="10" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Why Rest Doesn’t Always Restore</t>
         </is>
       </c>
       <c r="D210" s="10" t="inlineStr">
         <is>
-          <t>Biografie</t>
+          <t>Warum Ruhe nicht immer erholsam ist</t>
         </is>
       </c>
       <c r="E210" s="11" t="n"/>
@@ -5597,17 +5609,17 @@
       </c>
       <c r="B211" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].label</t>
+          <t>press.chapters[7].title</t>
         </is>
       </c>
       <c r="C211" s="10" t="inlineStr">
         <is>
-          <t>Short</t>
+          <t>Why You Cannot Start the Thing That Matters</t>
         </is>
       </c>
       <c r="D211" s="10" t="inlineStr">
         <is>
-          <t>Kurz</t>
+          <t>Warum Sie mit dem, was zählt, nicht anfangen können</t>
         </is>
       </c>
       <c r="E211" s="11" t="n"/>
@@ -5621,17 +5633,17 @@
       </c>
       <c r="B212" s="9" t="inlineStr">
         <is>
-          <t>press.bios[0].text</t>
+          <t>press.chapters[8].title</t>
         </is>
       </c>
       <c r="C212" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin is a clinical psychologist living and working in Luxembourg. State. Not Situation. is her first book.</t>
+          <t>The Open File</t>
         </is>
       </c>
       <c r="D212" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin ist klinische Psychologin und lebt und arbeitet in Luxemburg. State. Not Situation. ist ihr erstes Buch.</t>
+          <t>Die offene Akte</t>
         </is>
       </c>
       <c r="E212" s="11" t="n"/>
@@ -5645,17 +5657,17 @@
       </c>
       <c r="B213" s="9" t="inlineStr">
         <is>
-          <t>press.bios[1].label</t>
+          <t>press.chapters[9].title</t>
         </is>
       </c>
       <c r="C213" s="10" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>Two Nervous Systems Walk Into a Kitchen</t>
         </is>
       </c>
       <c r="D213" s="10" t="inlineStr">
         <is>
-          <t>Lang</t>
+          <t>Kommen zwei Nervensysteme in eine Küche</t>
         </is>
       </c>
       <c r="E213" s="11" t="n"/>
@@ -5669,17 +5681,17 @@
       </c>
       <c r="B214" s="9" t="inlineStr">
         <is>
-          <t>press.factsHeading</t>
+          <t>press.chapters[10].title</t>
         </is>
       </c>
       <c r="C214" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>The Argument That Was Tuesday</t>
         </is>
       </c>
       <c r="D214" s="10" t="inlineStr">
         <is>
-          <t>Bibliografische Angaben</t>
+          <t>Der Streit, der Dienstag war</t>
         </is>
       </c>
       <c r="E214" s="11" t="n"/>
@@ -5693,17 +5705,17 @@
       </c>
       <c r="B215" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].label</t>
+          <t>press.chapters[11].title</t>
         </is>
       </c>
       <c r="C215" s="10" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>The Thursday That Was Wednesday Night</t>
         </is>
       </c>
       <c r="D215" s="10" t="inlineStr">
         <is>
-          <t>Titel</t>
+          <t>Der Donnerstag, der Mittwochabend war</t>
         </is>
       </c>
       <c r="E215" s="11" t="n"/>
@@ -5717,17 +5729,17 @@
       </c>
       <c r="B216" s="9" t="inlineStr">
         <is>
-          <t>press.facts[0].value</t>
+          <t>press.chapters[12].title</t>
         </is>
       </c>
       <c r="C216" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>The Clean Panel</t>
         </is>
       </c>
       <c r="D216" s="10" t="inlineStr">
         <is>
-          <t>State. Not Situation.</t>
+          <t>Das saubere Instrumentenbrett</t>
         </is>
       </c>
       <c r="E216" s="11" t="n"/>
@@ -5741,17 +5753,17 @@
       </c>
       <c r="B217" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].label</t>
+          <t>press.chapters[13].title</t>
         </is>
       </c>
       <c r="C217" s="10" t="inlineStr">
         <is>
-          <t>Subtitle</t>
+          <t>The Time the Body Was Right</t>
         </is>
       </c>
       <c r="D217" s="10" t="inlineStr">
         <is>
-          <t>Untertitel</t>
+          <t>Das eine Mal, als der Körper recht hatte</t>
         </is>
       </c>
       <c r="E217" s="11" t="n"/>
@@ -5765,17 +5777,17 @@
       </c>
       <c r="B218" s="9" t="inlineStr">
         <is>
-          <t>press.facts[1].value</t>
+          <t>press.chapters[14].title</t>
         </is>
       </c>
       <c r="C218" s="10" t="inlineStr">
         <is>
-          <t>A field guide to the moment before interpretation becomes reality</t>
+          <t>Not About Me</t>
         </is>
       </c>
       <c r="D218" s="10" t="inlineStr">
         <is>
-          <t>Ein Bestimmungsbuch für den Moment, bevor aus Deutung Wirklichkeit wird</t>
+          <t>Es geht nicht um mich</t>
         </is>
       </c>
       <c r="E218" s="11" t="n"/>
@@ -5789,23 +5801,23 @@
       </c>
       <c r="B219" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].label</t>
+          <t>press.chapters[15].title</t>
         </is>
       </c>
       <c r="C219" s="10" t="inlineStr">
         <is>
-          <t>Author</t>
+          <t>The Forecast</t>
         </is>
       </c>
       <c r="D219" s="10" t="inlineStr">
         <is>
-          <t>Autorin</t>
+          <t>Die Vorhersage</t>
         </is>
       </c>
       <c r="E219" s="11" t="n"/>
       <c r="F219" s="11" t="n"/>
     </row>
-    <row r="220" ht="30" customHeight="1">
+    <row r="220" ht="90" customHeight="1">
       <c r="A220" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5813,17 +5825,17 @@
       </c>
       <c r="B220" s="9" t="inlineStr">
         <is>
-          <t>press.facts[2].value</t>
+          <t>press.sortingTool</t>
         </is>
       </c>
       <c r="C220" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>The chapters that follow are organised around three systems that shape how your body’s signals get weighted before your mind builds a story. They are not brain regions or neural pathways. They are a sorting tool, a way to ask three questions when everything feels wrong at once.</t>
         </is>
       </c>
       <c r="D220" s="10" t="inlineStr">
         <is>
-          <t>Ivana Budišin</t>
+          <t>Die folgenden Kapitel sind um drei Systeme herum aufgebaut, die prägen, wie die Signale Ihres Körpers gewichtet werden, bevor Ihr Kopf daraus eine Geschichte macht. Es sind keine Hirnregionen und keine Nervenbahnen. Diese Systeme sind ein Werkzeug zum Sortieren, eine Art, drei Fragen zu stellen, wenn sich alles auf einmal falsch anfühlt.</t>
         </is>
       </c>
       <c r="E220" s="11" t="n"/>
@@ -5837,23 +5849,23 @@
       </c>
       <c r="B221" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].label</t>
+          <t>press.sourcesHeading</t>
         </is>
       </c>
       <c r="C221" s="10" t="inlineStr">
         <is>
-          <t>Publisher</t>
+          <t>Sources and evidence</t>
         </is>
       </c>
       <c r="D221" s="10" t="inlineStr">
         <is>
-          <t>Verlag</t>
+          <t>Quellen und Belege</t>
         </is>
       </c>
       <c r="E221" s="11" t="n"/>
       <c r="F221" s="11" t="n"/>
     </row>
-    <row r="222" ht="30" customHeight="1">
+    <row r="222" ht="75" customHeight="1">
       <c r="A222" s="9" t="inlineStr">
         <is>
           <t>Press page</t>
@@ -5861,17 +5873,17 @@
       </c>
       <c r="B222" s="9" t="inlineStr">
         <is>
-          <t>press.facts[3].value</t>
+          <t>press.sources[0]</t>
         </is>
       </c>
       <c r="C222" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxembourg</t>
+          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
         </is>
       </c>
       <c r="D222" s="10" t="inlineStr">
         <is>
-          <t>Budisin Publishing, Luxemburg</t>
+          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
         </is>
       </c>
       <c r="E222" s="11" t="n"/>
@@ -5885,17 +5897,17 @@
       </c>
       <c r="B223" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].label</t>
+          <t>press.sources[1]</t>
         </is>
       </c>
       <c r="C223" s="10" t="inlineStr">
         <is>
-          <t>Publication</t>
+          <t>Leaving them out would make the argument look tidier than it is.</t>
         </is>
       </c>
       <c r="D223" s="10" t="inlineStr">
         <is>
-          <t>Erscheinungsjahr</t>
+          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
         </is>
       </c>
       <c r="E223" s="11" t="n"/>
@@ -5909,17 +5921,17 @@
       </c>
       <c r="B224" s="9" t="inlineStr">
         <is>
-          <t>press.facts[4].value</t>
+          <t>press.sourcesLabel</t>
         </is>
       </c>
       <c r="C224" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>The Scientific Heartbeat, page 226</t>
         </is>
       </c>
       <c r="D224" s="10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>Der wissenschaftliche Herzschlag, Seite 226</t>
         </is>
       </c>
       <c r="E224" s="11" t="n"/>
@@ -5933,17 +5945,17 @@
       </c>
       <c r="B225" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].label</t>
+          <t>press.creditsHeading</t>
         </is>
       </c>
       <c r="C225" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Credits</t>
         </is>
       </c>
       <c r="D225" s="10" t="inlineStr">
         <is>
-          <t>Format</t>
+          <t>Mitwirkende</t>
         </is>
       </c>
       <c r="E225" s="11" t="n"/>
@@ -5957,17 +5969,17 @@
       </c>
       <c r="B226" s="9" t="inlineStr">
         <is>
-          <t>press.facts[5].value</t>
+          <t>press.credits[0].label</t>
         </is>
       </c>
       <c r="C226" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 in</t>
+          <t>Cover design</t>
         </is>
       </c>
       <c r="D226" s="10" t="inlineStr">
         <is>
-          <t>Paperback, 6 × 9 Zoll (15,2 × 22,9 cm)</t>
+          <t>Umschlaggestaltung</t>
         </is>
       </c>
       <c r="E226" s="11" t="n"/>
@@ -5981,17 +5993,17 @@
       </c>
       <c r="B227" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].label</t>
+          <t>press.credits[0].value</t>
         </is>
       </c>
       <c r="C227" s="10" t="inlineStr">
         <is>
-          <t>Extent</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="D227" s="10" t="inlineStr">
         <is>
-          <t>Umfang</t>
+          <t>Zoe Larusson</t>
         </is>
       </c>
       <c r="E227" s="11" t="n"/>
@@ -6005,17 +6017,17 @@
       </c>
       <c r="B228" s="9" t="inlineStr">
         <is>
-          <t>press.facts[6].value</t>
+          <t>press.credits[1].label</t>
         </is>
       </c>
       <c r="C228" s="10" t="inlineStr">
         <is>
-          <t>278 pages</t>
+          <t>Book design and typesetting</t>
         </is>
       </c>
       <c r="D228" s="10" t="inlineStr">
         <is>
-          <t>278 Seiten</t>
+          <t>Buchgestaltung und Satz</t>
         </is>
       </c>
       <c r="E228" s="11" t="n"/>
@@ -6029,17 +6041,17 @@
       </c>
       <c r="B229" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].label</t>
+          <t>press.credits[1].value</t>
         </is>
       </c>
       <c r="C229" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="D229" s="10" t="inlineStr">
         <is>
-          <t>ISBN-13</t>
+          <t>Ivana Budišin</t>
         </is>
       </c>
       <c r="E229" s="11" t="n"/>
@@ -6053,17 +6065,17 @@
       </c>
       <c r="B230" s="9" t="inlineStr">
         <is>
-          <t>press.facts[7].value</t>
+          <t>press.credits[2].label</t>
         </is>
       </c>
       <c r="C230" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Published by</t>
         </is>
       </c>
       <c r="D230" s="10" t="inlineStr">
         <is>
-          <t>978-2-87996-258-0</t>
+          <t>Erschienen bei</t>
         </is>
       </c>
       <c r="E230" s="11" t="n"/>
@@ -6077,17 +6089,17 @@
       </c>
       <c r="B231" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].label</t>
+          <t>press.credits[2].value</t>
         </is>
       </c>
       <c r="C231" s="10" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="D231" s="10" t="inlineStr">
         <is>
-          <t>Kategorie</t>
+          <t>Budisin Publishing</t>
         </is>
       </c>
       <c r="E231" s="11" t="n"/>
@@ -6101,65 +6113,53 @@
       </c>
       <c r="B232" s="9" t="inlineStr">
         <is>
-          <t>press.facts[8].value</t>
+          <t>press.back</t>
         </is>
       </c>
       <c r="C232" s="10" t="inlineStr">
         <is>
-          <t>Psychology / Cognitive psychology</t>
+          <t>Back to the book</t>
         </is>
       </c>
       <c r="D232" s="10" t="inlineStr">
         <is>
-          <t>Psychologie / Kognitive Psychologie</t>
+          <t>Zurück zum Buch</t>
         </is>
       </c>
       <c r="E232" s="11" t="n"/>
       <c r="F232" s="11" t="n"/>
     </row>
-    <row r="233" ht="30" customHeight="1">
-      <c r="A233" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B233" s="9" t="inlineStr">
-        <is>
-          <t>press.facts[9].label</t>
-        </is>
-      </c>
-      <c r="C233" s="10" t="inlineStr">
-        <is>
-          <t>Language</t>
-        </is>
-      </c>
-      <c r="D233" s="10" t="inlineStr">
-        <is>
-          <t>Sprache</t>
-        </is>
-      </c>
-      <c r="E233" s="11" t="n"/>
-      <c r="F233" s="11" t="n"/>
+    <row r="233" ht="22" customHeight="1">
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t>FOOT OF EVERY PAGE</t>
+        </is>
+      </c>
+      <c r="B233" s="8" t="n"/>
+      <c r="C233" s="8" t="n"/>
+      <c r="D233" s="8" t="n"/>
+      <c r="E233" s="8" t="n"/>
+      <c r="F233" s="8" t="n"/>
     </row>
     <row r="234" ht="30" customHeight="1">
       <c r="A234" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B234" s="9" t="inlineStr">
         <is>
-          <t>press.facts[9].value</t>
+          <t>footer.band</t>
         </is>
       </c>
       <c r="C234" s="10" t="inlineStr">
         <is>
-          <t>English. French and German editions to follow.</t>
+          <t>Before you believe the story.</t>
         </is>
       </c>
       <c r="D234" s="10" t="inlineStr">
         <is>
-          <t>Englisch. Französische und deutsche Ausgabe folgen.</t>
+          <t>Bevor Sie der Geschichte glauben.</t>
         </is>
       </c>
       <c r="E234" s="11" t="n"/>
@@ -6168,22 +6168,22 @@
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B235" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].label</t>
+          <t>footer.pressLink</t>
         </is>
       </c>
       <c r="C235" s="10" t="inlineStr">
         <is>
-          <t>Legal deposit</t>
+          <t>Press</t>
         </is>
       </c>
       <c r="D235" s="10" t="inlineStr">
         <is>
-          <t>Pflichtexemplar</t>
+          <t>Presse</t>
         </is>
       </c>
       <c r="E235" s="11" t="n"/>
@@ -6192,22 +6192,22 @@
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B236" s="9" t="inlineStr">
         <is>
-          <t>press.facts[10].value</t>
+          <t>footer.contactLink</t>
         </is>
       </c>
       <c r="C236" s="10" t="inlineStr">
         <is>
-          <t>A CIP record is available at Bibliothèque nationale du Luxembourg.</t>
+          <t>Contact</t>
         </is>
       </c>
       <c r="D236" s="10" t="inlineStr">
         <is>
-          <t>Ein CIP-Eintrag liegt bei der Bibliothèque nationale du Luxembourg vor.</t>
+          <t>Kontakt</t>
         </is>
       </c>
       <c r="E236" s="11" t="n"/>
@@ -6216,94 +6216,82 @@
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Foot of every page</t>
         </is>
       </c>
       <c r="B237" s="9" t="inlineStr">
         <is>
-          <t>press.descriptionHeading</t>
+          <t>footer.rights</t>
         </is>
       </c>
       <c r="C237" s="10" t="inlineStr">
         <is>
-          <t>About the book</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="D237" s="10" t="inlineStr">
         <is>
-          <t>Über das Buch</t>
+          <t>© 2026 Budisin Publishing</t>
         </is>
       </c>
       <c r="E237" s="11" t="n"/>
       <c r="F237" s="11" t="n"/>
     </row>
-    <row r="238" ht="30" customHeight="1">
-      <c r="A238" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B238" s="9" t="inlineStr">
-        <is>
-          <t>press.description[0]</t>
-        </is>
-      </c>
-      <c r="C238" s="10" t="inlineStr">
-        <is>
-          <t>It is less interested in teaching you to trust your instincts than in showing you what, exactly, you are trusting.</t>
-        </is>
-      </c>
-      <c r="D238" s="10" t="inlineStr">
-        <is>
-          <t>Es will Ihnen weniger beibringen, Ihren Instinkten zu vertrauen, als Ihnen zeigen, worauf genau Sie da vertrauen.</t>
-        </is>
-      </c>
-      <c r="E238" s="11" t="n"/>
-      <c r="F238" s="11" t="n"/>
+    <row r="238" ht="22" customHeight="1">
+      <c r="A238" s="7" t="inlineStr">
+        <is>
+          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
+        </is>
+      </c>
+      <c r="B238" s="8" t="n"/>
+      <c r="C238" s="8" t="n"/>
+      <c r="D238" s="8" t="n"/>
+      <c r="E238" s="8" t="n"/>
+      <c r="F238" s="8" t="n"/>
     </row>
     <row r="239" ht="30" customHeight="1">
       <c r="A239" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B239" s="9" t="inlineStr">
         <is>
-          <t>press.description[1]</t>
+          <t>a11y.mainLandmark</t>
         </is>
       </c>
       <c r="C239" s="10" t="inlineStr">
         <is>
-          <t>16 cases. Three readings. One question: state or situation?</t>
+          <t>Main content</t>
         </is>
       </c>
       <c r="D239" s="10" t="inlineStr">
         <is>
-          <t>16 Fälle. Drei Befunde. Eine Frage: Zustand oder Situation?</t>
+          <t>Hauptinhalt</t>
         </is>
       </c>
       <c r="E239" s="11" t="n"/>
       <c r="F239" s="11" t="n"/>
     </row>
-    <row r="240" ht="75" customHeight="1">
+    <row r="240" ht="30" customHeight="1">
       <c r="A240" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B240" s="9" t="inlineStr">
         <is>
-          <t>press.description[2]</t>
+          <t>a11y.coverFigure</t>
         </is>
       </c>
       <c r="C240" s="10" t="inlineStr">
         <is>
-          <t>Each chapter has three parts here: a short note on where the thinking came from, a list of the work the chapter is built on, and a list of the work that limits it, complicates it, or explains the same evidence differently.</t>
+          <t>The book</t>
         </is>
       </c>
       <c r="D240" s="10" t="inlineStr">
         <is>
-          <t>Jedes Kapitel hat hier drei Teile: eine kurze Notiz dazu, woher die Überlegungen kamen, eine Liste der Arbeiten, auf denen das Kapitel aufbaut, und eine Liste der Arbeiten, die es einschränken, komplizierter machen oder dieselben Belege anders erklären.</t>
+          <t>Das Buch</t>
         </is>
       </c>
       <c r="E240" s="11" t="n"/>
@@ -6312,22 +6300,22 @@
     <row r="241" ht="30" customHeight="1">
       <c r="A241" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B241" s="9" t="inlineStr">
         <is>
-          <t>press.description[3]</t>
+          <t>a11y.languageSwitcher</t>
         </is>
       </c>
       <c r="C241" s="10" t="inlineStr">
         <is>
-          <t>Leaving them out would make the argument look tidier than it is.</t>
+          <t>Choose language</t>
         </is>
       </c>
       <c r="D241" s="10" t="inlineStr">
         <is>
-          <t>Ließe man sie weg, sähe die Argumentation aufgeräumter aus, als sie ist.</t>
+          <t>Sprache wählen</t>
         </is>
       </c>
       <c r="E241" s="11" t="n"/>
@@ -6336,629 +6324,29 @@
     <row r="242" ht="30" customHeight="1">
       <c r="A242" s="9" t="inlineStr">
         <is>
-          <t>Press page</t>
+          <t>Screen-reader labels (invisible, but read aloud)</t>
         </is>
       </c>
       <c r="B242" s="9" t="inlineStr">
         <is>
-          <t>press.creditsHeading</t>
+          <t>a11y.menu</t>
         </is>
       </c>
       <c r="C242" s="10" t="inlineStr">
         <is>
-          <t>Credits</t>
+          <t>Menu</t>
         </is>
       </c>
       <c r="D242" s="10" t="inlineStr">
         <is>
-          <t>Mitwirkende</t>
+          <t>Menü</t>
         </is>
       </c>
       <c r="E242" s="11" t="n"/>
       <c r="F242" s="11" t="n"/>
     </row>
-    <row r="243" ht="30" customHeight="1">
-      <c r="A243" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B243" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[0].label</t>
-        </is>
-      </c>
-      <c r="C243" s="10" t="inlineStr">
-        <is>
-          <t>Cover design</t>
-        </is>
-      </c>
-      <c r="D243" s="10" t="inlineStr">
-        <is>
-          <t>Umschlaggestaltung</t>
-        </is>
-      </c>
-      <c r="E243" s="11" t="n"/>
-      <c r="F243" s="11" t="n"/>
-    </row>
-    <row r="244" ht="30" customHeight="1">
-      <c r="A244" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B244" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[0].value</t>
-        </is>
-      </c>
-      <c r="C244" s="10" t="inlineStr">
-        <is>
-          <t>Zoe Larusson</t>
-        </is>
-      </c>
-      <c r="D244" s="10" t="inlineStr">
-        <is>
-          <t>Zoe Larusson</t>
-        </is>
-      </c>
-      <c r="E244" s="11" t="n"/>
-      <c r="F244" s="11" t="n"/>
-    </row>
-    <row r="245" ht="30" customHeight="1">
-      <c r="A245" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B245" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[1].label</t>
-        </is>
-      </c>
-      <c r="C245" s="10" t="inlineStr">
-        <is>
-          <t>Book design and typesetting</t>
-        </is>
-      </c>
-      <c r="D245" s="10" t="inlineStr">
-        <is>
-          <t>Buchgestaltung und Satz</t>
-        </is>
-      </c>
-      <c r="E245" s="11" t="n"/>
-      <c r="F245" s="11" t="n"/>
-    </row>
-    <row r="246" ht="30" customHeight="1">
-      <c r="A246" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B246" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[1].value</t>
-        </is>
-      </c>
-      <c r="C246" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="D246" s="10" t="inlineStr">
-        <is>
-          <t>Ivana Budišin</t>
-        </is>
-      </c>
-      <c r="E246" s="11" t="n"/>
-      <c r="F246" s="11" t="n"/>
-    </row>
-    <row r="247" ht="30" customHeight="1">
-      <c r="A247" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B247" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[2].label</t>
-        </is>
-      </c>
-      <c r="C247" s="10" t="inlineStr">
-        <is>
-          <t>Published by</t>
-        </is>
-      </c>
-      <c r="D247" s="10" t="inlineStr">
-        <is>
-          <t>Erschienen bei</t>
-        </is>
-      </c>
-      <c r="E247" s="11" t="n"/>
-      <c r="F247" s="11" t="n"/>
-    </row>
-    <row r="248" ht="30" customHeight="1">
-      <c r="A248" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B248" s="9" t="inlineStr">
-        <is>
-          <t>press.credits[2].value</t>
-        </is>
-      </c>
-      <c r="C248" s="10" t="inlineStr">
-        <is>
-          <t>Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="D248" s="10" t="inlineStr">
-        <is>
-          <t>Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="E248" s="11" t="n"/>
-      <c r="F248" s="11" t="n"/>
-    </row>
-    <row r="249" ht="30" customHeight="1">
-      <c r="A249" s="9" t="inlineStr">
-        <is>
-          <t>Press page</t>
-        </is>
-      </c>
-      <c r="B249" s="9" t="inlineStr">
-        <is>
-          <t>press.back</t>
-        </is>
-      </c>
-      <c r="C249" s="10" t="inlineStr">
-        <is>
-          <t>Back to the book</t>
-        </is>
-      </c>
-      <c r="D249" s="10" t="inlineStr">
-        <is>
-          <t>Zurück zum Buch</t>
-        </is>
-      </c>
-      <c r="E249" s="11" t="n"/>
-      <c r="F249" s="11" t="n"/>
-    </row>
-    <row r="250" ht="22" customHeight="1">
-      <c r="A250" s="7" t="inlineStr">
-        <is>
-          <t>FOOT OF EVERY PAGE</t>
-        </is>
-      </c>
-      <c r="B250" s="8" t="n"/>
-      <c r="C250" s="8" t="n"/>
-      <c r="D250" s="8" t="n"/>
-      <c r="E250" s="8" t="n"/>
-      <c r="F250" s="8" t="n"/>
-    </row>
-    <row r="251" ht="30" customHeight="1">
-      <c r="A251" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B251" s="9" t="inlineStr">
-        <is>
-          <t>footer.band</t>
-        </is>
-      </c>
-      <c r="C251" s="10" t="inlineStr">
-        <is>
-          <t>Before you believe the story.</t>
-        </is>
-      </c>
-      <c r="D251" s="10" t="inlineStr">
-        <is>
-          <t>Bevor Sie der Geschichte glauben.</t>
-        </is>
-      </c>
-      <c r="E251" s="11" t="n"/>
-      <c r="F251" s="11" t="n"/>
-    </row>
-    <row r="252" ht="30" customHeight="1">
-      <c r="A252" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B252" s="9" t="inlineStr">
-        <is>
-          <t>footer.method[0]</t>
-        </is>
-      </c>
-      <c r="C252" s="10" t="inlineStr">
-        <is>
-          <t>Read the dashboard.</t>
-        </is>
-      </c>
-      <c r="D252" s="10" t="inlineStr">
-        <is>
-          <t>Lesen Sie die Instrumente ab.</t>
-        </is>
-      </c>
-      <c r="E252" s="11" t="n"/>
-      <c r="F252" s="11" t="n"/>
-    </row>
-    <row r="253" ht="30" customHeight="1">
-      <c r="A253" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B253" s="9" t="inlineStr">
-        <is>
-          <t>footer.method[1]</t>
-        </is>
-      </c>
-      <c r="C253" s="10" t="inlineStr">
-        <is>
-          <t>Delay the story.</t>
-        </is>
-      </c>
-      <c r="D253" s="10" t="inlineStr">
-        <is>
-          <t>Lassen Sie die Geschichte warten.</t>
-        </is>
-      </c>
-      <c r="E253" s="11" t="n"/>
-      <c r="F253" s="11" t="n"/>
-    </row>
-    <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B254" s="9" t="inlineStr">
-        <is>
-          <t>footer.method[2]</t>
-        </is>
-      </c>
-      <c r="C254" s="10" t="inlineStr">
-        <is>
-          <t>Take the reading again.</t>
-        </is>
-      </c>
-      <c r="D254" s="10" t="inlineStr">
-        <is>
-          <t>Lesen Sie noch einmal ab.</t>
-        </is>
-      </c>
-      <c r="E254" s="11" t="n"/>
-      <c r="F254" s="11" t="n"/>
-    </row>
-    <row r="255" ht="30" customHeight="1">
-      <c r="A255" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B255" s="9" t="inlineStr">
-        <is>
-          <t>footer.rights</t>
-        </is>
-      </c>
-      <c r="C255" s="10" t="inlineStr">
-        <is>
-          <t>© 2026 Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="D255" s="10" t="inlineStr">
-        <is>
-          <t>© 2026 Budisin Publishing</t>
-        </is>
-      </c>
-      <c r="E255" s="11" t="n"/>
-      <c r="F255" s="11" t="n"/>
-    </row>
-    <row r="256" ht="30" customHeight="1">
-      <c r="A256" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B256" s="9" t="inlineStr">
-        <is>
-          <t>footer.pressLink</t>
-        </is>
-      </c>
-      <c r="C256" s="10" t="inlineStr">
-        <is>
-          <t>Press</t>
-        </is>
-      </c>
-      <c r="D256" s="10" t="inlineStr">
-        <is>
-          <t>Presse</t>
-        </is>
-      </c>
-      <c r="E256" s="11" t="n"/>
-      <c r="F256" s="11" t="n"/>
-    </row>
-    <row r="257" ht="30" customHeight="1">
-      <c r="A257" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B257" s="9" t="inlineStr">
-        <is>
-          <t>footer.contactLink</t>
-        </is>
-      </c>
-      <c r="C257" s="10" t="inlineStr">
-        <is>
-          <t>Contact</t>
-        </is>
-      </c>
-      <c r="D257" s="10" t="inlineStr">
-        <is>
-          <t>Kontakt</t>
-        </is>
-      </c>
-      <c r="E257" s="11" t="n"/>
-      <c r="F257" s="11" t="n"/>
-    </row>
-    <row r="258" ht="30" customHeight="1">
-      <c r="A258" s="9" t="inlineStr">
-        <is>
-          <t>Foot of every page</t>
-        </is>
-      </c>
-      <c r="B258" s="9" t="inlineStr">
-        <is>
-          <t>footer.madeLine</t>
-        </is>
-      </c>
-      <c r="C258" s="10" t="inlineStr">
-        <is>
-          <t>Same life. Different instrument settings.</t>
-        </is>
-      </c>
-      <c r="D258" s="10" t="inlineStr">
-        <is>
-          <t>Dasselbe Leben. Andere Einstellungen am Instrument.</t>
-        </is>
-      </c>
-      <c r="E258" s="11" t="n"/>
-      <c r="F258" s="11" t="n"/>
-    </row>
-    <row r="259" ht="22" customHeight="1">
-      <c r="A259" s="7" t="inlineStr">
-        <is>
-          <t>SCREEN-READER LABELS (INVISIBLE, BUT READ ALOUD)</t>
-        </is>
-      </c>
-      <c r="B259" s="8" t="n"/>
-      <c r="C259" s="8" t="n"/>
-      <c r="D259" s="8" t="n"/>
-      <c r="E259" s="8" t="n"/>
-      <c r="F259" s="8" t="n"/>
-    </row>
-    <row r="260" ht="30" customHeight="1">
-      <c r="A260" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B260" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mainLandmark</t>
-        </is>
-      </c>
-      <c r="C260" s="10" t="inlineStr">
-        <is>
-          <t>Main content</t>
-        </is>
-      </c>
-      <c r="D260" s="10" t="inlineStr">
-        <is>
-          <t>Hauptinhalt</t>
-        </is>
-      </c>
-      <c r="E260" s="11" t="n"/>
-      <c r="F260" s="11" t="n"/>
-    </row>
-    <row r="261" ht="30" customHeight="1">
-      <c r="A261" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B261" s="9" t="inlineStr">
-        <is>
-          <t>a11y.coverFigure</t>
-        </is>
-      </c>
-      <c r="C261" s="10" t="inlineStr">
-        <is>
-          <t>The book</t>
-        </is>
-      </c>
-      <c r="D261" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch</t>
-        </is>
-      </c>
-      <c r="E261" s="11" t="n"/>
-      <c r="F261" s="11" t="n"/>
-    </row>
-    <row r="262" ht="30" customHeight="1">
-      <c r="A262" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B262" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageSwitcher</t>
-        </is>
-      </c>
-      <c r="C262" s="10" t="inlineStr">
-        <is>
-          <t>Choose language</t>
-        </is>
-      </c>
-      <c r="D262" s="10" t="inlineStr">
-        <is>
-          <t>Sprache wählen</t>
-        </is>
-      </c>
-      <c r="E262" s="11" t="n"/>
-      <c r="F262" s="11" t="n"/>
-    </row>
-    <row r="263" ht="30" customHeight="1">
-      <c r="A263" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B263" s="9" t="inlineStr">
-        <is>
-          <t>a11y.languageComing</t>
-        </is>
-      </c>
-      <c r="C263" s="10" t="inlineStr">
-        <is>
-          <t>edition to follow</t>
-        </is>
-      </c>
-      <c r="D263" s="10" t="inlineStr">
-        <is>
-          <t>Ausgabe folgt</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="n"/>
-      <c r="F263" s="11" t="n"/>
-    </row>
-    <row r="264" ht="30" customHeight="1">
-      <c r="A264" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B264" s="9" t="inlineStr">
-        <is>
-          <t>a11y.casesRegion</t>
-        </is>
-      </c>
-      <c r="C264" s="10" t="inlineStr">
-        <is>
-          <t>Case evidence pages from the book</t>
-        </is>
-      </c>
-      <c r="D264" s="10" t="inlineStr">
-        <is>
-          <t>Seiten mit Beweismaterial aus dem Buch</t>
-        </is>
-      </c>
-      <c r="E264" s="11" t="n"/>
-      <c r="F264" s="11" t="n"/>
-    </row>
-    <row r="265" ht="30" customHeight="1">
-      <c r="A265" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B265" s="9" t="inlineStr">
-        <is>
-          <t>a11y.bookOpening</t>
-        </is>
-      </c>
-      <c r="C265" s="10" t="inlineStr">
-        <is>
-          <t>The book, opening</t>
-        </is>
-      </c>
-      <c r="D265" s="10" t="inlineStr">
-        <is>
-          <t>Das Buch beim Aufschlagen</t>
-        </is>
-      </c>
-      <c r="E265" s="11" t="n"/>
-      <c r="F265" s="11" t="n"/>
-    </row>
-    <row r="266" ht="30" customHeight="1">
-      <c r="A266" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B266" s="9" t="inlineStr">
-        <is>
-          <t>a11y.misreadingRegion</t>
-        </is>
-      </c>
-      <c r="C266" s="10" t="inlineStr">
-        <is>
-          <t>Page 10 of the book</t>
-        </is>
-      </c>
-      <c r="D266" s="10" t="inlineStr">
-        <is>
-          <t>Seite 10 des Buches</t>
-        </is>
-      </c>
-      <c r="E266" s="11" t="n"/>
-      <c r="F266" s="11" t="n"/>
-    </row>
-    <row r="267" ht="30" customHeight="1">
-      <c r="A267" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B267" s="9" t="inlineStr">
-        <is>
-          <t>a11y.mapRegion</t>
-        </is>
-      </c>
-      <c r="C267" s="10" t="inlineStr">
-        <is>
-          <t>A map of the book</t>
-        </is>
-      </c>
-      <c r="D267" s="10" t="inlineStr">
-        <is>
-          <t>Eine Karte des Buches</t>
-        </is>
-      </c>
-      <c r="E267" s="11" t="n"/>
-      <c r="F267" s="11" t="n"/>
-    </row>
-    <row r="268" ht="30" customHeight="1">
-      <c r="A268" s="9" t="inlineStr">
-        <is>
-          <t>Screen-reader labels (invisible, but read aloud)</t>
-        </is>
-      </c>
-      <c r="B268" s="9" t="inlineStr">
-        <is>
-          <t>a11y.evidenceRegion</t>
-        </is>
-      </c>
-      <c r="C268" s="10" t="inlineStr">
-        <is>
-          <t>Confidence markers, page 13</t>
-        </is>
-      </c>
-      <c r="D268" s="10" t="inlineStr">
-        <is>
-          <t>Markierungen zu den Belegen, Seite 13</t>
-        </is>
-      </c>
-      <c r="E268" s="11" t="n"/>
-      <c r="F268" s="11" t="n"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F268"/>
+  <autoFilter ref="A1:F242"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>